--- a/karte/out/Wangerooge_West_Landmarken_v1.xlsx
+++ b/karte/out/Wangerooge_West_Landmarken_v1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Landmarken" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pfade prüfen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Übersicht" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Landmarken" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pfade prüfen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Landmarken'!$A$1:$M$885</definedName>
@@ -44229,7 +44229,7 @@
       </c>
       <c r="F869" s="3" t="inlineStr">
         <is>
-          <t>OSM + aloeus.de: Zum Westen 32</t>
+          <t>OSM + aloeus.de: Zum Westen 32 + Feldbegehung JNK 13.10.2026</t>
         </is>
       </c>
       <c r="G869" s="9" t="n">

--- a/karte/out/Wangerooge_West_Landmarken_v1.xlsx
+++ b/karte/out/Wangerooge_West_Landmarken_v1.xlsx
@@ -45187,11 +45187,7 @@
           <t>footway</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Belag dirt, Länge 345 m, Luftbild sichtbar 29%</t>
-        </is>
-      </c>
+      <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45209,11 +45205,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Belag dirt, Länge 100 m, Luftbild sichtbar 15%</t>
-        </is>
-      </c>
+      <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45231,11 +45223,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Belag grass, Länge 34 m, Luftbild sichtbar 20%</t>
-        </is>
-      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45253,11 +45241,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Belag grass, Länge 191 m, Luftbild sichtbar 35%</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45275,11 +45259,7 @@
           <t>footway</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Belag unbekannt, Länge 46 m, Luftbild sichtbar 37%</t>
-        </is>
-      </c>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45297,11 +45277,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Belag dirt, Länge 38 m, Luftbild sichtbar 23%</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45319,11 +45295,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Belag sand, Länge 1308 m, Luftbild sichtbar 31%</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45341,11 +45313,7 @@
           <t>footway</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Belag unbekannt, Länge 72 m, Luftbild sichtbar 40%</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45363,11 +45331,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Belag sand, Länge 6 m, Luftbild sichtbar 43%</t>
-        </is>
-      </c>
+      <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45385,11 +45349,7 @@
           <t>footway</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Belag unbekannt, Länge 51 m, Luftbild sichtbar 31%</t>
-        </is>
-      </c>
+      <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45407,11 +45367,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Belag grass, Länge 97 m, Luftbild sichtbar 5%</t>
-        </is>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45429,11 +45385,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Belag sand, Länge 50 m, Luftbild sichtbar 2%</t>
-        </is>
-      </c>
+      <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45451,11 +45403,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Belag dirt, Länge 24 m, Luftbild sichtbar 24%</t>
-        </is>
-      </c>
+      <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45473,11 +45421,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Belag dirt, Länge 54 m, Luftbild sichtbar 35%</t>
-        </is>
-      </c>
+      <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45495,11 +45439,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Belag sand, Länge 155 m, Luftbild sichtbar 34%</t>
-        </is>
-      </c>
+      <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45517,11 +45457,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Belag dirt, Länge 67 m, Luftbild sichtbar 19%</t>
-        </is>
-      </c>
+      <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45539,11 +45475,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Belag dirt, Länge 254 m, Luftbild sichtbar 41%</t>
-        </is>
-      </c>
+      <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45561,11 +45493,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Belag grass, Länge 53 m, Luftbild sichtbar 7%</t>
-        </is>
-      </c>
+      <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45583,11 +45511,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Belag unbekannt, Länge 78 m, Luftbild sichtbar 35%</t>
-        </is>
-      </c>
+      <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45605,11 +45529,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Belag grass, Länge 146 m, Luftbild sichtbar 29%</t>
-        </is>
-      </c>
+      <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45627,11 +45547,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Belag dirt, Länge 218 m, Luftbild sichtbar 42%</t>
-        </is>
-      </c>
+      <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45649,11 +45565,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Belag unbekannt, Länge 163 m, Luftbild sichtbar 42%</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45671,11 +45583,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Belag sand, Länge 26 m, Luftbild sichtbar 8%</t>
-        </is>
-      </c>
+      <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45693,11 +45601,7 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Belag grass, Länge 56 m, Luftbild sichtbar 34%</t>
-        </is>
-      </c>
+      <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>

--- a/karte/out/Wangerooge_West_Landmarken_v1.xlsx
+++ b/karte/out/Wangerooge_West_Landmarken_v1.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pfade prüfen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Landmarken'!$A$1:$M$885</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Landmarken'!$A$1:$N$885</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,14 +518,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Version 1.2 vom 11.10.2026 (neue Symbole und Landmarken) · Kartenrahmen UTM32 E 423750–427150, N 5958850–5961650 · Start: Inselheim Rüstringen mit Sternwarte</t>
+          <t>Version 1.5 vom 15.10.2026 · Kartenrahmen UTM32 E 423750–427150, N 5958850–5961650 · Start: Inselheim Rüstringen mit Sternwarte</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Status „sicher“ = mindestens zwei unabhängige Quellen. „prüfen“ = nur eine Quelle; in der Karte grau, auf der Feldcheck-Seite als weißer Marker. IDs sind ab Version 1.1 stabil.</t>
+          <t>Status „sicher“ = mindestens zwei unabhängige Quellen. „prüfen“ = nur eine Quelle; in der Karte normal gezeichnet, in der Feldcheck-App als weißer Marker. IDs sind ab Version 1.1 stabil.</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M885"/>
+  <dimension ref="A1:N885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1234,7 +1234,8 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="64" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1300,6 +1301,11 @@
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
+          <t>Vor Ort (Feldcheck)</t>
+        </is>
+      </c>
+      <c r="N1" s="8" t="inlineStr">
+        <is>
           <t>OSM-ID</t>
         </is>
       </c>
@@ -1349,7 +1355,8 @@
           <t>Weg kreuzt die Inselbahn</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>n538730564</t>
         </is>
@@ -1400,7 +1407,8 @@
           <t>Weg kreuzt die Inselbahn</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>n538730562</t>
         </is>
@@ -1451,7 +1459,8 @@
           <t>Weg kreuzt die Inselbahn</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>n613218684</t>
         </is>
@@ -1502,7 +1511,8 @@
           <t>Weg kreuzt die Inselbahn</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>n325153870</t>
         </is>
@@ -1553,7 +1563,8 @@
           <t>Weg kreuzt die Inselbahn</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>n6401369308</t>
         </is>
@@ -1604,7 +1615,8 @@
           <t>Weg kreuzt die Inselbahn</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>n4624140713</t>
         </is>
@@ -1655,7 +1667,8 @@
           <t>backrest=no</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>n2322972140</t>
         </is>
@@ -1706,7 +1719,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>n2322972139</t>
         </is>
@@ -1757,7 +1771,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>n2322975870</t>
         </is>
@@ -1808,7 +1823,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>n2322975867</t>
         </is>
@@ -1859,7 +1875,8 @@
           <t>backrest=yes, material=wood</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>n2322975869</t>
         </is>
@@ -1910,7 +1927,8 @@
           <t>backrest=no, material=wood</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>n743377534</t>
         </is>
@@ -1961,7 +1979,8 @@
           <t>backrest=no</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>n2322176443</t>
         </is>
@@ -2012,7 +2031,8 @@
           <t>backrest=no</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>n2322176445</t>
         </is>
@@ -2063,7 +2083,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>n2322972135</t>
         </is>
@@ -2114,7 +2135,8 @@
           <t>backrest=no</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>n10816313725</t>
         </is>
@@ -2165,7 +2187,8 @@
           <t>backrest=yes, seats=4</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>n1385089149</t>
         </is>
@@ -2216,7 +2239,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>n1430929580</t>
         </is>
@@ -2267,7 +2291,8 @@
           <t>backrest=yes, check_date=2026-03-04, material=wood, seats=4</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>n1430929590</t>
         </is>
@@ -2318,7 +2343,8 @@
           <t>backrest=yes, material=wood, seats=4</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>n1430929584</t>
         </is>
@@ -2369,7 +2395,8 @@
           <t>backrest=yes, check_date=2026-03-04, material=wood, seats=4</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>n1430929582</t>
         </is>
@@ -2420,7 +2447,8 @@
           <t>backrest=yes, material=wood</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>n1430929588</t>
         </is>
@@ -2471,7 +2499,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>n2319734913</t>
         </is>
@@ -2522,7 +2551,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>n2319734916</t>
         </is>
@@ -2573,7 +2603,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>n9919478756</t>
         </is>
@@ -2624,7 +2655,8 @@
           <t>backrest=yes, material=wood</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>n2322997555</t>
         </is>
@@ -2675,7 +2707,8 @@
           <t>backrest=no</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>n2322176440</t>
         </is>
@@ -2730,7 +2763,8 @@
           <t>backrest=yes, seats=4</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>n12504080887</t>
         </is>
@@ -2785,7 +2819,8 @@
           <t>backrest=yes, seats=4</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr">
         <is>
           <t>n1431891144</t>
         </is>
@@ -2836,7 +2871,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>n1430929569</t>
         </is>
@@ -2887,7 +2923,8 @@
           <t>backrest=yes, material=wood</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t>n1430929571</t>
         </is>
@@ -2938,7 +2975,8 @@
           <t>backrest=no</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>n2322997548</t>
         </is>
@@ -2989,7 +3027,8 @@
           <t>backrest=no</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>n2322997540</t>
         </is>
@@ -3040,7 +3079,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>n2319753490</t>
         </is>
@@ -3091,7 +3131,8 @@
           <t>backrest=yes, material=plastic</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>n2322151573</t>
         </is>
@@ -3138,7 +3179,8 @@
       </c>
       <c r="K37" s="3" t="inlineStr"/>
       <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr">
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr">
         <is>
           <t>n1431891143</t>
         </is>
@@ -3189,7 +3231,8 @@
           <t>backrest=no</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>n743377607</t>
         </is>
@@ -3240,7 +3283,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr">
         <is>
           <t>n3670463635</t>
         </is>
@@ -3295,7 +3339,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr">
         <is>
           <t>n1431891141</t>
         </is>
@@ -3346,7 +3391,8 @@
           <t>backrest=yes, check_date=2023-04-10, seats=4</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr">
         <is>
           <t>n1385089137</t>
         </is>
@@ -3397,7 +3443,8 @@
           <t>backrest=yes, check_date=2023-04-10, seats=4</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr">
         <is>
           <t>n1385089135</t>
         </is>
@@ -3448,7 +3495,8 @@
           <t>backrest=yes, material=wood</t>
         </is>
       </c>
-      <c r="M43" s="3" t="inlineStr">
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr">
         <is>
           <t>n1430929567</t>
         </is>
@@ -3499,7 +3547,8 @@
           <t>backrest=yes, material=wood</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr">
         <is>
           <t>n2323231690</t>
         </is>
@@ -3550,7 +3599,8 @@
           <t>backrest=yes, check_date=2026-07-24, material=wood, seats=4</t>
         </is>
       </c>
-      <c r="M45" s="3" t="inlineStr">
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr">
         <is>
           <t>n6549301866</t>
         </is>
@@ -3601,7 +3651,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr">
         <is>
           <t>n2322032111</t>
         </is>
@@ -3652,7 +3703,8 @@
           <t>backrest=yes, material=wood</t>
         </is>
       </c>
-      <c r="M47" s="3" t="inlineStr">
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr">
         <is>
           <t>n2323592758</t>
         </is>
@@ -3703,7 +3755,8 @@
           <t>backrest=yes, material=wood</t>
         </is>
       </c>
-      <c r="M48" s="3" t="inlineStr">
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr">
         <is>
           <t>n2323592756</t>
         </is>
@@ -3754,7 +3807,8 @@
           <t>backrest=no</t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr">
+      <c r="M49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr">
         <is>
           <t>n2322035378</t>
         </is>
@@ -3809,7 +3863,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>n743377549</t>
         </is>
@@ -3860,7 +3915,8 @@
           <t>backrest=yes</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr">
+      <c r="M51" s="3" t="inlineStr"/>
+      <c r="N51" s="3" t="inlineStr">
         <is>
           <t>n2323592754</t>
         </is>
@@ -3911,7 +3967,8 @@
           <t>backrest=yes, material=wood, seats=4</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
+      <c r="M52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr">
         <is>
           <t>n6549301865</t>
         </is>
@@ -3962,7 +4019,8 @@
           <t>backrest=no, material=wood, seats=5</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="M53" s="3" t="inlineStr"/>
+      <c r="N53" s="3" t="inlineStr">
         <is>
           <t>n14085387067</t>
         </is>
@@ -4013,7 +4071,8 @@
           <t>backrest=no</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr">
         <is>
           <t>n2323592750</t>
         </is>
@@ -4060,7 +4119,8 @@
       </c>
       <c r="K55" s="3" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr"/>
-      <c r="M55" s="3" t="inlineStr">
+      <c r="M55" s="3" t="inlineStr"/>
+      <c r="N55" s="3" t="inlineStr">
         <is>
           <t>n14017915761</t>
         </is>
@@ -4111,7 +4171,8 @@
           <t>material=wood</t>
         </is>
       </c>
-      <c r="M56" s="3" t="inlineStr">
+      <c r="M56" s="3" t="inlineStr"/>
+      <c r="N56" s="3" t="inlineStr">
         <is>
           <t>n14017911216</t>
         </is>
@@ -4162,7 +4223,8 @@
           <t>material=wood</t>
         </is>
       </c>
-      <c r="M57" s="3" t="inlineStr">
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr">
         <is>
           <t>n14017911089</t>
         </is>
@@ -4213,7 +4275,8 @@
           <t>material=wood</t>
         </is>
       </c>
-      <c r="M58" s="3" t="inlineStr">
+      <c r="M58" s="3" t="inlineStr"/>
+      <c r="N58" s="3" t="inlineStr">
         <is>
           <t>n14017903128</t>
         </is>
@@ -4264,7 +4327,8 @@
           <t>material=wood</t>
         </is>
       </c>
-      <c r="M59" s="3" t="inlineStr">
+      <c r="M59" s="3" t="inlineStr"/>
+      <c r="N59" s="3" t="inlineStr">
         <is>
           <t>n14017912830</t>
         </is>
@@ -4315,7 +4379,8 @@
           <t>material=wood</t>
         </is>
       </c>
-      <c r="M60" s="3" t="inlineStr">
+      <c r="M60" s="3" t="inlineStr"/>
+      <c r="N60" s="3" t="inlineStr">
         <is>
           <t>n14017893549</t>
         </is>
@@ -4370,7 +4435,8 @@
           <t>backrest=yes, material=wood, seats=4</t>
         </is>
       </c>
-      <c r="M61" s="3" t="inlineStr">
+      <c r="M61" s="3" t="inlineStr"/>
+      <c r="N61" s="3" t="inlineStr">
         <is>
           <t>n2368694042</t>
         </is>
@@ -4421,7 +4487,8 @@
           <t>backrest=yes, check_date=2021-07-22</t>
         </is>
       </c>
-      <c r="M62" s="3" t="inlineStr">
+      <c r="M62" s="3" t="inlineStr"/>
+      <c r="N62" s="3" t="inlineStr">
         <is>
           <t>n2368694038</t>
         </is>
@@ -4472,7 +4539,8 @@
           <t>backrest=yes, check_date=2021-07-22, material=wood</t>
         </is>
       </c>
-      <c r="M63" s="3" t="inlineStr">
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="3" t="inlineStr">
         <is>
           <t>n8980686839</t>
         </is>
@@ -4523,7 +4591,8 @@
           <t>weather_shelter</t>
         </is>
       </c>
-      <c r="M64" s="3" t="inlineStr">
+      <c r="M64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr">
         <is>
           <t>n2322972136</t>
         </is>
@@ -4570,7 +4639,8 @@
       </c>
       <c r="K65" s="3" t="inlineStr"/>
       <c r="L65" s="3" t="inlineStr"/>
-      <c r="M65" s="3" t="inlineStr">
+      <c r="M65" s="3" t="inlineStr"/>
+      <c r="N65" s="3" t="inlineStr">
         <is>
           <t>n1430929577</t>
         </is>
@@ -4617,7 +4687,8 @@
       </c>
       <c r="K66" s="3" t="inlineStr"/>
       <c r="L66" s="3" t="inlineStr"/>
-      <c r="M66" s="3" t="inlineStr">
+      <c r="M66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr">
         <is>
           <t>n1430929575</t>
         </is>
@@ -4668,7 +4739,8 @@
       </c>
       <c r="K67" s="3" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr"/>
-      <c r="M67" s="3" t="inlineStr">
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="3" t="inlineStr">
         <is>
           <t>w165518794</t>
         </is>
@@ -4723,7 +4795,8 @@
           <t>Lage korrigiert: Kuppel im Luftbild sichtbar, 8,6 m östlich vom OSM-Punkt auf dem Nordflügel des Inselheims</t>
         </is>
       </c>
-      <c r="M68" s="3" t="inlineStr">
+      <c r="M68" s="3" t="inlineStr"/>
+      <c r="N68" s="3" t="inlineStr">
         <is>
           <t>n2322038072</t>
         </is>
@@ -4774,7 +4847,8 @@
           <t>weather_shelter</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr">
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="3" t="inlineStr">
         <is>
           <t>n2011974486</t>
         </is>
@@ -4833,7 +4907,8 @@
           <t>narrow_gauge-Brücke, 11 m</t>
         </is>
       </c>
-      <c r="M70" s="3" t="inlineStr">
+      <c r="M70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="inlineStr">
         <is>
           <t>w112074867</t>
         </is>
@@ -4892,7 +4967,8 @@
           <t>narrow_gauge-Brücke, 15 m</t>
         </is>
       </c>
-      <c r="M71" s="3" t="inlineStr">
+      <c r="M71" s="3" t="inlineStr"/>
+      <c r="N71" s="3" t="inlineStr">
         <is>
           <t>w112074860</t>
         </is>
@@ -4951,7 +5027,8 @@
           <t>narrow_gauge-Brücke, 13 m</t>
         </is>
       </c>
-      <c r="M72" s="3" t="inlineStr">
+      <c r="M72" s="3" t="inlineStr"/>
+      <c r="N72" s="3" t="inlineStr">
         <is>
           <t>w112074865</t>
         </is>
@@ -5006,7 +5083,8 @@
           <t>Rohrdurchlass unter dem Weg</t>
         </is>
       </c>
-      <c r="M73" s="3" t="inlineStr">
+      <c r="M73" s="3" t="inlineStr"/>
+      <c r="N73" s="3" t="inlineStr">
         <is>
           <t>w1363832880</t>
         </is>
@@ -5065,7 +5143,8 @@
           <t>narrow_gauge-Brücke, 7 m</t>
         </is>
       </c>
-      <c r="M74" s="3" t="inlineStr">
+      <c r="M74" s="3" t="inlineStr"/>
+      <c r="N74" s="3" t="inlineStr">
         <is>
           <t>w120151450</t>
         </is>
@@ -5120,7 +5199,8 @@
           <t>Buhne K, Länge 235 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M75" s="3" t="inlineStr">
+      <c r="M75" s="3" t="inlineStr"/>
+      <c r="N75" s="3" t="inlineStr">
         <is>
           <t>w48588645</t>
         </is>
@@ -5175,7 +5255,8 @@
           <t>Buhne C, Länge 153 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M76" s="3" t="inlineStr">
+      <c r="M76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="inlineStr">
         <is>
           <t>w48203008</t>
         </is>
@@ -5230,7 +5311,8 @@
           <t>Buhne D, Länge 176 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M77" s="3" t="inlineStr">
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="3" t="inlineStr">
         <is>
           <t>w48203002</t>
         </is>
@@ -5285,7 +5367,8 @@
           <t>Buhne I, Länge 249 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M78" s="3" t="inlineStr">
+      <c r="M78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="inlineStr">
         <is>
           <t>w48245398</t>
         </is>
@@ -5340,7 +5423,8 @@
           <t>Buhne L, Länge 254 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M79" s="3" t="inlineStr">
+      <c r="M79" s="3" t="inlineStr"/>
+      <c r="N79" s="3" t="inlineStr">
         <is>
           <t>w391922805</t>
         </is>
@@ -5395,7 +5479,8 @@
           <t>Buhne B, Länge 296 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M80" s="3" t="inlineStr">
+      <c r="M80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="inlineStr">
         <is>
           <t>w48203044</t>
         </is>
@@ -5450,7 +5535,8 @@
           <t>Buhne G, Länge 225 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M81" s="3" t="inlineStr">
+      <c r="M81" s="3" t="inlineStr"/>
+      <c r="N81" s="3" t="inlineStr">
         <is>
           <t>w48203007</t>
         </is>
@@ -5505,7 +5591,8 @@
           <t>Buhne F, Länge 180 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M82" s="3" t="inlineStr">
+      <c r="M82" s="3" t="inlineStr"/>
+      <c r="N82" s="3" t="inlineStr">
         <is>
           <t>w48203004</t>
         </is>
@@ -5560,7 +5647,8 @@
           <t>Buhne B, Länge 65 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M83" s="3" t="inlineStr">
+      <c r="M83" s="3" t="inlineStr"/>
+      <c r="N83" s="3" t="inlineStr">
         <is>
           <t>w48203006</t>
         </is>
@@ -5615,7 +5703,8 @@
           <t>Buhne E, Länge 278 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M84" s="3" t="inlineStr">
+      <c r="M84" s="3" t="inlineStr"/>
+      <c r="N84" s="3" t="inlineStr">
         <is>
           <t>w48202995</t>
         </is>
@@ -5670,7 +5759,8 @@
           <t>Buhne H, Länge 1375 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M85" s="3" t="inlineStr">
+      <c r="M85" s="3" t="inlineStr"/>
+      <c r="N85" s="3" t="inlineStr">
         <is>
           <t>w48202998</t>
         </is>
@@ -5725,7 +5815,8 @@
           <t>Buhne U, Länge 255 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M86" s="3" t="inlineStr">
+      <c r="M86" s="3" t="inlineStr"/>
+      <c r="N86" s="3" t="inlineStr">
         <is>
           <t>w48202999</t>
         </is>
@@ -5780,7 +5871,8 @@
           <t>Buhne V, Länge 284 m; Punkt = landseitiges Ende</t>
         </is>
       </c>
-      <c r="M87" s="3" t="inlineStr">
+      <c r="M87" s="3" t="inlineStr"/>
+      <c r="N87" s="3" t="inlineStr">
         <is>
           <t>w48203000</t>
         </is>
@@ -5827,7 +5919,8 @@
       </c>
       <c r="K88" s="3" t="inlineStr"/>
       <c r="L88" s="3" t="inlineStr"/>
-      <c r="M88" s="3" t="inlineStr">
+      <c r="M88" s="3" t="inlineStr"/>
+      <c r="N88" s="3" t="inlineStr">
         <is>
           <t>n12134557254</t>
         </is>
@@ -5874,7 +5967,8 @@
       </c>
       <c r="K89" s="3" t="inlineStr"/>
       <c r="L89" s="3" t="inlineStr"/>
-      <c r="M89" s="3" t="inlineStr">
+      <c r="M89" s="3" t="inlineStr"/>
+      <c r="N89" s="3" t="inlineStr">
         <is>
           <t>n13831102167</t>
         </is>
@@ -5921,7 +6015,8 @@
       </c>
       <c r="K90" s="3" t="inlineStr"/>
       <c r="L90" s="3" t="inlineStr"/>
-      <c r="M90" s="3" t="inlineStr">
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="3" t="inlineStr">
         <is>
           <t>n531034570</t>
         </is>
@@ -5968,7 +6063,8 @@
       </c>
       <c r="K91" s="3" t="inlineStr"/>
       <c r="L91" s="3" t="inlineStr"/>
-      <c r="M91" s="3" t="inlineStr">
+      <c r="M91" s="3" t="inlineStr"/>
+      <c r="N91" s="3" t="inlineStr">
         <is>
           <t>n5237377557</t>
         </is>
@@ -6015,7 +6111,8 @@
       </c>
       <c r="K92" s="3" t="inlineStr"/>
       <c r="L92" s="3" t="inlineStr"/>
-      <c r="M92" s="3" t="inlineStr">
+      <c r="M92" s="3" t="inlineStr"/>
+      <c r="N92" s="3" t="inlineStr">
         <is>
           <t>n12269593015</t>
         </is>
@@ -6062,7 +6159,8 @@
       </c>
       <c r="K93" s="3" t="inlineStr"/>
       <c r="L93" s="3" t="inlineStr"/>
-      <c r="M93" s="3" t="inlineStr">
+      <c r="M93" s="3" t="inlineStr"/>
+      <c r="N93" s="3" t="inlineStr">
         <is>
           <t>n552395097</t>
         </is>
@@ -6109,7 +6207,8 @@
       </c>
       <c r="K94" s="3" t="inlineStr"/>
       <c r="L94" s="3" t="inlineStr"/>
-      <c r="M94" s="3" t="inlineStr">
+      <c r="M94" s="3" t="inlineStr"/>
+      <c r="N94" s="3" t="inlineStr">
         <is>
           <t>n12133117625</t>
         </is>
@@ -6156,7 +6255,8 @@
       </c>
       <c r="K95" s="3" t="inlineStr"/>
       <c r="L95" s="3" t="inlineStr"/>
-      <c r="M95" s="3" t="inlineStr">
+      <c r="M95" s="3" t="inlineStr"/>
+      <c r="N95" s="3" t="inlineStr">
         <is>
           <t>n613194183</t>
         </is>
@@ -6203,7 +6303,8 @@
       </c>
       <c r="K96" s="3" t="inlineStr"/>
       <c r="L96" s="3" t="inlineStr"/>
-      <c r="M96" s="3" t="inlineStr">
+      <c r="M96" s="3" t="inlineStr"/>
+      <c r="N96" s="3" t="inlineStr">
         <is>
           <t>n9943371115</t>
         </is>
@@ -6250,7 +6351,8 @@
       </c>
       <c r="K97" s="3" t="inlineStr"/>
       <c r="L97" s="3" t="inlineStr"/>
-      <c r="M97" s="3" t="inlineStr">
+      <c r="M97" s="3" t="inlineStr"/>
+      <c r="N97" s="3" t="inlineStr">
         <is>
           <t>n9943371114</t>
         </is>
@@ -6297,7 +6399,8 @@
       </c>
       <c r="K98" s="3" t="inlineStr"/>
       <c r="L98" s="3" t="inlineStr"/>
-      <c r="M98" s="3" t="inlineStr">
+      <c r="M98" s="3" t="inlineStr"/>
+      <c r="N98" s="3" t="inlineStr">
         <is>
           <t>n2322047757</t>
         </is>
@@ -6344,7 +6447,8 @@
       </c>
       <c r="K99" s="3" t="inlineStr"/>
       <c r="L99" s="3" t="inlineStr"/>
-      <c r="M99" s="3" t="inlineStr">
+      <c r="M99" s="3" t="inlineStr"/>
+      <c r="N99" s="3" t="inlineStr">
         <is>
           <t>n12269593025</t>
         </is>
@@ -6391,7 +6495,8 @@
       </c>
       <c r="K100" s="3" t="inlineStr"/>
       <c r="L100" s="3" t="inlineStr"/>
-      <c r="M100" s="3" t="inlineStr">
+      <c r="M100" s="3" t="inlineStr"/>
+      <c r="N100" s="3" t="inlineStr">
         <is>
           <t>n9182584489</t>
         </is>
@@ -6438,7 +6543,8 @@
       </c>
       <c r="K101" s="3" t="inlineStr"/>
       <c r="L101" s="3" t="inlineStr"/>
-      <c r="M101" s="3" t="inlineStr">
+      <c r="M101" s="3" t="inlineStr"/>
+      <c r="N101" s="3" t="inlineStr">
         <is>
           <t>n612586574</t>
         </is>
@@ -6485,7 +6591,8 @@
       </c>
       <c r="K102" s="3" t="inlineStr"/>
       <c r="L102" s="3" t="inlineStr"/>
-      <c r="M102" s="3" t="inlineStr">
+      <c r="M102" s="3" t="inlineStr"/>
+      <c r="N102" s="3" t="inlineStr">
         <is>
           <t>n13897677636</t>
         </is>
@@ -6532,7 +6639,8 @@
       </c>
       <c r="K103" s="3" t="inlineStr"/>
       <c r="L103" s="3" t="inlineStr"/>
-      <c r="M103" s="3" t="inlineStr">
+      <c r="M103" s="3" t="inlineStr"/>
+      <c r="N103" s="3" t="inlineStr">
         <is>
           <t>n13897637598</t>
         </is>
@@ -6579,7 +6687,8 @@
       </c>
       <c r="K104" s="3" t="inlineStr"/>
       <c r="L104" s="3" t="inlineStr"/>
-      <c r="M104" s="3" t="inlineStr">
+      <c r="M104" s="3" t="inlineStr"/>
+      <c r="N104" s="3" t="inlineStr">
         <is>
           <t>n13897711657</t>
         </is>
@@ -6630,7 +6739,8 @@
           <t>Länge 55 m, wood</t>
         </is>
       </c>
-      <c r="M105" s="3" t="inlineStr">
+      <c r="M105" s="3" t="inlineStr"/>
+      <c r="N105" s="3" t="inlineStr">
         <is>
           <t>w995236394</t>
         </is>
@@ -6681,7 +6791,8 @@
           <t>Länge 42 m, wood</t>
         </is>
       </c>
-      <c r="M106" s="3" t="inlineStr">
+      <c r="M106" s="3" t="inlineStr"/>
+      <c r="N106" s="3" t="inlineStr">
         <is>
           <t>w1270795370</t>
         </is>
@@ -6732,7 +6843,8 @@
           <t>Länge 12 m, concrete</t>
         </is>
       </c>
-      <c r="M107" s="3" t="inlineStr">
+      <c r="M107" s="3" t="inlineStr"/>
+      <c r="N107" s="3" t="inlineStr">
         <is>
           <t>w223399412</t>
         </is>
@@ -6783,7 +6895,8 @@
           <t>Länge 2 m, unhewn_cobblestone</t>
         </is>
       </c>
-      <c r="M108" s="3" t="inlineStr">
+      <c r="M108" s="3" t="inlineStr"/>
+      <c r="N108" s="3" t="inlineStr">
         <is>
           <t>w1514018344</t>
         </is>
@@ -6834,7 +6947,8 @@
           <t xml:space="preserve">Länge 3 m, </t>
         </is>
       </c>
-      <c r="M109" s="3" t="inlineStr">
+      <c r="M109" s="3" t="inlineStr"/>
+      <c r="N109" s="3" t="inlineStr">
         <is>
           <t>w1310761590</t>
         </is>
@@ -6889,7 +7003,8 @@
           <t>Länge 6 m, concrete</t>
         </is>
       </c>
-      <c r="M110" s="3" t="inlineStr">
+      <c r="M110" s="3" t="inlineStr"/>
+      <c r="N110" s="3" t="inlineStr">
         <is>
           <t>w42478892</t>
         </is>
@@ -6940,7 +7055,8 @@
           <t>Länge 22 m, concrete</t>
         </is>
       </c>
-      <c r="M111" s="3" t="inlineStr">
+      <c r="M111" s="3" t="inlineStr"/>
+      <c r="N111" s="3" t="inlineStr">
         <is>
           <t>w43548566</t>
         </is>
@@ -6995,7 +7111,8 @@
           <t>Länge 6 m, concrete</t>
         </is>
       </c>
-      <c r="M112" s="3" t="inlineStr">
+      <c r="M112" s="3" t="inlineStr"/>
+      <c r="N112" s="3" t="inlineStr">
         <is>
           <t>w1248237258</t>
         </is>
@@ -7050,7 +7167,8 @@
           <t>Länge 6 m, concrete</t>
         </is>
       </c>
-      <c r="M113" s="3" t="inlineStr">
+      <c r="M113" s="3" t="inlineStr"/>
+      <c r="N113" s="3" t="inlineStr">
         <is>
           <t>w1248237259</t>
         </is>
@@ -7105,7 +7223,8 @@
           <t>Länge 7 m, concrete</t>
         </is>
       </c>
-      <c r="M114" s="3" t="inlineStr">
+      <c r="M114" s="3" t="inlineStr"/>
+      <c r="N114" s="3" t="inlineStr">
         <is>
           <t>w1248237260</t>
         </is>
@@ -7156,7 +7275,8 @@
           <t>Länge 5 m, metal</t>
         </is>
       </c>
-      <c r="M115" s="3" t="inlineStr">
+      <c r="M115" s="3" t="inlineStr"/>
+      <c r="N115" s="3" t="inlineStr">
         <is>
           <t>w1188477290</t>
         </is>
@@ -7207,7 +7327,8 @@
           <t>Länge 6 m, wood</t>
         </is>
       </c>
-      <c r="M116" s="3" t="inlineStr">
+      <c r="M116" s="3" t="inlineStr"/>
+      <c r="N116" s="3" t="inlineStr">
         <is>
           <t>w993926336</t>
         </is>
@@ -7258,7 +7379,8 @@
           <t>Länge 5 m, wood</t>
         </is>
       </c>
-      <c r="M117" s="3" t="inlineStr">
+      <c r="M117" s="3" t="inlineStr"/>
+      <c r="N117" s="3" t="inlineStr">
         <is>
           <t>w1363812311</t>
         </is>
@@ -7309,7 +7431,8 @@
           <t>Länge 8 m, wood</t>
         </is>
       </c>
-      <c r="M118" s="3" t="inlineStr">
+      <c r="M118" s="3" t="inlineStr"/>
+      <c r="N118" s="3" t="inlineStr">
         <is>
           <t>w993926340</t>
         </is>
@@ -7356,7 +7479,8 @@
       </c>
       <c r="K119" s="3" t="inlineStr"/>
       <c r="L119" s="3" t="inlineStr"/>
-      <c r="M119" s="3" t="inlineStr">
+      <c r="M119" s="3" t="inlineStr"/>
+      <c r="N119" s="3" t="inlineStr">
         <is>
           <t>n14002871301</t>
         </is>
@@ -7403,7 +7527,8 @@
       </c>
       <c r="K120" s="3" t="inlineStr"/>
       <c r="L120" s="3" t="inlineStr"/>
-      <c r="M120" s="3" t="inlineStr">
+      <c r="M120" s="3" t="inlineStr"/>
+      <c r="N120" s="3" t="inlineStr">
         <is>
           <t>n10816290631</t>
         </is>
@@ -7454,7 +7579,8 @@
       </c>
       <c r="K121" s="3" t="inlineStr"/>
       <c r="L121" s="3" t="inlineStr"/>
-      <c r="M121" s="3" t="inlineStr">
+      <c r="M121" s="3" t="inlineStr"/>
+      <c r="N121" s="3" t="inlineStr">
         <is>
           <t>n3134841232</t>
         </is>
@@ -7501,7 +7627,8 @@
       </c>
       <c r="K122" s="3" t="inlineStr"/>
       <c r="L122" s="3" t="inlineStr"/>
-      <c r="M122" s="3" t="inlineStr">
+      <c r="M122" s="3" t="inlineStr"/>
+      <c r="N122" s="3" t="inlineStr">
         <is>
           <t>n743377610</t>
         </is>
@@ -7548,7 +7675,8 @@
       </c>
       <c r="K123" s="3" t="inlineStr"/>
       <c r="L123" s="3" t="inlineStr"/>
-      <c r="M123" s="3" t="inlineStr">
+      <c r="M123" s="3" t="inlineStr"/>
+      <c r="N123" s="3" t="inlineStr">
         <is>
           <t>n3160000887</t>
         </is>
@@ -7595,7 +7723,8 @@
       </c>
       <c r="K124" s="3" t="inlineStr"/>
       <c r="L124" s="3" t="inlineStr"/>
-      <c r="M124" s="3" t="inlineStr">
+      <c r="M124" s="3" t="inlineStr"/>
+      <c r="N124" s="3" t="inlineStr">
         <is>
           <t>n9182584490</t>
         </is>
@@ -7646,7 +7775,8 @@
       </c>
       <c r="K125" s="3" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr"/>
-      <c r="M125" s="3" t="inlineStr">
+      <c r="M125" s="3" t="inlineStr"/>
+      <c r="N125" s="3" t="inlineStr">
         <is>
           <t>n4271324911</t>
         </is>
@@ -7693,7 +7823,8 @@
       </c>
       <c r="K126" s="3" t="inlineStr"/>
       <c r="L126" s="3" t="inlineStr"/>
-      <c r="M126" s="3" t="inlineStr">
+      <c r="M126" s="3" t="inlineStr"/>
+      <c r="N126" s="3" t="inlineStr">
         <is>
           <t>n9182584488</t>
         </is>
@@ -7740,7 +7871,8 @@
       </c>
       <c r="K127" s="3" t="inlineStr"/>
       <c r="L127" s="3" t="inlineStr"/>
-      <c r="M127" s="3" t="inlineStr">
+      <c r="M127" s="3" t="inlineStr"/>
+      <c r="N127" s="3" t="inlineStr">
         <is>
           <t>n13987866751</t>
         </is>
@@ -7787,7 +7919,8 @@
       </c>
       <c r="K128" s="3" t="inlineStr"/>
       <c r="L128" s="3" t="inlineStr"/>
-      <c r="M128" s="3" t="inlineStr">
+      <c r="M128" s="3" t="inlineStr"/>
+      <c r="N128" s="3" t="inlineStr">
         <is>
           <t>n13987880793</t>
         </is>
@@ -7838,7 +7971,8 @@
       </c>
       <c r="K129" s="3" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr"/>
-      <c r="M129" s="3" t="inlineStr">
+      <c r="M129" s="3" t="inlineStr"/>
+      <c r="N129" s="3" t="inlineStr">
         <is>
           <t>n1274835526</t>
         </is>
@@ -7885,7 +8019,8 @@
       </c>
       <c r="K130" s="3" t="inlineStr"/>
       <c r="L130" s="3" t="inlineStr"/>
-      <c r="M130" s="3" t="inlineStr">
+      <c r="M130" s="3" t="inlineStr"/>
+      <c r="N130" s="3" t="inlineStr">
         <is>
           <t>n14023812711</t>
         </is>
@@ -7936,7 +8071,8 @@
           <t>14</t>
         </is>
       </c>
-      <c r="M131" s="3" t="inlineStr">
+      <c r="M131" s="3" t="inlineStr"/>
+      <c r="N131" s="3" t="inlineStr">
         <is>
           <t>n10816310306</t>
         </is>
@@ -7983,7 +8119,8 @@
       </c>
       <c r="K132" s="3" t="inlineStr"/>
       <c r="L132" s="3" t="inlineStr"/>
-      <c r="M132" s="3" t="inlineStr">
+      <c r="M132" s="3" t="inlineStr"/>
+      <c r="N132" s="3" t="inlineStr">
         <is>
           <t>n14017311149</t>
         </is>
@@ -8030,7 +8167,8 @@
       </c>
       <c r="K133" s="3" t="inlineStr"/>
       <c r="L133" s="3" t="inlineStr"/>
-      <c r="M133" s="3" t="inlineStr">
+      <c r="M133" s="3" t="inlineStr"/>
+      <c r="N133" s="3" t="inlineStr">
         <is>
           <t>n12110663647</t>
         </is>
@@ -8081,7 +8219,8 @@
       </c>
       <c r="K134" s="3" t="inlineStr"/>
       <c r="L134" s="3" t="inlineStr"/>
-      <c r="M134" s="3" t="inlineStr">
+      <c r="M134" s="3" t="inlineStr"/>
+      <c r="N134" s="3" t="inlineStr">
         <is>
           <t>n3134811151</t>
         </is>
@@ -8132,7 +8271,8 @@
       </c>
       <c r="K135" s="3" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr"/>
-      <c r="M135" s="3" t="inlineStr">
+      <c r="M135" s="3" t="inlineStr"/>
+      <c r="N135" s="3" t="inlineStr">
         <is>
           <t>n1385089103</t>
         </is>
@@ -8183,7 +8323,8 @@
       </c>
       <c r="K136" s="3" t="inlineStr"/>
       <c r="L136" s="3" t="inlineStr"/>
-      <c r="M136" s="3" t="inlineStr">
+      <c r="M136" s="3" t="inlineStr"/>
+      <c r="N136" s="3" t="inlineStr">
         <is>
           <t>n1430301782</t>
         </is>
@@ -8234,7 +8375,8 @@
       </c>
       <c r="K137" s="3" t="inlineStr"/>
       <c r="L137" s="3" t="inlineStr"/>
-      <c r="M137" s="3" t="inlineStr">
+      <c r="M137" s="3" t="inlineStr"/>
+      <c r="N137" s="3" t="inlineStr">
         <is>
           <t>n10816281230</t>
         </is>
@@ -8285,7 +8427,8 @@
       </c>
       <c r="K138" s="3" t="inlineStr"/>
       <c r="L138" s="3" t="inlineStr"/>
-      <c r="M138" s="3" t="inlineStr">
+      <c r="M138" s="3" t="inlineStr"/>
+      <c r="N138" s="3" t="inlineStr">
         <is>
           <t>n11795321556</t>
         </is>
@@ -8336,7 +8479,8 @@
       </c>
       <c r="K139" s="3" t="inlineStr"/>
       <c r="L139" s="3" t="inlineStr"/>
-      <c r="M139" s="3" t="inlineStr">
+      <c r="M139" s="3" t="inlineStr"/>
+      <c r="N139" s="3" t="inlineStr">
         <is>
           <t>w42701588</t>
         </is>
@@ -8387,7 +8531,8 @@
       </c>
       <c r="K140" s="3" t="inlineStr"/>
       <c r="L140" s="3" t="inlineStr"/>
-      <c r="M140" s="3" t="inlineStr">
+      <c r="M140" s="3" t="inlineStr"/>
+      <c r="N140" s="3" t="inlineStr">
         <is>
           <t>w233273068</t>
         </is>
@@ -8438,7 +8583,8 @@
       </c>
       <c r="K141" s="3" t="inlineStr"/>
       <c r="L141" s="3" t="inlineStr"/>
-      <c r="M141" s="3" t="inlineStr">
+      <c r="M141" s="3" t="inlineStr"/>
+      <c r="N141" s="3" t="inlineStr">
         <is>
           <t>w222569725</t>
         </is>
@@ -8489,7 +8635,8 @@
       </c>
       <c r="K142" s="3" t="inlineStr"/>
       <c r="L142" s="3" t="inlineStr"/>
-      <c r="M142" s="3" t="inlineStr">
+      <c r="M142" s="3" t="inlineStr"/>
+      <c r="N142" s="3" t="inlineStr">
         <is>
           <t>w139834004</t>
         </is>
@@ -8540,7 +8687,8 @@
       </c>
       <c r="K143" s="3" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr"/>
-      <c r="M143" s="3" t="inlineStr">
+      <c r="M143" s="3" t="inlineStr"/>
+      <c r="N143" s="3" t="inlineStr">
         <is>
           <t>w48648272</t>
         </is>
@@ -8591,7 +8739,8 @@
       </c>
       <c r="K144" s="3" t="inlineStr"/>
       <c r="L144" s="3" t="inlineStr"/>
-      <c r="M144" s="3" t="inlineStr">
+      <c r="M144" s="3" t="inlineStr"/>
+      <c r="N144" s="3" t="inlineStr">
         <is>
           <t>w48648244</t>
         </is>
@@ -8642,7 +8791,8 @@
       </c>
       <c r="K145" s="3" t="inlineStr"/>
       <c r="L145" s="3" t="inlineStr"/>
-      <c r="M145" s="3" t="inlineStr">
+      <c r="M145" s="3" t="inlineStr"/>
+      <c r="N145" s="3" t="inlineStr">
         <is>
           <t>w185158359</t>
         </is>
@@ -8693,7 +8843,8 @@
       </c>
       <c r="K146" s="3" t="inlineStr"/>
       <c r="L146" s="3" t="inlineStr"/>
-      <c r="M146" s="3" t="inlineStr">
+      <c r="M146" s="3" t="inlineStr"/>
+      <c r="N146" s="3" t="inlineStr">
         <is>
           <t>w139548471</t>
         </is>
@@ -8744,7 +8895,8 @@
       </c>
       <c r="K147" s="3" t="inlineStr"/>
       <c r="L147" s="3" t="inlineStr"/>
-      <c r="M147" s="3" t="inlineStr">
+      <c r="M147" s="3" t="inlineStr"/>
+      <c r="N147" s="3" t="inlineStr">
         <is>
           <t>w899567472</t>
         </is>
@@ -8799,7 +8951,8 @@
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
-      <c r="M148" s="3" t="inlineStr">
+      <c r="M148" s="3" t="inlineStr"/>
+      <c r="N148" s="3" t="inlineStr">
         <is>
           <t>w1324232941</t>
         </is>
@@ -8850,7 +9003,8 @@
       </c>
       <c r="K149" s="3" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr"/>
-      <c r="M149" s="3" t="inlineStr">
+      <c r="M149" s="3" t="inlineStr"/>
+      <c r="N149" s="3" t="inlineStr">
         <is>
           <t>w59869587</t>
         </is>
@@ -8901,7 +9055,8 @@
       </c>
       <c r="K150" s="3" t="inlineStr"/>
       <c r="L150" s="3" t="inlineStr"/>
-      <c r="M150" s="3" t="inlineStr">
+      <c r="M150" s="3" t="inlineStr"/>
+      <c r="N150" s="3" t="inlineStr">
         <is>
           <t>w48255690</t>
         </is>
@@ -8952,7 +9107,8 @@
       </c>
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
-      <c r="M151" s="3" t="inlineStr">
+      <c r="M151" s="3" t="inlineStr"/>
+      <c r="N151" s="3" t="inlineStr">
         <is>
           <t>w48254484</t>
         </is>
@@ -9007,7 +9163,8 @@
           <t>ele=17</t>
         </is>
       </c>
-      <c r="M152" s="3" t="inlineStr">
+      <c r="M152" s="3" t="inlineStr"/>
+      <c r="N152" s="3" t="inlineStr">
         <is>
           <t>n529702340</t>
         </is>
@@ -9058,7 +9215,8 @@
           <t>Fläche 31 m², Ø≈6 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M153" s="3" t="inlineStr">
+      <c r="M153" s="3" t="inlineStr"/>
+      <c r="N153" s="3" t="inlineStr">
         <is>
           <t>w1548444172</t>
         </is>
@@ -9109,7 +9267,8 @@
           <t>Fläche 116 m², Ø≈12 m, Rundheit 0.80. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M154" s="3" t="inlineStr">
+      <c r="M154" s="3" t="inlineStr"/>
+      <c r="N154" s="3" t="inlineStr">
         <is>
           <t>w377900236</t>
         </is>
@@ -9160,7 +9319,8 @@
           <t>Fläche 426 m², Ø≈23 m, Rundheit 0.78. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M155" s="3" t="inlineStr">
+      <c r="M155" s="3" t="inlineStr"/>
+      <c r="N155" s="3" t="inlineStr">
         <is>
           <t>w48648271</t>
         </is>
@@ -9215,7 +9375,8 @@
           <t>Fläche 31 m², Ø≈6 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M156" s="3" t="inlineStr">
+      <c r="M156" s="3" t="inlineStr"/>
+      <c r="N156" s="3" t="inlineStr">
         <is>
           <t>w1548444181</t>
         </is>
@@ -9270,7 +9431,8 @@
           <t>Fläche 31 m², Ø≈6 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M157" s="3" t="inlineStr">
+      <c r="M157" s="3" t="inlineStr"/>
+      <c r="N157" s="3" t="inlineStr">
         <is>
           <t>w1548444180</t>
         </is>
@@ -9325,7 +9487,8 @@
           <t xml:space="preserve">Fläche 129 m², Ø≈13 m, Rundheit 0.58. </t>
         </is>
       </c>
-      <c r="M158" s="3" t="inlineStr">
+      <c r="M158" s="3" t="inlineStr"/>
+      <c r="N158" s="3" t="inlineStr">
         <is>
           <t>w1548444174</t>
         </is>
@@ -9380,7 +9543,8 @@
           <t>Fläche 111 m², Ø≈12 m, Rundheit 0.87. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M159" s="3" t="inlineStr">
+      <c r="M159" s="3" t="inlineStr"/>
+      <c r="N159" s="3" t="inlineStr">
         <is>
           <t>w1548444184</t>
         </is>
@@ -9435,7 +9599,8 @@
           <t xml:space="preserve">Fläche 178 m², Ø≈15 m, Rundheit 0.68. </t>
         </is>
       </c>
-      <c r="M160" s="3" t="inlineStr">
+      <c r="M160" s="3" t="inlineStr"/>
+      <c r="N160" s="3" t="inlineStr">
         <is>
           <t>w1548444173</t>
         </is>
@@ -9490,7 +9655,8 @@
           <t>Fläche 156 m², Ø≈14 m, Rundheit 0.97. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M161" s="3" t="inlineStr">
+      <c r="M161" s="3" t="inlineStr"/>
+      <c r="N161" s="3" t="inlineStr">
         <is>
           <t>w1548444186</t>
         </is>
@@ -9545,7 +9711,8 @@
           <t>Fläche 95 m², Ø≈11 m, Rundheit 0.96. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M162" s="3" t="inlineStr">
+      <c r="M162" s="3" t="inlineStr"/>
+      <c r="N162" s="3" t="inlineStr">
         <is>
           <t>w1548444182</t>
         </is>
@@ -9600,7 +9767,8 @@
           <t>Fläche 156 m², Ø≈14 m, Rundheit 0.97. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M163" s="3" t="inlineStr">
+      <c r="M163" s="3" t="inlineStr"/>
+      <c r="N163" s="3" t="inlineStr">
         <is>
           <t>w1548444187</t>
         </is>
@@ -9655,7 +9823,8 @@
           <t>Fläche 156 m², Ø≈14 m, Rundheit 0.97. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M164" s="3" t="inlineStr">
+      <c r="M164" s="3" t="inlineStr"/>
+      <c r="N164" s="3" t="inlineStr">
         <is>
           <t>w277994337</t>
         </is>
@@ -9706,7 +9875,8 @@
           <t>Fläche 31 m², Ø≈6 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M165" s="3" t="inlineStr">
+      <c r="M165" s="3" t="inlineStr"/>
+      <c r="N165" s="3" t="inlineStr">
         <is>
           <t>w1548444177</t>
         </is>
@@ -9761,7 +9931,8 @@
           <t>Fläche 70 m², Ø≈9 m, Rundheit 0.93. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M166" s="3" t="inlineStr">
+      <c r="M166" s="3" t="inlineStr"/>
+      <c r="N166" s="3" t="inlineStr">
         <is>
           <t>w1324232939</t>
         </is>
@@ -9816,7 +9987,8 @@
           <t>Fläche 108 m², Ø≈12 m, Rundheit 0.96. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M167" s="3" t="inlineStr">
+      <c r="M167" s="3" t="inlineStr"/>
+      <c r="N167" s="3" t="inlineStr">
         <is>
           <t>w136072920</t>
         </is>
@@ -9871,7 +10043,8 @@
           <t>Fläche 177 m², Ø≈15 m, Rundheit 0.76. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M168" s="3" t="inlineStr">
+      <c r="M168" s="3" t="inlineStr"/>
+      <c r="N168" s="3" t="inlineStr">
         <is>
           <t>w136072914</t>
         </is>
@@ -9926,7 +10099,8 @@
           <t>Fläche 70 m², Ø≈9 m, Rundheit 0.93. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M169" s="3" t="inlineStr">
+      <c r="M169" s="3" t="inlineStr"/>
+      <c r="N169" s="3" t="inlineStr">
         <is>
           <t>w136072917</t>
         </is>
@@ -9981,7 +10155,8 @@
           <t>Fläche 59 m², Ø≈9 m, Rundheit 0.82. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M170" s="3" t="inlineStr">
+      <c r="M170" s="3" t="inlineStr"/>
+      <c r="N170" s="3" t="inlineStr">
         <is>
           <t>w136072913</t>
         </is>
@@ -10036,7 +10211,8 @@
           <t>Fläche 396 m², Ø≈22 m, Rundheit 0.33.  | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M171" s="3" t="inlineStr">
+      <c r="M171" s="3" t="inlineStr"/>
+      <c r="N171" s="3" t="inlineStr">
         <is>
           <t>w136072916</t>
         </is>
@@ -10091,7 +10267,8 @@
           <t xml:space="preserve">Fläche 229 m², Ø≈17 m, Rundheit 0.65. </t>
         </is>
       </c>
-      <c r="M172" s="3" t="inlineStr">
+      <c r="M172" s="3" t="inlineStr"/>
+      <c r="N172" s="3" t="inlineStr">
         <is>
           <t>w136072915</t>
         </is>
@@ -10146,7 +10323,8 @@
           <t>Fläche 19 m², Ø≈5 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M173" s="3" t="inlineStr">
+      <c r="M173" s="3" t="inlineStr"/>
+      <c r="N173" s="3" t="inlineStr">
         <is>
           <t>w1548447422</t>
         </is>
@@ -10197,7 +10375,8 @@
           <t>Fläche 148 m², Ø≈14 m, Rundheit 0.83. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M174" s="3" t="inlineStr">
+      <c r="M174" s="3" t="inlineStr"/>
+      <c r="N174" s="3" t="inlineStr">
         <is>
           <t>w377900235</t>
         </is>
@@ -10248,7 +10427,8 @@
           <t>Fläche 76 m², Ø≈10 m, Rundheit 0.93. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M175" s="3" t="inlineStr">
+      <c r="M175" s="3" t="inlineStr"/>
+      <c r="N175" s="3" t="inlineStr">
         <is>
           <t>w377900231</t>
         </is>
@@ -10303,7 +10483,8 @@
           <t>Fläche 562 m², Ø≈27 m, Rundheit 0.70.  | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M176" s="3" t="inlineStr">
+      <c r="M176" s="3" t="inlineStr"/>
+      <c r="N176" s="3" t="inlineStr">
         <is>
           <t>w137468180</t>
         </is>
@@ -10358,7 +10539,8 @@
           <t>Fläche 45 m², Ø≈8 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M177" s="3" t="inlineStr">
+      <c r="M177" s="3" t="inlineStr"/>
+      <c r="N177" s="3" t="inlineStr">
         <is>
           <t>w1548444176</t>
         </is>
@@ -10413,7 +10595,8 @@
           <t>Fläche 179 m², Ø≈15 m, Rundheit 0.86. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M178" s="3" t="inlineStr">
+      <c r="M178" s="3" t="inlineStr"/>
+      <c r="N178" s="3" t="inlineStr">
         <is>
           <t>w1248237261</t>
         </is>
@@ -10468,7 +10651,8 @@
           <t>Fläche 31 m², Ø≈6 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M179" s="3" t="inlineStr">
+      <c r="M179" s="3" t="inlineStr"/>
+      <c r="N179" s="3" t="inlineStr">
         <is>
           <t>w1548444179</t>
         </is>
@@ -10523,7 +10707,8 @@
           <t>Fläche 58 m², Ø≈9 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M180" s="3" t="inlineStr">
+      <c r="M180" s="3" t="inlineStr"/>
+      <c r="N180" s="3" t="inlineStr">
         <is>
           <t>w1548444175</t>
         </is>
@@ -10578,7 +10763,8 @@
           <t>Fläche 58 m², Ø≈9 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M181" s="3" t="inlineStr">
+      <c r="M181" s="3" t="inlineStr"/>
+      <c r="N181" s="3" t="inlineStr">
         <is>
           <t>w1548444178</t>
         </is>
@@ -10633,7 +10819,8 @@
           <t>Fläche 19 m², Ø≈5 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M182" s="3" t="inlineStr">
+      <c r="M182" s="3" t="inlineStr"/>
+      <c r="N182" s="3" t="inlineStr">
         <is>
           <t>w1548447423</t>
         </is>
@@ -10684,7 +10871,8 @@
           <t xml:space="preserve">Fläche 132 m², Ø≈13 m, Rundheit 0.49. </t>
         </is>
       </c>
-      <c r="M183" s="3" t="inlineStr">
+      <c r="M183" s="3" t="inlineStr"/>
+      <c r="N183" s="3" t="inlineStr">
         <is>
           <t>w1548447418</t>
         </is>
@@ -10735,7 +10923,8 @@
           <t>Fläche 59 m², Ø≈9 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M184" s="3" t="inlineStr">
+      <c r="M184" s="3" t="inlineStr"/>
+      <c r="N184" s="3" t="inlineStr">
         <is>
           <t>w1548447419</t>
         </is>
@@ -10786,7 +10975,8 @@
           <t>Fläche 58 m², Ø≈9 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M185" s="3" t="inlineStr">
+      <c r="M185" s="3" t="inlineStr"/>
+      <c r="N185" s="3" t="inlineStr">
         <is>
           <t>w1548447420</t>
         </is>
@@ -10837,7 +11027,8 @@
           <t>Fläche 163 m², Ø≈14 m, Rundheit 0.96. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M186" s="3" t="inlineStr">
+      <c r="M186" s="3" t="inlineStr"/>
+      <c r="N186" s="3" t="inlineStr">
         <is>
           <t>w1548447421</t>
         </is>
@@ -10888,7 +11079,8 @@
           <t xml:space="preserve">Fläche 762 m², Ø≈31 m, Rundheit 0.28. </t>
         </is>
       </c>
-      <c r="M187" s="3" t="inlineStr">
+      <c r="M187" s="3" t="inlineStr"/>
+      <c r="N187" s="3" t="inlineStr">
         <is>
           <t>w995236395</t>
         </is>
@@ -10939,7 +11131,8 @@
           <t>Fläche 287 m², Ø≈19 m, Rundheit 0.92. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M188" s="3" t="inlineStr">
+      <c r="M188" s="3" t="inlineStr"/>
+      <c r="N188" s="3" t="inlineStr">
         <is>
           <t>w137468185</t>
         </is>
@@ -10994,7 +11187,8 @@
           <t xml:space="preserve">Fläche 1720 m², Ø≈47 m, Rundheit 0.19. </t>
         </is>
       </c>
-      <c r="M189" s="3" t="inlineStr">
+      <c r="M189" s="3" t="inlineStr"/>
+      <c r="N189" s="3" t="inlineStr">
         <is>
           <t>w136072919</t>
         </is>
@@ -11049,7 +11243,8 @@
           <t>Fläche 58 m², Ø≈9 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M190" s="3" t="inlineStr">
+      <c r="M190" s="3" t="inlineStr"/>
+      <c r="N190" s="3" t="inlineStr">
         <is>
           <t>w1548447417</t>
         </is>
@@ -11100,7 +11295,8 @@
           <t>Fläche 474 m², Ø≈25 m, Rundheit 0.75.  | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M191" s="3" t="inlineStr">
+      <c r="M191" s="3" t="inlineStr"/>
+      <c r="N191" s="3" t="inlineStr">
         <is>
           <t>w377900239</t>
         </is>
@@ -11151,7 +11347,8 @@
           <t>Fläche 154 m², Ø≈14 m, Rundheit 0.94. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M192" s="3" t="inlineStr">
+      <c r="M192" s="3" t="inlineStr"/>
+      <c r="N192" s="3" t="inlineStr">
         <is>
           <t>w377900232</t>
         </is>
@@ -11202,7 +11399,8 @@
           <t>Fläche 227 m², Ø≈17 m, Rundheit 0.84. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M193" s="3" t="inlineStr">
+      <c r="M193" s="3" t="inlineStr"/>
+      <c r="N193" s="3" t="inlineStr">
         <is>
           <t>w377900238</t>
         </is>
@@ -11257,7 +11455,8 @@
           <t>Fläche 246 m², Ø≈18 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M194" s="3" t="inlineStr">
+      <c r="M194" s="3" t="inlineStr"/>
+      <c r="N194" s="3" t="inlineStr">
         <is>
           <t>w731986528</t>
         </is>
@@ -11312,7 +11511,8 @@
           <t>Fläche 156 m², Ø≈14 m, Rundheit 0.97. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M195" s="3" t="inlineStr">
+      <c r="M195" s="3" t="inlineStr"/>
+      <c r="N195" s="3" t="inlineStr">
         <is>
           <t>w1548444185</t>
         </is>
@@ -11363,7 +11563,8 @@
           <t>Fläche 94 m², Ø≈11 m, Rundheit 0.89. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M196" s="3" t="inlineStr">
+      <c r="M196" s="3" t="inlineStr"/>
+      <c r="N196" s="3" t="inlineStr">
         <is>
           <t>w377900233</t>
         </is>
@@ -11414,7 +11615,8 @@
           <t>Fläche 110 m², Ø≈12 m, Rundheit 0.94. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M197" s="3" t="inlineStr">
+      <c r="M197" s="3" t="inlineStr"/>
+      <c r="N197" s="3" t="inlineStr">
         <is>
           <t>w377900234</t>
         </is>
@@ -11469,7 +11671,8 @@
           <t>Fläche 109 m², Ø≈12 m, Rundheit 0.99. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M198" s="3" t="inlineStr">
+      <c r="M198" s="3" t="inlineStr"/>
+      <c r="N198" s="3" t="inlineStr">
         <is>
           <t>w1548444183</t>
         </is>
@@ -11524,7 +11727,8 @@
           <t>Fläche 45 m², Ø≈8 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M199" s="3" t="inlineStr">
+      <c r="M199" s="3" t="inlineStr"/>
+      <c r="N199" s="3" t="inlineStr">
         <is>
           <t>w1548444171</t>
         </is>
@@ -11579,7 +11783,8 @@
           <t>Fläche 31 m², Ø≈6 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M200" s="3" t="inlineStr">
+      <c r="M200" s="3" t="inlineStr"/>
+      <c r="N200" s="3" t="inlineStr">
         <is>
           <t>w1548444164</t>
         </is>
@@ -11634,7 +11839,8 @@
           <t>Fläche 45 m², Ø≈8 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M201" s="3" t="inlineStr">
+      <c r="M201" s="3" t="inlineStr"/>
+      <c r="N201" s="3" t="inlineStr">
         <is>
           <t>w1548444170</t>
         </is>
@@ -11689,7 +11895,8 @@
           <t>Fläche 45 m², Ø≈8 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M202" s="3" t="inlineStr">
+      <c r="M202" s="3" t="inlineStr"/>
+      <c r="N202" s="3" t="inlineStr">
         <is>
           <t>w1548444169</t>
         </is>
@@ -11744,7 +11951,8 @@
           <t>Fläche 45 m², Ø≈8 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M203" s="3" t="inlineStr">
+      <c r="M203" s="3" t="inlineStr"/>
+      <c r="N203" s="3" t="inlineStr">
         <is>
           <t>w1548444167</t>
         </is>
@@ -11799,7 +12007,8 @@
           <t>Fläche 45 m², Ø≈8 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M204" s="3" t="inlineStr">
+      <c r="M204" s="3" t="inlineStr"/>
+      <c r="N204" s="3" t="inlineStr">
         <is>
           <t>w1548444166</t>
         </is>
@@ -11854,7 +12063,8 @@
           <t>Fläche 45 m², Ø≈8 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M205" s="3" t="inlineStr">
+      <c r="M205" s="3" t="inlineStr"/>
+      <c r="N205" s="3" t="inlineStr">
         <is>
           <t>w1548444165</t>
         </is>
@@ -11909,7 +12119,8 @@
           <t>Fläche 31 m², Ø≈6 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M206" s="3" t="inlineStr">
+      <c r="M206" s="3" t="inlineStr"/>
+      <c r="N206" s="3" t="inlineStr">
         <is>
           <t>w1548444163</t>
         </is>
@@ -11964,7 +12175,8 @@
           <t>Fläche 45 m², Ø≈8 m, Rundheit 0.98. Kandidat Bombentrichter (rund, klein) – DGM-Check | wassergefüllter Trichter?</t>
         </is>
       </c>
-      <c r="M207" s="3" t="inlineStr">
+      <c r="M207" s="3" t="inlineStr"/>
+      <c r="N207" s="3" t="inlineStr">
         <is>
           <t>w1548444168</t>
         </is>
@@ -12019,7 +12231,8 @@
           <t xml:space="preserve">Fläche 4160 m², Ø≈73 m, Rundheit 0.10. </t>
         </is>
       </c>
-      <c r="M208" s="3" t="inlineStr">
+      <c r="M208" s="3" t="inlineStr"/>
+      <c r="N208" s="3" t="inlineStr">
         <is>
           <t>w136072918</t>
         </is>
@@ -12078,7 +12291,8 @@
           <t xml:space="preserve">Fläche 17899 m², Ø≈151 m, Rundheit 0.23. </t>
         </is>
       </c>
-      <c r="M209" s="3" t="inlineStr">
+      <c r="M209" s="3" t="inlineStr"/>
+      <c r="N209" s="3" t="inlineStr">
         <is>
           <t>w136072909</t>
         </is>
@@ -12129,7 +12343,8 @@
       </c>
       <c r="K210" s="3" t="inlineStr"/>
       <c r="L210" s="3" t="inlineStr"/>
-      <c r="M210" s="3" t="inlineStr">
+      <c r="M210" s="3" t="inlineStr"/>
+      <c r="N210" s="3" t="inlineStr">
         <is>
           <t>n531034541</t>
         </is>
@@ -12180,7 +12395,8 @@
       </c>
       <c r="K211" s="3" t="inlineStr"/>
       <c r="L211" s="3" t="inlineStr"/>
-      <c r="M211" s="3" t="inlineStr">
+      <c r="M211" s="3" t="inlineStr"/>
+      <c r="N211" s="3" t="inlineStr">
         <is>
           <t>n1274835530</t>
         </is>
@@ -12235,7 +12451,8 @@
           <t>Hier sind im zerbombten Bunker 20 Menschen gestorben und im verschütteten Bunker belassen worden.</t>
         </is>
       </c>
-      <c r="M212" s="3" t="inlineStr">
+      <c r="M212" s="3" t="inlineStr"/>
+      <c r="N212" s="3" t="inlineStr">
         <is>
           <t>n1486246330</t>
         </is>
@@ -12286,7 +12503,8 @@
       </c>
       <c r="K213" s="3" t="inlineStr"/>
       <c r="L213" s="3" t="inlineStr"/>
-      <c r="M213" s="3" t="inlineStr">
+      <c r="M213" s="3" t="inlineStr"/>
+      <c r="N213" s="3" t="inlineStr">
         <is>
           <t>n1431099411</t>
         </is>
@@ -12337,7 +12555,8 @@
       </c>
       <c r="K214" s="3" t="inlineStr"/>
       <c r="L214" s="3" t="inlineStr"/>
-      <c r="M214" s="3" t="inlineStr">
+      <c r="M214" s="3" t="inlineStr"/>
+      <c r="N214" s="3" t="inlineStr">
         <is>
           <t>w30127323</t>
         </is>
@@ -12388,7 +12607,8 @@
       </c>
       <c r="K215" s="3" t="inlineStr"/>
       <c r="L215" s="3" t="inlineStr"/>
-      <c r="M215" s="3" t="inlineStr">
+      <c r="M215" s="3" t="inlineStr"/>
+      <c r="N215" s="3" t="inlineStr">
         <is>
           <t>w60164668</t>
         </is>
@@ -12443,7 +12663,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M216" s="3" t="inlineStr">
+      <c r="M216" s="3" t="inlineStr"/>
+      <c r="N216" s="3" t="inlineStr">
         <is>
           <t>n2377907039</t>
         </is>
@@ -12498,7 +12719,8 @@
           <t>fire_hydrant:diameter=100, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M217" s="3" t="inlineStr">
+      <c r="M217" s="3" t="inlineStr"/>
+      <c r="N217" s="3" t="inlineStr">
         <is>
           <t>n2377907032</t>
         </is>
@@ -12553,7 +12775,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M218" s="3" t="inlineStr">
+      <c r="M218" s="3" t="inlineStr"/>
+      <c r="N218" s="3" t="inlineStr">
         <is>
           <t>n2377907015</t>
         </is>
@@ -12608,7 +12831,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M219" s="3" t="inlineStr">
+      <c r="M219" s="3" t="inlineStr"/>
+      <c r="N219" s="3" t="inlineStr">
         <is>
           <t>n2377907027</t>
         </is>
@@ -12663,7 +12887,8 @@
           <t>fire_hydrant:diameter=125, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M220" s="3" t="inlineStr">
+      <c r="M220" s="3" t="inlineStr"/>
+      <c r="N220" s="3" t="inlineStr">
         <is>
           <t>n2377907030</t>
         </is>
@@ -12718,7 +12943,8 @@
           <t>fire_hydrant:diameter=125, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M221" s="3" t="inlineStr">
+      <c r="M221" s="3" t="inlineStr"/>
+      <c r="N221" s="3" t="inlineStr">
         <is>
           <t>n2377907023</t>
         </is>
@@ -12773,7 +12999,8 @@
           <t>fire_hydrant:diameter=125, fire_hydrant:position=lane, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M222" s="3" t="inlineStr">
+      <c r="M222" s="3" t="inlineStr"/>
+      <c r="N222" s="3" t="inlineStr">
         <is>
           <t>n9919478763</t>
         </is>
@@ -12828,7 +13055,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M223" s="3" t="inlineStr">
+      <c r="M223" s="3" t="inlineStr"/>
+      <c r="N223" s="3" t="inlineStr">
         <is>
           <t>n2377907003</t>
         </is>
@@ -12883,7 +13111,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M224" s="3" t="inlineStr">
+      <c r="M224" s="3" t="inlineStr"/>
+      <c r="N224" s="3" t="inlineStr">
         <is>
           <t>n2377906991</t>
         </is>
@@ -12938,7 +13167,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:position=lane, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M225" s="3" t="inlineStr">
+      <c r="M225" s="3" t="inlineStr"/>
+      <c r="N225" s="3" t="inlineStr">
         <is>
           <t>n2377906969</t>
         </is>
@@ -12993,7 +13223,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M226" s="3" t="inlineStr">
+      <c r="M226" s="3" t="inlineStr"/>
+      <c r="N226" s="3" t="inlineStr">
         <is>
           <t>n2377906947</t>
         </is>
@@ -13048,7 +13279,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:position=lane, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M227" s="3" t="inlineStr">
+      <c r="M227" s="3" t="inlineStr"/>
+      <c r="N227" s="3" t="inlineStr">
         <is>
           <t>n2377906961</t>
         </is>
@@ -13103,7 +13335,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M228" s="3" t="inlineStr">
+      <c r="M228" s="3" t="inlineStr"/>
+      <c r="N228" s="3" t="inlineStr">
         <is>
           <t>n2377906936</t>
         </is>
@@ -13158,7 +13391,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M229" s="3" t="inlineStr">
+      <c r="M229" s="3" t="inlineStr"/>
+      <c r="N229" s="3" t="inlineStr">
         <is>
           <t>n2377906934</t>
         </is>
@@ -13213,7 +13447,8 @@
           <t>fire_hydrant:diameter=80, fire_hydrant:position=green, fire_hydrant:type=underground</t>
         </is>
       </c>
-      <c r="M230" s="3" t="inlineStr">
+      <c r="M230" s="3" t="inlineStr"/>
+      <c r="N230" s="3" t="inlineStr">
         <is>
           <t>n2377906933</t>
         </is>
@@ -13264,7 +13499,8 @@
       </c>
       <c r="K231" s="3" t="inlineStr"/>
       <c r="L231" s="3" t="inlineStr"/>
-      <c r="M231" s="3" t="inlineStr">
+      <c r="M231" s="3" t="inlineStr"/>
+      <c r="N231" s="3" t="inlineStr">
         <is>
           <t>n9710900352</t>
         </is>
@@ -13315,7 +13551,8 @@
       </c>
       <c r="K232" s="3" t="inlineStr"/>
       <c r="L232" s="3" t="inlineStr"/>
-      <c r="M232" s="3" t="inlineStr">
+      <c r="M232" s="3" t="inlineStr"/>
+      <c r="N232" s="3" t="inlineStr">
         <is>
           <t>n12134557255</t>
         </is>
@@ -13370,7 +13607,8 @@
         </is>
       </c>
       <c r="L233" s="3" t="inlineStr"/>
-      <c r="M233" s="3" t="inlineStr">
+      <c r="M233" s="3" t="inlineStr"/>
+      <c r="N233" s="3" t="inlineStr">
         <is>
           <t>n1431891145</t>
         </is>
@@ -13421,7 +13659,8 @@
       </c>
       <c r="K234" s="3" t="inlineStr"/>
       <c r="L234" s="3" t="inlineStr"/>
-      <c r="M234" s="3" t="inlineStr">
+      <c r="M234" s="3" t="inlineStr"/>
+      <c r="N234" s="3" t="inlineStr">
         <is>
           <t>n1430929572</t>
         </is>
@@ -13472,7 +13711,8 @@
       </c>
       <c r="K235" s="3" t="inlineStr"/>
       <c r="L235" s="3" t="inlineStr"/>
-      <c r="M235" s="3" t="inlineStr">
+      <c r="M235" s="3" t="inlineStr"/>
+      <c r="N235" s="3" t="inlineStr">
         <is>
           <t>n13370492761</t>
         </is>
@@ -13523,7 +13763,8 @@
       </c>
       <c r="K236" s="3" t="inlineStr"/>
       <c r="L236" s="3" t="inlineStr"/>
-      <c r="M236" s="3" t="inlineStr">
+      <c r="M236" s="3" t="inlineStr"/>
+      <c r="N236" s="3" t="inlineStr">
         <is>
           <t>n13370496186</t>
         </is>
@@ -13574,7 +13815,8 @@
       </c>
       <c r="K237" s="3" t="inlineStr"/>
       <c r="L237" s="3" t="inlineStr"/>
-      <c r="M237" s="3" t="inlineStr">
+      <c r="M237" s="3" t="inlineStr"/>
+      <c r="N237" s="3" t="inlineStr">
         <is>
           <t>n13990299824</t>
         </is>
@@ -13621,7 +13863,8 @@
       </c>
       <c r="K238" s="3" t="inlineStr"/>
       <c r="L238" s="3" t="inlineStr"/>
-      <c r="M238" s="3" t="inlineStr">
+      <c r="M238" s="3" t="inlineStr"/>
+      <c r="N238" s="3" t="inlineStr">
         <is>
           <t>n13993595640</t>
         </is>
@@ -13668,7 +13911,8 @@
       </c>
       <c r="K239" s="3" t="inlineStr"/>
       <c r="L239" s="3" t="inlineStr"/>
-      <c r="M239" s="3" t="inlineStr">
+      <c r="M239" s="3" t="inlineStr"/>
+      <c r="N239" s="3" t="inlineStr">
         <is>
           <t>n1431891138</t>
         </is>
@@ -13715,7 +13959,8 @@
       </c>
       <c r="K240" s="3" t="inlineStr"/>
       <c r="L240" s="3" t="inlineStr"/>
-      <c r="M240" s="3" t="inlineStr">
+      <c r="M240" s="3" t="inlineStr"/>
+      <c r="N240" s="3" t="inlineStr">
         <is>
           <t>n14017913418</t>
         </is>
@@ -13762,7 +14007,8 @@
       </c>
       <c r="K241" s="3" t="inlineStr"/>
       <c r="L241" s="3" t="inlineStr"/>
-      <c r="M241" s="3" t="inlineStr">
+      <c r="M241" s="3" t="inlineStr"/>
+      <c r="N241" s="3" t="inlineStr">
         <is>
           <t>n2314627172</t>
         </is>
@@ -13809,7 +14055,8 @@
       </c>
       <c r="K242" s="3" t="inlineStr"/>
       <c r="L242" s="3" t="inlineStr"/>
-      <c r="M242" s="3" t="inlineStr">
+      <c r="M242" s="3" t="inlineStr"/>
+      <c r="N242" s="3" t="inlineStr">
         <is>
           <t>n2314627171</t>
         </is>
@@ -13856,7 +14103,8 @@
       </c>
       <c r="K243" s="3" t="inlineStr"/>
       <c r="L243" s="3" t="inlineStr"/>
-      <c r="M243" s="3" t="inlineStr">
+      <c r="M243" s="3" t="inlineStr"/>
+      <c r="N243" s="3" t="inlineStr">
         <is>
           <t>n13987849164</t>
         </is>
@@ -13907,7 +14155,8 @@
       </c>
       <c r="K244" s="3" t="inlineStr"/>
       <c r="L244" s="3" t="inlineStr"/>
-      <c r="M244" s="3" t="inlineStr">
+      <c r="M244" s="3" t="inlineStr"/>
+      <c r="N244" s="3" t="inlineStr">
         <is>
           <t>n14017892134</t>
         </is>
@@ -13958,7 +14207,8 @@
       </c>
       <c r="K245" s="3" t="inlineStr"/>
       <c r="L245" s="3" t="inlineStr"/>
-      <c r="M245" s="3" t="inlineStr">
+      <c r="M245" s="3" t="inlineStr"/>
+      <c r="N245" s="3" t="inlineStr">
         <is>
           <t>n2446054248</t>
         </is>
@@ -14014,6 +14264,7 @@
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr"/>
+      <c r="N246" s="3" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -14065,6 +14316,7 @@
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr"/>
+      <c r="N247" s="3" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -14116,6 +14368,7 @@
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr"/>
+      <c r="N248" s="3" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
@@ -14167,6 +14420,7 @@
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr"/>
+      <c r="N249" s="3" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
@@ -14218,6 +14472,7 @@
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr"/>
+      <c r="N250" s="3" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -14269,6 +14524,7 @@
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr"/>
+      <c r="N251" s="3" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
@@ -14320,6 +14576,7 @@
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr"/>
+      <c r="N252" s="3" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
@@ -14371,6 +14628,7 @@
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr"/>
+      <c r="N253" s="3" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
@@ -14422,6 +14680,7 @@
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr"/>
+      <c r="N254" s="3" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -14473,6 +14732,7 @@
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr"/>
+      <c r="N255" s="3" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
@@ -14524,6 +14784,7 @@
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr"/>
+      <c r="N256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -14575,6 +14836,7 @@
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr"/>
+      <c r="N257" s="3" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
@@ -14626,6 +14888,7 @@
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr"/>
+      <c r="N258" s="3" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -14677,6 +14940,7 @@
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr"/>
+      <c r="N259" s="3" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
@@ -14728,6 +14992,7 @@
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr"/>
+      <c r="N260" s="3" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -14779,6 +15044,7 @@
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr"/>
+      <c r="N261" s="3" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -14830,6 +15096,7 @@
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr"/>
+      <c r="N262" s="3" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -14881,6 +15148,7 @@
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr"/>
+      <c r="N263" s="3" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
@@ -14932,6 +15200,7 @@
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr"/>
+      <c r="N264" s="3" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -14976,13 +15245,18 @@
       <c r="J265" s="10" t="n">
         <v>5959992.5</v>
       </c>
-      <c r="K265" s="3" t="inlineStr"/>
+      <c r="K265" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
           <t>Höhe 14.3 m NHN, ragt 9.0 m über die Umgebung</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr"/>
+      <c r="N265" s="3" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
@@ -15034,6 +15308,7 @@
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr"/>
+      <c r="N266" s="3" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
@@ -15085,6 +15360,7 @@
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr"/>
+      <c r="N267" s="3" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -15136,6 +15412,7 @@
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr"/>
+      <c r="N268" s="3" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -15187,6 +15464,7 @@
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr"/>
+      <c r="N269" s="3" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
@@ -15238,6 +15516,7 @@
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr"/>
+      <c r="N270" s="3" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -15289,6 +15568,7 @@
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr"/>
+      <c r="N271" s="3" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
@@ -15340,6 +15620,7 @@
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr"/>
+      <c r="N272" s="3" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -15391,6 +15672,7 @@
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr"/>
+      <c r="N273" s="3" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
@@ -15442,6 +15724,7 @@
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr"/>
+      <c r="N274" s="3" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
@@ -15486,13 +15769,18 @@
       <c r="J275" s="10" t="n">
         <v>5959757.5</v>
       </c>
-      <c r="K275" s="3" t="inlineStr"/>
+      <c r="K275" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L275" s="3" t="inlineStr">
         <is>
           <t>Höhe 12.4 m NHN, ragt 8.3 m über die Umgebung</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr"/>
+      <c r="N275" s="3" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
@@ -15544,6 +15832,7 @@
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr"/>
+      <c r="N276" s="3" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
@@ -15588,13 +15877,18 @@
       <c r="J277" s="10" t="n">
         <v>5959561.5</v>
       </c>
-      <c r="K277" s="3" t="inlineStr"/>
+      <c r="K277" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L277" s="3" t="inlineStr">
         <is>
           <t>Höhe 12.3 m NHN, ragt 8.6 m über die Umgebung</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr"/>
+      <c r="N277" s="3" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
@@ -15639,13 +15933,18 @@
       <c r="J278" s="10" t="n">
         <v>5959848.5</v>
       </c>
-      <c r="K278" s="3" t="inlineStr"/>
+      <c r="K278" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
           <t>Höhe 12.1 m NHN, ragt 8.6 m über die Umgebung</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr"/>
+      <c r="N278" s="3" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
@@ -15690,13 +15989,18 @@
       <c r="J279" s="10" t="n">
         <v>5959876.5</v>
       </c>
-      <c r="K279" s="3" t="inlineStr"/>
+      <c r="K279" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L279" s="3" t="inlineStr">
         <is>
           <t>Höhe 12.1 m NHN, ragt 8.4 m über die Umgebung</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr"/>
+      <c r="N279" s="3" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
@@ -15741,13 +16045,18 @@
       <c r="J280" s="10" t="n">
         <v>5959640.5</v>
       </c>
-      <c r="K280" s="3" t="inlineStr"/>
+      <c r="K280" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
           <t>Höhe 12.1 m NHN, ragt 8.3 m über die Umgebung</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr"/>
+      <c r="N280" s="3" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
@@ -15792,13 +16101,18 @@
       <c r="J281" s="10" t="n">
         <v>5959974.5</v>
       </c>
-      <c r="K281" s="3" t="inlineStr"/>
+      <c r="K281" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
           <t>Höhe 11.7 m NHN, ragt 4.7 m über die Umgebung</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr"/>
+      <c r="N281" s="3" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
@@ -15843,13 +16157,18 @@
       <c r="J282" s="10" t="n">
         <v>5959510.5</v>
       </c>
-      <c r="K282" s="3" t="inlineStr"/>
+      <c r="K282" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
           <t>Höhe 11.6 m NHN, ragt 8.3 m über die Umgebung</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr"/>
+      <c r="N282" s="3" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -15901,6 +16220,7 @@
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr"/>
+      <c r="N283" s="3" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
@@ -15952,6 +16272,7 @@
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr"/>
+      <c r="N284" s="3" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
@@ -16003,6 +16324,7 @@
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr"/>
+      <c r="N285" s="3" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
@@ -16054,6 +16376,7 @@
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr"/>
+      <c r="N286" s="3" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
@@ -16105,6 +16428,7 @@
         </is>
       </c>
       <c r="M287" s="3" t="inlineStr"/>
+      <c r="N287" s="3" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
@@ -16156,6 +16480,7 @@
         </is>
       </c>
       <c r="M288" s="3" t="inlineStr"/>
+      <c r="N288" s="3" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
@@ -16207,6 +16532,7 @@
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr"/>
+      <c r="N289" s="3" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
@@ -16258,6 +16584,7 @@
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr"/>
+      <c r="N290" s="3" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
@@ -16309,6 +16636,7 @@
         </is>
       </c>
       <c r="M291" s="3" t="inlineStr"/>
+      <c r="N291" s="3" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
@@ -16360,6 +16688,7 @@
         </is>
       </c>
       <c r="M292" s="3" t="inlineStr"/>
+      <c r="N292" s="3" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
@@ -16411,6 +16740,7 @@
         </is>
       </c>
       <c r="M293" s="3" t="inlineStr"/>
+      <c r="N293" s="3" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
@@ -16462,6 +16792,7 @@
         </is>
       </c>
       <c r="M294" s="3" t="inlineStr"/>
+      <c r="N294" s="3" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
@@ -16513,6 +16844,7 @@
         </is>
       </c>
       <c r="M295" s="3" t="inlineStr"/>
+      <c r="N295" s="3" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
@@ -16564,6 +16896,7 @@
         </is>
       </c>
       <c r="M296" s="3" t="inlineStr"/>
+      <c r="N296" s="3" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -16615,6 +16948,7 @@
         </is>
       </c>
       <c r="M297" s="3" t="inlineStr"/>
+      <c r="N297" s="3" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
@@ -16666,6 +17000,7 @@
         </is>
       </c>
       <c r="M298" s="3" t="inlineStr"/>
+      <c r="N298" s="3" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
@@ -16717,6 +17052,7 @@
         </is>
       </c>
       <c r="M299" s="3" t="inlineStr"/>
+      <c r="N299" s="3" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
@@ -16768,6 +17104,7 @@
         </is>
       </c>
       <c r="M300" s="3" t="inlineStr"/>
+      <c r="N300" s="3" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
@@ -16819,6 +17156,7 @@
         </is>
       </c>
       <c r="M301" s="3" t="inlineStr"/>
+      <c r="N301" s="3" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
@@ -16870,6 +17208,7 @@
         </is>
       </c>
       <c r="M302" s="3" t="inlineStr"/>
+      <c r="N302" s="3" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
@@ -16921,6 +17260,7 @@
         </is>
       </c>
       <c r="M303" s="3" t="inlineStr"/>
+      <c r="N303" s="3" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
@@ -16972,6 +17312,7 @@
         </is>
       </c>
       <c r="M304" s="3" t="inlineStr"/>
+      <c r="N304" s="3" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
@@ -17023,6 +17364,7 @@
         </is>
       </c>
       <c r="M305" s="3" t="inlineStr"/>
+      <c r="N305" s="3" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
@@ -17074,6 +17416,7 @@
         </is>
       </c>
       <c r="M306" s="3" t="inlineStr"/>
+      <c r="N306" s="3" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -17125,6 +17468,7 @@
         </is>
       </c>
       <c r="M307" s="3" t="inlineStr"/>
+      <c r="N307" s="3" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
@@ -17176,6 +17520,7 @@
         </is>
       </c>
       <c r="M308" s="3" t="inlineStr"/>
+      <c r="N308" s="3" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
@@ -17227,6 +17572,7 @@
         </is>
       </c>
       <c r="M309" s="3" t="inlineStr"/>
+      <c r="N309" s="3" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
@@ -17278,6 +17624,7 @@
         </is>
       </c>
       <c r="M310" s="3" t="inlineStr"/>
+      <c r="N310" s="3" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
@@ -17329,6 +17676,7 @@
         </is>
       </c>
       <c r="M311" s="3" t="inlineStr"/>
+      <c r="N311" s="3" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
@@ -17380,6 +17728,7 @@
         </is>
       </c>
       <c r="M312" s="3" t="inlineStr"/>
+      <c r="N312" s="3" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
@@ -17431,6 +17780,7 @@
         </is>
       </c>
       <c r="M313" s="3" t="inlineStr"/>
+      <c r="N313" s="3" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
@@ -17482,6 +17832,7 @@
         </is>
       </c>
       <c r="M314" s="3" t="inlineStr"/>
+      <c r="N314" s="3" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
@@ -17533,6 +17884,7 @@
         </is>
       </c>
       <c r="M315" s="3" t="inlineStr"/>
+      <c r="N315" s="3" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
@@ -17584,6 +17936,7 @@
         </is>
       </c>
       <c r="M316" s="3" t="inlineStr"/>
+      <c r="N316" s="3" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
@@ -17628,13 +17981,18 @@
       <c r="J317" s="10" t="n">
         <v>5960217.5</v>
       </c>
-      <c r="K317" s="3" t="inlineStr"/>
+      <c r="K317" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L317" s="3" t="inlineStr">
         <is>
           <t>Höhe 6.3 m NHN, ragt 3.5 m über die Umgebung</t>
         </is>
       </c>
       <c r="M317" s="3" t="inlineStr"/>
+      <c r="N317" s="3" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
@@ -17686,6 +18044,7 @@
         </is>
       </c>
       <c r="M318" s="3" t="inlineStr"/>
+      <c r="N318" s="3" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
@@ -17737,6 +18096,7 @@
         </is>
       </c>
       <c r="M319" s="3" t="inlineStr"/>
+      <c r="N319" s="3" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
@@ -17788,6 +18148,7 @@
         </is>
       </c>
       <c r="M320" s="3" t="inlineStr"/>
+      <c r="N320" s="3" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
@@ -17839,6 +18200,7 @@
         </is>
       </c>
       <c r="M321" s="3" t="inlineStr"/>
+      <c r="N321" s="3" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
@@ -17890,6 +18252,7 @@
         </is>
       </c>
       <c r="M322" s="3" t="inlineStr"/>
+      <c r="N322" s="3" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
@@ -17934,13 +18297,18 @@
       <c r="J323" s="10" t="n">
         <v>5960217.5</v>
       </c>
-      <c r="K323" s="3" t="inlineStr"/>
+      <c r="K323" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L323" s="3" t="inlineStr">
         <is>
           <t>Höhe 5.9 m NHN, ragt 2.9 m über die Umgebung</t>
         </is>
       </c>
       <c r="M323" s="3" t="inlineStr"/>
+      <c r="N323" s="3" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
@@ -17992,6 +18360,7 @@
         </is>
       </c>
       <c r="M324" s="3" t="inlineStr"/>
+      <c r="N324" s="3" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -18043,6 +18412,7 @@
         </is>
       </c>
       <c r="M325" s="3" t="inlineStr"/>
+      <c r="N325" s="3" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
@@ -18094,6 +18464,7 @@
         </is>
       </c>
       <c r="M326" s="3" t="inlineStr"/>
+      <c r="N326" s="3" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -18138,13 +18509,18 @@
       <c r="J327" s="10" t="n">
         <v>5960776.5</v>
       </c>
-      <c r="K327" s="3" t="inlineStr"/>
+      <c r="K327" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L327" s="3" t="inlineStr">
         <is>
           <t>Höhe 5.6 m NHN, ragt 2.1 m über die Umgebung</t>
         </is>
       </c>
       <c r="M327" s="3" t="inlineStr"/>
+      <c r="N327" s="3" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
@@ -18196,6 +18572,7 @@
         </is>
       </c>
       <c r="M328" s="3" t="inlineStr"/>
+      <c r="N328" s="3" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
@@ -18247,6 +18624,7 @@
         </is>
       </c>
       <c r="M329" s="3" t="inlineStr"/>
+      <c r="N329" s="3" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
@@ -18291,13 +18669,18 @@
       <c r="J330" s="10" t="n">
         <v>5960219.5</v>
       </c>
-      <c r="K330" s="3" t="inlineStr"/>
+      <c r="K330" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L330" s="3" t="inlineStr">
         <is>
           <t>Höhe 5.4 m NHN, ragt 2.9 m über die Umgebung</t>
         </is>
       </c>
       <c r="M330" s="3" t="inlineStr"/>
+      <c r="N330" s="3" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
@@ -18349,6 +18732,7 @@
         </is>
       </c>
       <c r="M331" s="3" t="inlineStr"/>
+      <c r="N331" s="3" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
@@ -18400,6 +18784,7 @@
         </is>
       </c>
       <c r="M332" s="3" t="inlineStr"/>
+      <c r="N332" s="3" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
@@ -18446,7 +18831,8 @@
           <t>glass_bottles</t>
         </is>
       </c>
-      <c r="M333" s="3" t="inlineStr">
+      <c r="M333" s="3" t="inlineStr"/>
+      <c r="N333" s="3" t="inlineStr">
         <is>
           <t>n743377509</t>
         </is>
@@ -18497,7 +18883,8 @@
           <t>glass_bottles</t>
         </is>
       </c>
-      <c r="M334" s="3" t="inlineStr">
+      <c r="M334" s="3" t="inlineStr"/>
+      <c r="N334" s="3" t="inlineStr">
         <is>
           <t>n743377614</t>
         </is>
@@ -18548,7 +18935,8 @@
       </c>
       <c r="K335" s="3" t="inlineStr"/>
       <c r="L335" s="3" t="inlineStr"/>
-      <c r="M335" s="3" t="inlineStr">
+      <c r="M335" s="3" t="inlineStr"/>
+      <c r="N335" s="3" t="inlineStr">
         <is>
           <t>n12102857779</t>
         </is>
@@ -18599,7 +18987,8 @@
           <t>glass_bottles</t>
         </is>
       </c>
-      <c r="M336" s="3" t="inlineStr">
+      <c r="M336" s="3" t="inlineStr"/>
+      <c r="N336" s="3" t="inlineStr">
         <is>
           <t>n12778228548</t>
         </is>
@@ -18650,7 +19039,8 @@
           <t>glass_bottles</t>
         </is>
       </c>
-      <c r="M337" s="3" t="inlineStr">
+      <c r="M337" s="3" t="inlineStr"/>
+      <c r="N337" s="3" t="inlineStr">
         <is>
           <t>n743377571</t>
         </is>
@@ -18705,7 +19095,8 @@
           <t>Straße zum Westen, Dünenübergang in der S-Kurve westlich der Saline - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M338" s="3" t="inlineStr">
+      <c r="M338" s="3" t="inlineStr"/>
+      <c r="N338" s="3" t="inlineStr">
         <is>
           <t>n2522177126</t>
         </is>
@@ -18760,7 +19151,8 @@
           <t>Weststrand, Übergang beim Ehrenfriedhof, nur mit Allradfahrzeug erreichen.</t>
         </is>
       </c>
-      <c r="M339" s="3" t="inlineStr">
+      <c r="M339" s="3" t="inlineStr"/>
+      <c r="N339" s="3" t="inlineStr">
         <is>
           <t>n2522165185</t>
         </is>
@@ -18815,7 +19207,8 @@
           <t>Weststrand, Übergang Bielefelder Heim, Aussichtsdüne, nur mit Allradfahrzeug zu erreichen. | OSM-Hinweis: Position?</t>
         </is>
       </c>
-      <c r="M340" s="3" t="inlineStr">
+      <c r="M340" s="3" t="inlineStr"/>
+      <c r="N340" s="3" t="inlineStr">
         <is>
           <t>n2522163266</t>
         </is>
@@ -18870,7 +19263,8 @@
           <t>Aussichtsdüne Weststrand, Anfahrt : Straße zum Westen, Bielefelder Haus, ab da nur zu Fuss durch die Dünen Richtung Strand, Anfahrt vom Strand : Richtung Westen bis Übergang Bielefelder Haus - Achtung : nur mit Allradfahrzeug zu erreichen</t>
         </is>
       </c>
-      <c r="M341" s="3" t="inlineStr">
+      <c r="M341" s="3" t="inlineStr"/>
+      <c r="N341" s="3" t="inlineStr">
         <is>
           <t>n2522164616</t>
         </is>
@@ -18925,7 +19319,8 @@
           <t>Straße zum Westen, Schutzhütte auf der langen geraden zwischen Saline und Westen- für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M342" s="3" t="inlineStr">
+      <c r="M342" s="3" t="inlineStr"/>
+      <c r="N342" s="3" t="inlineStr">
         <is>
           <t>n2522177562</t>
         </is>
@@ -18980,7 +19375,8 @@
           <t>Straße zum Westen, Dünenübergang Saline -Fussweg bei der Saline Richtung Strand - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M343" s="3" t="inlineStr">
+      <c r="M343" s="3" t="inlineStr"/>
+      <c r="N343" s="3" t="inlineStr">
         <is>
           <t>n2522175440</t>
         </is>
@@ -19035,7 +19431,8 @@
           <t>Fussweg zum Westen, Dünenüberweg hinter dem Ehrenfriedhof - Anfahrt über Straße zum Westen - beim Bielefelder Haus rechts - den Fussweg links rein - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M344" s="3" t="inlineStr">
+      <c r="M344" s="3" t="inlineStr"/>
+      <c r="N344" s="3" t="inlineStr">
         <is>
           <t>n2522171524</t>
         </is>
@@ -19090,7 +19487,8 @@
           <t>Fussweg zum Westen, Eingang Ehrenfriedhof, Anfahrt über Straße zum Westen -beim Bielefelder Haus rechts - den Fussweg links rein - für alle Fahrzeuge geeignet</t>
         </is>
       </c>
-      <c r="M345" s="3" t="inlineStr">
+      <c r="M345" s="3" t="inlineStr"/>
+      <c r="N345" s="3" t="inlineStr">
         <is>
           <t>n2522171456</t>
         </is>
@@ -19145,7 +19543,8 @@
           <t>Straße zum Westen, in der Kurve beim Bielefelder Heim - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M346" s="3" t="inlineStr">
+      <c r="M346" s="3" t="inlineStr"/>
+      <c r="N346" s="3" t="inlineStr">
         <is>
           <t>n2522192201</t>
         </is>
@@ -19200,7 +19599,8 @@
           <t>Weg zum Surfstrand, Parkbank Höhe Tennisplatz - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M347" s="3" t="inlineStr">
+      <c r="M347" s="3" t="inlineStr"/>
+      <c r="N347" s="3" t="inlineStr">
         <is>
           <t>n2522191067</t>
         </is>
@@ -19255,7 +19655,8 @@
           <t>Straße zum Westen, Dünenübergang beim Lagerplatz am neuen Leuchtturm - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M348" s="3" t="inlineStr">
+      <c r="M348" s="3" t="inlineStr"/>
+      <c r="N348" s="3" t="inlineStr">
         <is>
           <t>n2522179435</t>
         </is>
@@ -19314,7 +19715,8 @@
           <t>Westdeich, Übergang alter Deich, bei der Hinweistafel, für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M349" s="3" t="inlineStr">
+      <c r="M349" s="3" t="inlineStr"/>
+      <c r="N349" s="3" t="inlineStr">
         <is>
           <t>n2522187773</t>
         </is>
@@ -19369,7 +19771,8 @@
           <t>Straße zum Westen, Schutzhütte ehem. Yachtclub kurz vor Saline. Für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M350" s="3" t="inlineStr">
+      <c r="M350" s="3" t="inlineStr"/>
+      <c r="N350" s="3" t="inlineStr">
         <is>
           <t>n2522156300</t>
         </is>
@@ -19424,7 +19827,8 @@
           <t>Strasse zum Westen - Parkbank kurz vor Wetterhäuschen ehem. Yachtclub</t>
         </is>
       </c>
-      <c r="M351" s="3" t="inlineStr">
+      <c r="M351" s="3" t="inlineStr"/>
+      <c r="N351" s="3" t="inlineStr">
         <is>
           <t>n2522204511</t>
         </is>
@@ -19479,7 +19883,8 @@
           <t>Straße zum Westen, zwischen Friedhof und Saline - wo der Fussweg auf die Strasse trifft - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M352" s="3" t="inlineStr">
+      <c r="M352" s="3" t="inlineStr"/>
+      <c r="N352" s="3" t="inlineStr">
         <is>
           <t>n2522172835</t>
         </is>
@@ -19534,7 +19939,8 @@
           <t>Straße zum Westen, am Friedhof vorbei - Dünenweg bei der Ausweichbucht auf der Erhöhung - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M353" s="3" t="inlineStr">
+      <c r="M353" s="3" t="inlineStr"/>
+      <c r="N353" s="3" t="inlineStr">
         <is>
           <t>n2522172316</t>
         </is>
@@ -19589,7 +19995,8 @@
           <t>Strasse zum Westen, bei der Friedhofkapelle, für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M354" s="3" t="inlineStr">
+      <c r="M354" s="3" t="inlineStr"/>
+      <c r="N354" s="3" t="inlineStr">
         <is>
           <t>n2522166093</t>
         </is>
@@ -19644,7 +20051,8 @@
           <t>Westdeich, ehemaliger Yachthafen, für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M355" s="3" t="inlineStr">
+      <c r="M355" s="3" t="inlineStr"/>
+      <c r="N355" s="3" t="inlineStr">
         <is>
           <t>n2522171197</t>
         </is>
@@ -19699,7 +20107,8 @@
           <t>In den Dünen, Reitweg westlich vom Friedhof - nur mit Allradfahrzeug zu erreichen.</t>
         </is>
       </c>
-      <c r="M356" s="3" t="inlineStr">
+      <c r="M356" s="3" t="inlineStr"/>
+      <c r="N356" s="3" t="inlineStr">
         <is>
           <t>n2522193020</t>
         </is>
@@ -19754,7 +20163,8 @@
           <t>Erlengrund, Thunpad Anfahrt über Straße zum Westen - bei der neuen Feuerwehr den Schotterweg links rein - in Höhe Friesenstrasse auf der rechten Seite - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M357" s="3" t="inlineStr">
+      <c r="M357" s="3" t="inlineStr"/>
+      <c r="N357" s="3" t="inlineStr">
         <is>
           <t>n2522172152</t>
         </is>
@@ -19809,7 +20219,8 @@
           <t>Westdeckwerk, Weg beim WSA / Haus am Meer - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M358" s="3" t="inlineStr">
+      <c r="M358" s="3" t="inlineStr"/>
+      <c r="N358" s="3" t="inlineStr">
         <is>
           <t>n2522187324</t>
         </is>
@@ -19868,7 +20279,8 @@
           <t>Westdeich, Parkbank Mitte zwischen Saline und Westturm - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M359" s="3" t="inlineStr">
+      <c r="M359" s="3" t="inlineStr"/>
+      <c r="N359" s="3" t="inlineStr">
         <is>
           <t>n2522186231</t>
         </is>
@@ -19923,7 +20335,8 @@
           <t>Westdeich, zwischen Müllumschlagstation und ehemaligen Yachthafen (Saline) - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M360" s="3" t="inlineStr">
+      <c r="M360" s="3" t="inlineStr"/>
+      <c r="N360" s="3" t="inlineStr">
         <is>
           <t>n2522167728</t>
         </is>
@@ -19978,7 +20391,8 @@
           <t>Westgrodendeich, westlich Müllumschlagstation beim Pad zum Friedhof - für alle Fahrzeuge geeignet</t>
         </is>
       </c>
-      <c r="M361" s="3" t="inlineStr">
+      <c r="M361" s="3" t="inlineStr"/>
+      <c r="N361" s="3" t="inlineStr">
         <is>
           <t>n2522167444</t>
         </is>
@@ -20037,7 +20451,8 @@
           <t>Westdeich, Parkbank beim Pumpenhaus, für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M362" s="3" t="inlineStr">
+      <c r="M362" s="3" t="inlineStr"/>
+      <c r="N362" s="3" t="inlineStr">
         <is>
           <t>n2522189558</t>
         </is>
@@ -20092,7 +20507,8 @@
           <t>Wendehammer Straße am Wattenmeer/Deich, am Schaukasten Wattenmeer, für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M363" s="3" t="inlineStr">
+      <c r="M363" s="3" t="inlineStr"/>
+      <c r="N363" s="3" t="inlineStr">
         <is>
           <t>n2522154152</t>
         </is>
@@ -20143,7 +20559,8 @@
       </c>
       <c r="K364" s="3" t="inlineStr"/>
       <c r="L364" s="3" t="inlineStr"/>
-      <c r="M364" s="3" t="inlineStr">
+      <c r="M364" s="3" t="inlineStr"/>
+      <c r="N364" s="3" t="inlineStr">
         <is>
           <t>n12269593010</t>
         </is>
@@ -20198,7 +20615,8 @@
           <t>Dorfdeich, Treffpunkt Niedergang Wattwanderer, für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M365" s="3" t="inlineStr">
+      <c r="M365" s="3" t="inlineStr"/>
+      <c r="N365" s="3" t="inlineStr">
         <is>
           <t>n2522153669</t>
         </is>
@@ -20253,7 +20671,8 @@
           <t>Westdeckwerk, Dünenübergang beim Westturm, Anfahrt über Strasse zum Westen - beim Haus am Meer den Fussweg hoch zum Deckwerk - dann links bis zum Ende - Achtung : von Oktober bis März Anfahrt nur mit Allradfahrzeug möglich. | Nr. 54 ist in OSM 2x an verschiedenen Stellen eingetragen – vor Ort klären, welche stimmt</t>
         </is>
       </c>
-      <c r="M366" s="3" t="inlineStr">
+      <c r="M366" s="3" t="inlineStr"/>
+      <c r="N366" s="3" t="inlineStr">
         <is>
           <t>n2522182930</t>
         </is>
@@ -20308,7 +20727,8 @@
           <t>Westdeckwerk, Höhe Rüstr. Heim - Anfahrt über Strasse zum Westen - beim Haus am Meer den Fussweg hoch zum Deckwerk - dann links - Achtung : von Oktober bis März ist die Zufahrt gesperrt, dann Anfahrt nur mit Allradfahrzeug möglic</t>
         </is>
       </c>
-      <c r="M367" s="3" t="inlineStr">
+      <c r="M367" s="3" t="inlineStr"/>
+      <c r="N367" s="3" t="inlineStr">
         <is>
           <t>n2522182299</t>
         </is>
@@ -20363,7 +20783,8 @@
           <t>Nr. 54 ist in OSM 2x an verschiedenen Stellen eingetragen – vor Ort klären, welche stimmt</t>
         </is>
       </c>
-      <c r="M368" s="3" t="inlineStr">
+      <c r="M368" s="3" t="inlineStr"/>
+      <c r="N368" s="3" t="inlineStr">
         <is>
           <t>n3716917431</t>
         </is>
@@ -20418,7 +20839,8 @@
           <t>Straße zum Westanleger, Schutzhütte hinter dem Westturm - für alle Fahrzeuge geeignet</t>
         </is>
       </c>
-      <c r="M369" s="3" t="inlineStr">
+      <c r="M369" s="3" t="inlineStr"/>
+      <c r="N369" s="3" t="inlineStr">
         <is>
           <t>n2522183389</t>
         </is>
@@ -20477,7 +20899,8 @@
           <t>Weststrand, auf halber Strecke zwischen Westturm und Anleger - nur mit Allradfahrzeug zu erreichen.</t>
         </is>
       </c>
-      <c r="M370" s="3" t="inlineStr">
+      <c r="M370" s="3" t="inlineStr"/>
+      <c r="N370" s="3" t="inlineStr">
         <is>
           <t>n2522184173</t>
         </is>
@@ -20536,7 +20959,8 @@
           <t>Straße zum Westanleger - auf halber Strecke zum Anleger - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M371" s="3" t="inlineStr">
+      <c r="M371" s="3" t="inlineStr"/>
+      <c r="N371" s="3" t="inlineStr">
         <is>
           <t>n2522183676</t>
         </is>
@@ -20595,7 +21019,8 @@
           <t>Straße zum Anleger, Parkbank kurz vor dem Anleger - für alleFahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M372" s="3" t="inlineStr">
+      <c r="M372" s="3" t="inlineStr"/>
+      <c r="N372" s="3" t="inlineStr">
         <is>
           <t>n2522190681</t>
         </is>
@@ -20650,7 +21075,8 @@
           <t>Straße zum Anleger - rechts vom Eingang Vereinsheim Yachtclub - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M373" s="3" t="inlineStr">
+      <c r="M373" s="3" t="inlineStr"/>
+      <c r="N373" s="3" t="inlineStr">
         <is>
           <t>n2522185157</t>
         </is>
@@ -20705,7 +21131,8 @@
           <t>Westanleger, erster Steg vom Yachthafen - Anfahrt über Strasse zum Westanleger - Achtung : Schlüssel für Tor wird benötigt - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M374" s="3" t="inlineStr">
+      <c r="M374" s="3" t="inlineStr"/>
+      <c r="N374" s="3" t="inlineStr">
         <is>
           <t>n2522184988</t>
         </is>
@@ -20760,7 +21187,8 @@
           <t>Westanleger, bei der Badebucht - Anfahrt über Strasse zum Westanleger - am Ende des Anlegers beim Frachthafen - Achtung : Schlüssel für Tor wird benötigt - für alle Fahrzeuge geeignet.</t>
         </is>
       </c>
-      <c r="M375" s="3" t="inlineStr">
+      <c r="M375" s="3" t="inlineStr"/>
+      <c r="N375" s="3" t="inlineStr">
         <is>
           <t>n2522184915</t>
         </is>
@@ -20811,7 +21239,8 @@
           <t>1334 m²</t>
         </is>
       </c>
-      <c r="M376" s="3" t="inlineStr">
+      <c r="M376" s="3" t="inlineStr"/>
+      <c r="N376" s="3" t="inlineStr">
         <is>
           <t>w135228676</t>
         </is>
@@ -20866,7 +21295,8 @@
           <t>666 m²</t>
         </is>
       </c>
-      <c r="M377" s="3" t="inlineStr">
+      <c r="M377" s="3" t="inlineStr"/>
+      <c r="N377" s="3" t="inlineStr">
         <is>
           <t>w223032308</t>
         </is>
@@ -20917,7 +21347,8 @@
           <t>2112 m²</t>
         </is>
       </c>
-      <c r="M378" s="3" t="inlineStr">
+      <c r="M378" s="3" t="inlineStr"/>
+      <c r="N378" s="3" t="inlineStr">
         <is>
           <t>w117237507</t>
         </is>
@@ -20968,7 +21399,8 @@
           <t>1947 m²</t>
         </is>
       </c>
-      <c r="M379" s="3" t="inlineStr">
+      <c r="M379" s="3" t="inlineStr"/>
+      <c r="N379" s="3" t="inlineStr">
         <is>
           <t>w48648269</t>
         </is>
@@ -21019,7 +21451,8 @@
           <t>1197 m²</t>
         </is>
       </c>
-      <c r="M380" s="3" t="inlineStr">
+      <c r="M380" s="3" t="inlineStr"/>
+      <c r="N380" s="3" t="inlineStr">
         <is>
           <t>w48648253</t>
         </is>
@@ -21070,7 +21503,8 @@
           <t>470 m²</t>
         </is>
       </c>
-      <c r="M381" s="3" t="inlineStr">
+      <c r="M381" s="3" t="inlineStr"/>
+      <c r="N381" s="3" t="inlineStr">
         <is>
           <t>w48648248</t>
         </is>
@@ -21121,7 +21555,8 @@
           <t>972 m²</t>
         </is>
       </c>
-      <c r="M382" s="3" t="inlineStr">
+      <c r="M382" s="3" t="inlineStr"/>
+      <c r="N382" s="3" t="inlineStr">
         <is>
           <t>w139558025</t>
         </is>
@@ -21172,7 +21607,8 @@
           <t>843 m²</t>
         </is>
       </c>
-      <c r="M383" s="3" t="inlineStr">
+      <c r="M383" s="3" t="inlineStr"/>
+      <c r="N383" s="3" t="inlineStr">
         <is>
           <t>w165518796</t>
         </is>
@@ -21224,6 +21660,7 @@
         </is>
       </c>
       <c r="M384" s="3" t="inlineStr"/>
+      <c r="N384" s="3" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
@@ -21271,6 +21708,7 @@
         </is>
       </c>
       <c r="M385" s="3" t="inlineStr"/>
+      <c r="N385" s="3" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="3" t="inlineStr">
@@ -21318,6 +21756,7 @@
         </is>
       </c>
       <c r="M386" s="3" t="inlineStr"/>
+      <c r="N386" s="3" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
@@ -21365,6 +21804,7 @@
         </is>
       </c>
       <c r="M387" s="3" t="inlineStr"/>
+      <c r="N387" s="3" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
@@ -21412,6 +21852,7 @@
         </is>
       </c>
       <c r="M388" s="3" t="inlineStr"/>
+      <c r="N388" s="3" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
@@ -21452,13 +21893,18 @@
       <c r="J389" s="10" t="n">
         <v>5959194.8</v>
       </c>
-      <c r="K389" s="3" t="inlineStr"/>
+      <c r="K389" s="3" t="inlineStr">
+        <is>
+          <t>Ruhezone I/32</t>
+        </is>
+      </c>
       <c r="L389" s="3" t="inlineStr">
         <is>
           <t>Länge 16 m, Höhenunterschied 4.4 m, steiler als 35°</t>
         </is>
       </c>
       <c r="M389" s="3" t="inlineStr"/>
+      <c r="N389" s="3" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
@@ -21506,6 +21952,7 @@
         </is>
       </c>
       <c r="M390" s="3" t="inlineStr"/>
+      <c r="N390" s="3" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
@@ -21553,6 +22000,7 @@
         </is>
       </c>
       <c r="M391" s="3" t="inlineStr"/>
+      <c r="N391" s="3" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="inlineStr">
@@ -21600,6 +22048,7 @@
         </is>
       </c>
       <c r="M392" s="3" t="inlineStr"/>
+      <c r="N392" s="3" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="3" t="inlineStr">
@@ -21647,6 +22096,7 @@
         </is>
       </c>
       <c r="M393" s="3" t="inlineStr"/>
+      <c r="N393" s="3" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="inlineStr">
@@ -21694,6 +22144,7 @@
         </is>
       </c>
       <c r="M394" s="3" t="inlineStr"/>
+      <c r="N394" s="3" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
@@ -21741,6 +22192,7 @@
         </is>
       </c>
       <c r="M395" s="3" t="inlineStr"/>
+      <c r="N395" s="3" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="inlineStr">
@@ -21788,6 +22240,7 @@
         </is>
       </c>
       <c r="M396" s="3" t="inlineStr"/>
+      <c r="N396" s="3" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
@@ -21835,6 +22288,7 @@
         </is>
       </c>
       <c r="M397" s="3" t="inlineStr"/>
+      <c r="N397" s="3" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
@@ -21882,6 +22336,7 @@
         </is>
       </c>
       <c r="M398" s="3" t="inlineStr"/>
+      <c r="N398" s="3" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
@@ -21929,6 +22384,7 @@
         </is>
       </c>
       <c r="M399" s="3" t="inlineStr"/>
+      <c r="N399" s="3" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="3" t="inlineStr">
@@ -21976,6 +22432,7 @@
         </is>
       </c>
       <c r="M400" s="3" t="inlineStr"/>
+      <c r="N400" s="3" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
@@ -22023,6 +22480,7 @@
         </is>
       </c>
       <c r="M401" s="3" t="inlineStr"/>
+      <c r="N401" s="3" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="3" t="inlineStr">
@@ -22070,6 +22528,7 @@
         </is>
       </c>
       <c r="M402" s="3" t="inlineStr"/>
+      <c r="N402" s="3" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
@@ -22117,6 +22576,7 @@
         </is>
       </c>
       <c r="M403" s="3" t="inlineStr"/>
+      <c r="N403" s="3" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="3" t="inlineStr">
@@ -22164,6 +22624,7 @@
         </is>
       </c>
       <c r="M404" s="3" t="inlineStr"/>
+      <c r="N404" s="3" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
@@ -22211,6 +22672,7 @@
         </is>
       </c>
       <c r="M405" s="3" t="inlineStr"/>
+      <c r="N405" s="3" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="3" t="inlineStr">
@@ -22258,6 +22720,7 @@
         </is>
       </c>
       <c r="M406" s="3" t="inlineStr"/>
+      <c r="N406" s="3" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="3" t="inlineStr">
@@ -22305,6 +22768,7 @@
         </is>
       </c>
       <c r="M407" s="3" t="inlineStr"/>
+      <c r="N407" s="3" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
@@ -22352,6 +22816,7 @@
         </is>
       </c>
       <c r="M408" s="3" t="inlineStr"/>
+      <c r="N408" s="3" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
@@ -22399,6 +22864,7 @@
         </is>
       </c>
       <c r="M409" s="3" t="inlineStr"/>
+      <c r="N409" s="3" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
@@ -22446,6 +22912,7 @@
         </is>
       </c>
       <c r="M410" s="3" t="inlineStr"/>
+      <c r="N410" s="3" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
@@ -22493,6 +22960,7 @@
         </is>
       </c>
       <c r="M411" s="3" t="inlineStr"/>
+      <c r="N411" s="3" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
@@ -22540,6 +23008,7 @@
         </is>
       </c>
       <c r="M412" s="3" t="inlineStr"/>
+      <c r="N412" s="3" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
@@ -22587,6 +23056,7 @@
         </is>
       </c>
       <c r="M413" s="3" t="inlineStr"/>
+      <c r="N413" s="3" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="3" t="inlineStr">
@@ -22634,6 +23104,7 @@
         </is>
       </c>
       <c r="M414" s="3" t="inlineStr"/>
+      <c r="N414" s="3" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
@@ -22681,6 +23152,7 @@
         </is>
       </c>
       <c r="M415" s="3" t="inlineStr"/>
+      <c r="N415" s="3" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
@@ -22728,6 +23200,7 @@
         </is>
       </c>
       <c r="M416" s="3" t="inlineStr"/>
+      <c r="N416" s="3" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
@@ -22775,6 +23248,7 @@
         </is>
       </c>
       <c r="M417" s="3" t="inlineStr"/>
+      <c r="N417" s="3" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
@@ -22822,6 +23296,7 @@
         </is>
       </c>
       <c r="M418" s="3" t="inlineStr"/>
+      <c r="N418" s="3" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
@@ -22869,6 +23344,7 @@
         </is>
       </c>
       <c r="M419" s="3" t="inlineStr"/>
+      <c r="N419" s="3" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="3" t="inlineStr">
@@ -22916,6 +23392,7 @@
         </is>
       </c>
       <c r="M420" s="3" t="inlineStr"/>
+      <c r="N420" s="3" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="3" t="inlineStr">
@@ -22963,6 +23440,7 @@
         </is>
       </c>
       <c r="M421" s="3" t="inlineStr"/>
+      <c r="N421" s="3" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="inlineStr">
@@ -23010,6 +23488,7 @@
         </is>
       </c>
       <c r="M422" s="3" t="inlineStr"/>
+      <c r="N422" s="3" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
@@ -23057,6 +23536,7 @@
         </is>
       </c>
       <c r="M423" s="3" t="inlineStr"/>
+      <c r="N423" s="3" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
@@ -23104,6 +23584,7 @@
         </is>
       </c>
       <c r="M424" s="3" t="inlineStr"/>
+      <c r="N424" s="3" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
@@ -23151,6 +23632,7 @@
         </is>
       </c>
       <c r="M425" s="3" t="inlineStr"/>
+      <c r="N425" s="3" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
@@ -23198,6 +23680,7 @@
         </is>
       </c>
       <c r="M426" s="3" t="inlineStr"/>
+      <c r="N426" s="3" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="3" t="inlineStr">
@@ -23245,6 +23728,7 @@
         </is>
       </c>
       <c r="M427" s="3" t="inlineStr"/>
+      <c r="N427" s="3" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="3" t="inlineStr">
@@ -23292,6 +23776,7 @@
         </is>
       </c>
       <c r="M428" s="3" t="inlineStr"/>
+      <c r="N428" s="3" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
@@ -23339,6 +23824,7 @@
         </is>
       </c>
       <c r="M429" s="3" t="inlineStr"/>
+      <c r="N429" s="3" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
@@ -23386,6 +23872,7 @@
         </is>
       </c>
       <c r="M430" s="3" t="inlineStr"/>
+      <c r="N430" s="3" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
@@ -23433,6 +23920,7 @@
         </is>
       </c>
       <c r="M431" s="3" t="inlineStr"/>
+      <c r="N431" s="3" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
@@ -23480,6 +23968,7 @@
         </is>
       </c>
       <c r="M432" s="3" t="inlineStr"/>
+      <c r="N432" s="3" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
@@ -23527,6 +24016,7 @@
         </is>
       </c>
       <c r="M433" s="3" t="inlineStr"/>
+      <c r="N433" s="3" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
@@ -23574,6 +24064,7 @@
         </is>
       </c>
       <c r="M434" s="3" t="inlineStr"/>
+      <c r="N434" s="3" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
@@ -23621,6 +24112,7 @@
         </is>
       </c>
       <c r="M435" s="3" t="inlineStr"/>
+      <c r="N435" s="3" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
@@ -23668,6 +24160,7 @@
         </is>
       </c>
       <c r="M436" s="3" t="inlineStr"/>
+      <c r="N436" s="3" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
@@ -23715,6 +24208,7 @@
         </is>
       </c>
       <c r="M437" s="3" t="inlineStr"/>
+      <c r="N437" s="3" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="inlineStr">
@@ -23762,6 +24256,7 @@
         </is>
       </c>
       <c r="M438" s="3" t="inlineStr"/>
+      <c r="N438" s="3" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
@@ -23809,6 +24304,7 @@
         </is>
       </c>
       <c r="M439" s="3" t="inlineStr"/>
+      <c r="N439" s="3" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
@@ -23856,6 +24352,7 @@
         </is>
       </c>
       <c r="M440" s="3" t="inlineStr"/>
+      <c r="N440" s="3" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
@@ -23903,6 +24400,7 @@
         </is>
       </c>
       <c r="M441" s="3" t="inlineStr"/>
+      <c r="N441" s="3" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="3" t="inlineStr">
@@ -23950,6 +24448,7 @@
         </is>
       </c>
       <c r="M442" s="3" t="inlineStr"/>
+      <c r="N442" s="3" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
@@ -23997,6 +24496,7 @@
         </is>
       </c>
       <c r="M443" s="3" t="inlineStr"/>
+      <c r="N443" s="3" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
@@ -24044,6 +24544,7 @@
         </is>
       </c>
       <c r="M444" s="3" t="inlineStr"/>
+      <c r="N444" s="3" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
@@ -24091,6 +24592,7 @@
         </is>
       </c>
       <c r="M445" s="3" t="inlineStr"/>
+      <c r="N445" s="3" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
@@ -24138,6 +24640,7 @@
         </is>
       </c>
       <c r="M446" s="3" t="inlineStr"/>
+      <c r="N446" s="3" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
@@ -24185,6 +24688,7 @@
         </is>
       </c>
       <c r="M447" s="3" t="inlineStr"/>
+      <c r="N447" s="3" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
@@ -24232,6 +24736,7 @@
         </is>
       </c>
       <c r="M448" s="3" t="inlineStr"/>
+      <c r="N448" s="3" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
@@ -24279,6 +24784,7 @@
         </is>
       </c>
       <c r="M449" s="3" t="inlineStr"/>
+      <c r="N449" s="3" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
@@ -24326,6 +24832,7 @@
         </is>
       </c>
       <c r="M450" s="3" t="inlineStr"/>
+      <c r="N450" s="3" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
@@ -24373,6 +24880,7 @@
         </is>
       </c>
       <c r="M451" s="3" t="inlineStr"/>
+      <c r="N451" s="3" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
@@ -24420,6 +24928,7 @@
         </is>
       </c>
       <c r="M452" s="3" t="inlineStr"/>
+      <c r="N452" s="3" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
@@ -24467,6 +24976,7 @@
         </is>
       </c>
       <c r="M453" s="3" t="inlineStr"/>
+      <c r="N453" s="3" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
@@ -24514,6 +25024,7 @@
         </is>
       </c>
       <c r="M454" s="3" t="inlineStr"/>
+      <c r="N454" s="3" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
@@ -24561,6 +25072,7 @@
         </is>
       </c>
       <c r="M455" s="3" t="inlineStr"/>
+      <c r="N455" s="3" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="3" t="inlineStr">
@@ -24608,6 +25120,7 @@
         </is>
       </c>
       <c r="M456" s="3" t="inlineStr"/>
+      <c r="N456" s="3" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
@@ -24655,6 +25168,7 @@
         </is>
       </c>
       <c r="M457" s="3" t="inlineStr"/>
+      <c r="N457" s="3" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
@@ -24702,6 +25216,7 @@
         </is>
       </c>
       <c r="M458" s="3" t="inlineStr"/>
+      <c r="N458" s="3" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
@@ -24749,6 +25264,7 @@
         </is>
       </c>
       <c r="M459" s="3" t="inlineStr"/>
+      <c r="N459" s="3" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
@@ -24796,6 +25312,7 @@
         </is>
       </c>
       <c r="M460" s="3" t="inlineStr"/>
+      <c r="N460" s="3" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
@@ -24843,6 +25360,7 @@
         </is>
       </c>
       <c r="M461" s="3" t="inlineStr"/>
+      <c r="N461" s="3" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
@@ -24890,6 +25408,7 @@
         </is>
       </c>
       <c r="M462" s="3" t="inlineStr"/>
+      <c r="N462" s="3" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="3" t="inlineStr">
@@ -24937,6 +25456,7 @@
         </is>
       </c>
       <c r="M463" s="3" t="inlineStr"/>
+      <c r="N463" s="3" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
@@ -24984,6 +25504,7 @@
         </is>
       </c>
       <c r="M464" s="3" t="inlineStr"/>
+      <c r="N464" s="3" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
@@ -25031,6 +25552,7 @@
         </is>
       </c>
       <c r="M465" s="3" t="inlineStr"/>
+      <c r="N465" s="3" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
@@ -25078,6 +25600,7 @@
         </is>
       </c>
       <c r="M466" s="3" t="inlineStr"/>
+      <c r="N466" s="3" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
@@ -25125,6 +25648,7 @@
         </is>
       </c>
       <c r="M467" s="3" t="inlineStr"/>
+      <c r="N467" s="3" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
@@ -25172,6 +25696,7 @@
         </is>
       </c>
       <c r="M468" s="3" t="inlineStr"/>
+      <c r="N468" s="3" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
@@ -25219,6 +25744,7 @@
         </is>
       </c>
       <c r="M469" s="3" t="inlineStr"/>
+      <c r="N469" s="3" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="3" t="inlineStr">
@@ -25266,6 +25792,7 @@
         </is>
       </c>
       <c r="M470" s="3" t="inlineStr"/>
+      <c r="N470" s="3" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
@@ -25313,6 +25840,7 @@
         </is>
       </c>
       <c r="M471" s="3" t="inlineStr"/>
+      <c r="N471" s="3" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
@@ -25360,6 +25888,7 @@
         </is>
       </c>
       <c r="M472" s="3" t="inlineStr"/>
+      <c r="N472" s="3" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
@@ -25407,6 +25936,7 @@
         </is>
       </c>
       <c r="M473" s="3" t="inlineStr"/>
+      <c r="N473" s="3" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
@@ -25454,6 +25984,7 @@
         </is>
       </c>
       <c r="M474" s="3" t="inlineStr"/>
+      <c r="N474" s="3" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
@@ -25501,6 +26032,7 @@
         </is>
       </c>
       <c r="M475" s="3" t="inlineStr"/>
+      <c r="N475" s="3" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
@@ -25548,6 +26080,7 @@
         </is>
       </c>
       <c r="M476" s="3" t="inlineStr"/>
+      <c r="N476" s="3" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="3" t="inlineStr">
@@ -25595,6 +26128,7 @@
         </is>
       </c>
       <c r="M477" s="3" t="inlineStr"/>
+      <c r="N477" s="3" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
@@ -25642,6 +26176,7 @@
         </is>
       </c>
       <c r="M478" s="3" t="inlineStr"/>
+      <c r="N478" s="3" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
@@ -25689,6 +26224,7 @@
         </is>
       </c>
       <c r="M479" s="3" t="inlineStr"/>
+      <c r="N479" s="3" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
@@ -25736,6 +26272,7 @@
         </is>
       </c>
       <c r="M480" s="3" t="inlineStr"/>
+      <c r="N480" s="3" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
@@ -25783,6 +26320,7 @@
         </is>
       </c>
       <c r="M481" s="3" t="inlineStr"/>
+      <c r="N481" s="3" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
@@ -25830,6 +26368,7 @@
         </is>
       </c>
       <c r="M482" s="3" t="inlineStr"/>
+      <c r="N482" s="3" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
@@ -25877,6 +26416,7 @@
         </is>
       </c>
       <c r="M483" s="3" t="inlineStr"/>
+      <c r="N483" s="3" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="3" t="inlineStr">
@@ -25924,6 +26464,7 @@
         </is>
       </c>
       <c r="M484" s="3" t="inlineStr"/>
+      <c r="N484" s="3" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
@@ -25971,6 +26512,7 @@
         </is>
       </c>
       <c r="M485" s="3" t="inlineStr"/>
+      <c r="N485" s="3" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
@@ -26018,6 +26560,7 @@
         </is>
       </c>
       <c r="M486" s="3" t="inlineStr"/>
+      <c r="N486" s="3" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
@@ -26065,6 +26608,7 @@
         </is>
       </c>
       <c r="M487" s="3" t="inlineStr"/>
+      <c r="N487" s="3" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
@@ -26112,6 +26656,7 @@
         </is>
       </c>
       <c r="M488" s="3" t="inlineStr"/>
+      <c r="N488" s="3" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
@@ -26159,6 +26704,7 @@
         </is>
       </c>
       <c r="M489" s="3" t="inlineStr"/>
+      <c r="N489" s="3" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
@@ -26206,6 +26752,7 @@
         </is>
       </c>
       <c r="M490" s="3" t="inlineStr"/>
+      <c r="N490" s="3" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
@@ -26253,6 +26800,7 @@
         </is>
       </c>
       <c r="M491" s="3" t="inlineStr"/>
+      <c r="N491" s="3" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
@@ -26300,6 +26848,7 @@
         </is>
       </c>
       <c r="M492" s="3" t="inlineStr"/>
+      <c r="N492" s="3" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
@@ -26347,6 +26896,7 @@
         </is>
       </c>
       <c r="M493" s="3" t="inlineStr"/>
+      <c r="N493" s="3" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
@@ -26394,6 +26944,7 @@
         </is>
       </c>
       <c r="M494" s="3" t="inlineStr"/>
+      <c r="N494" s="3" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
@@ -26441,6 +26992,7 @@
         </is>
       </c>
       <c r="M495" s="3" t="inlineStr"/>
+      <c r="N495" s="3" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
@@ -26488,6 +27040,7 @@
         </is>
       </c>
       <c r="M496" s="3" t="inlineStr"/>
+      <c r="N496" s="3" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
@@ -26535,6 +27088,7 @@
         </is>
       </c>
       <c r="M497" s="3" t="inlineStr"/>
+      <c r="N497" s="3" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
@@ -26582,6 +27136,7 @@
         </is>
       </c>
       <c r="M498" s="3" t="inlineStr"/>
+      <c r="N498" s="3" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
@@ -26629,6 +27184,7 @@
         </is>
       </c>
       <c r="M499" s="3" t="inlineStr"/>
+      <c r="N499" s="3" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
@@ -26676,6 +27232,7 @@
         </is>
       </c>
       <c r="M500" s="3" t="inlineStr"/>
+      <c r="N500" s="3" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
@@ -26723,6 +27280,7 @@
         </is>
       </c>
       <c r="M501" s="3" t="inlineStr"/>
+      <c r="N501" s="3" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
@@ -26770,6 +27328,7 @@
         </is>
       </c>
       <c r="M502" s="3" t="inlineStr"/>
+      <c r="N502" s="3" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
@@ -26817,6 +27376,7 @@
         </is>
       </c>
       <c r="M503" s="3" t="inlineStr"/>
+      <c r="N503" s="3" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
@@ -26864,6 +27424,7 @@
         </is>
       </c>
       <c r="M504" s="3" t="inlineStr"/>
+      <c r="N504" s="3" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
@@ -26911,6 +27472,7 @@
         </is>
       </c>
       <c r="M505" s="3" t="inlineStr"/>
+      <c r="N505" s="3" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
@@ -26958,6 +27520,7 @@
         </is>
       </c>
       <c r="M506" s="3" t="inlineStr"/>
+      <c r="N506" s="3" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
@@ -27005,6 +27568,7 @@
         </is>
       </c>
       <c r="M507" s="3" t="inlineStr"/>
+      <c r="N507" s="3" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
@@ -27052,6 +27616,7 @@
         </is>
       </c>
       <c r="M508" s="3" t="inlineStr"/>
+      <c r="N508" s="3" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
@@ -27099,6 +27664,7 @@
         </is>
       </c>
       <c r="M509" s="3" t="inlineStr"/>
+      <c r="N509" s="3" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
@@ -27146,6 +27712,7 @@
         </is>
       </c>
       <c r="M510" s="3" t="inlineStr"/>
+      <c r="N510" s="3" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
@@ -27193,6 +27760,7 @@
         </is>
       </c>
       <c r="M511" s="3" t="inlineStr"/>
+      <c r="N511" s="3" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="3" t="inlineStr">
@@ -27240,6 +27808,7 @@
         </is>
       </c>
       <c r="M512" s="3" t="inlineStr"/>
+      <c r="N512" s="3" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
@@ -27287,6 +27856,7 @@
         </is>
       </c>
       <c r="M513" s="3" t="inlineStr"/>
+      <c r="N513" s="3" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
@@ -27334,6 +27904,7 @@
         </is>
       </c>
       <c r="M514" s="3" t="inlineStr"/>
+      <c r="N514" s="3" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
@@ -27381,6 +27952,7 @@
         </is>
       </c>
       <c r="M515" s="3" t="inlineStr"/>
+      <c r="N515" s="3" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
@@ -27428,6 +28000,7 @@
         </is>
       </c>
       <c r="M516" s="3" t="inlineStr"/>
+      <c r="N516" s="3" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
@@ -27475,6 +28048,7 @@
         </is>
       </c>
       <c r="M517" s="3" t="inlineStr"/>
+      <c r="N517" s="3" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="3" t="inlineStr">
@@ -27522,6 +28096,7 @@
         </is>
       </c>
       <c r="M518" s="3" t="inlineStr"/>
+      <c r="N518" s="3" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="3" t="inlineStr">
@@ -27569,6 +28144,7 @@
         </is>
       </c>
       <c r="M519" s="3" t="inlineStr"/>
+      <c r="N519" s="3" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="3" t="inlineStr">
@@ -27616,6 +28192,7 @@
         </is>
       </c>
       <c r="M520" s="3" t="inlineStr"/>
+      <c r="N520" s="3" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
@@ -27663,6 +28240,7 @@
         </is>
       </c>
       <c r="M521" s="3" t="inlineStr"/>
+      <c r="N521" s="3" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
@@ -27710,6 +28288,7 @@
         </is>
       </c>
       <c r="M522" s="3" t="inlineStr"/>
+      <c r="N522" s="3" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
@@ -27757,6 +28336,7 @@
         </is>
       </c>
       <c r="M523" s="3" t="inlineStr"/>
+      <c r="N523" s="3" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
@@ -27804,6 +28384,7 @@
         </is>
       </c>
       <c r="M524" s="3" t="inlineStr"/>
+      <c r="N524" s="3" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="3" t="inlineStr">
@@ -27851,6 +28432,7 @@
         </is>
       </c>
       <c r="M525" s="3" t="inlineStr"/>
+      <c r="N525" s="3" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
@@ -27898,6 +28480,7 @@
         </is>
       </c>
       <c r="M526" s="3" t="inlineStr"/>
+      <c r="N526" s="3" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
@@ -27945,6 +28528,7 @@
         </is>
       </c>
       <c r="M527" s="3" t="inlineStr"/>
+      <c r="N527" s="3" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
@@ -27992,6 +28576,7 @@
         </is>
       </c>
       <c r="M528" s="3" t="inlineStr"/>
+      <c r="N528" s="3" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
@@ -28039,6 +28624,7 @@
         </is>
       </c>
       <c r="M529" s="3" t="inlineStr"/>
+      <c r="N529" s="3" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
@@ -28086,6 +28672,7 @@
         </is>
       </c>
       <c r="M530" s="3" t="inlineStr"/>
+      <c r="N530" s="3" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
@@ -28133,6 +28720,7 @@
         </is>
       </c>
       <c r="M531" s="3" t="inlineStr"/>
+      <c r="N531" s="3" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="3" t="inlineStr">
@@ -28180,6 +28768,7 @@
         </is>
       </c>
       <c r="M532" s="3" t="inlineStr"/>
+      <c r="N532" s="3" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="3" t="inlineStr">
@@ -28227,6 +28816,7 @@
         </is>
       </c>
       <c r="M533" s="3" t="inlineStr"/>
+      <c r="N533" s="3" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="3" t="inlineStr">
@@ -28274,6 +28864,7 @@
         </is>
       </c>
       <c r="M534" s="3" t="inlineStr"/>
+      <c r="N534" s="3" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="3" t="inlineStr">
@@ -28321,6 +28912,7 @@
         </is>
       </c>
       <c r="M535" s="3" t="inlineStr"/>
+      <c r="N535" s="3" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="3" t="inlineStr">
@@ -28368,6 +28960,7 @@
         </is>
       </c>
       <c r="M536" s="3" t="inlineStr"/>
+      <c r="N536" s="3" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="3" t="inlineStr">
@@ -28415,6 +29008,7 @@
         </is>
       </c>
       <c r="M537" s="3" t="inlineStr"/>
+      <c r="N537" s="3" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="3" t="inlineStr">
@@ -28462,6 +29056,7 @@
         </is>
       </c>
       <c r="M538" s="3" t="inlineStr"/>
+      <c r="N538" s="3" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="3" t="inlineStr">
@@ -28509,6 +29104,7 @@
         </is>
       </c>
       <c r="M539" s="3" t="inlineStr"/>
+      <c r="N539" s="3" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="3" t="inlineStr">
@@ -28556,6 +29152,7 @@
         </is>
       </c>
       <c r="M540" s="3" t="inlineStr"/>
+      <c r="N540" s="3" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="3" t="inlineStr">
@@ -28603,6 +29200,7 @@
         </is>
       </c>
       <c r="M541" s="3" t="inlineStr"/>
+      <c r="N541" s="3" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="3" t="inlineStr">
@@ -28650,6 +29248,7 @@
         </is>
       </c>
       <c r="M542" s="3" t="inlineStr"/>
+      <c r="N542" s="3" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="3" t="inlineStr">
@@ -28697,6 +29296,7 @@
         </is>
       </c>
       <c r="M543" s="3" t="inlineStr"/>
+      <c r="N543" s="3" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="3" t="inlineStr">
@@ -28744,6 +29344,7 @@
         </is>
       </c>
       <c r="M544" s="3" t="inlineStr"/>
+      <c r="N544" s="3" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="3" t="inlineStr">
@@ -28791,6 +29392,7 @@
         </is>
       </c>
       <c r="M545" s="3" t="inlineStr"/>
+      <c r="N545" s="3" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="3" t="inlineStr">
@@ -28838,6 +29440,7 @@
         </is>
       </c>
       <c r="M546" s="3" t="inlineStr"/>
+      <c r="N546" s="3" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="3" t="inlineStr">
@@ -28885,6 +29488,7 @@
         </is>
       </c>
       <c r="M547" s="3" t="inlineStr"/>
+      <c r="N547" s="3" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="3" t="inlineStr">
@@ -28932,6 +29536,7 @@
         </is>
       </c>
       <c r="M548" s="3" t="inlineStr"/>
+      <c r="N548" s="3" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="3" t="inlineStr">
@@ -28979,6 +29584,7 @@
         </is>
       </c>
       <c r="M549" s="3" t="inlineStr"/>
+      <c r="N549" s="3" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="3" t="inlineStr">
@@ -29026,6 +29632,7 @@
         </is>
       </c>
       <c r="M550" s="3" t="inlineStr"/>
+      <c r="N550" s="3" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="3" t="inlineStr">
@@ -29073,6 +29680,7 @@
         </is>
       </c>
       <c r="M551" s="3" t="inlineStr"/>
+      <c r="N551" s="3" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="3" t="inlineStr">
@@ -29120,6 +29728,7 @@
         </is>
       </c>
       <c r="M552" s="3" t="inlineStr"/>
+      <c r="N552" s="3" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="3" t="inlineStr">
@@ -29167,6 +29776,7 @@
         </is>
       </c>
       <c r="M553" s="3" t="inlineStr"/>
+      <c r="N553" s="3" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="3" t="inlineStr">
@@ -29214,6 +29824,7 @@
         </is>
       </c>
       <c r="M554" s="3" t="inlineStr"/>
+      <c r="N554" s="3" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="3" t="inlineStr">
@@ -29261,6 +29872,7 @@
         </is>
       </c>
       <c r="M555" s="3" t="inlineStr"/>
+      <c r="N555" s="3" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="3" t="inlineStr">
@@ -29308,6 +29920,7 @@
         </is>
       </c>
       <c r="M556" s="3" t="inlineStr"/>
+      <c r="N556" s="3" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="3" t="inlineStr">
@@ -29355,6 +29968,7 @@
         </is>
       </c>
       <c r="M557" s="3" t="inlineStr"/>
+      <c r="N557" s="3" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="3" t="inlineStr">
@@ -29402,6 +30016,7 @@
         </is>
       </c>
       <c r="M558" s="3" t="inlineStr"/>
+      <c r="N558" s="3" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="3" t="inlineStr">
@@ -29449,6 +30064,7 @@
         </is>
       </c>
       <c r="M559" s="3" t="inlineStr"/>
+      <c r="N559" s="3" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="3" t="inlineStr">
@@ -29496,6 +30112,7 @@
         </is>
       </c>
       <c r="M560" s="3" t="inlineStr"/>
+      <c r="N560" s="3" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="3" t="inlineStr">
@@ -29543,6 +30160,7 @@
         </is>
       </c>
       <c r="M561" s="3" t="inlineStr"/>
+      <c r="N561" s="3" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="3" t="inlineStr">
@@ -29590,6 +30208,7 @@
         </is>
       </c>
       <c r="M562" s="3" t="inlineStr"/>
+      <c r="N562" s="3" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="3" t="inlineStr">
@@ -29637,6 +30256,7 @@
         </is>
       </c>
       <c r="M563" s="3" t="inlineStr"/>
+      <c r="N563" s="3" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="3" t="inlineStr">
@@ -29684,6 +30304,7 @@
         </is>
       </c>
       <c r="M564" s="3" t="inlineStr"/>
+      <c r="N564" s="3" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="3" t="inlineStr">
@@ -29731,6 +30352,7 @@
         </is>
       </c>
       <c r="M565" s="3" t="inlineStr"/>
+      <c r="N565" s="3" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="3" t="inlineStr">
@@ -29778,6 +30400,7 @@
         </is>
       </c>
       <c r="M566" s="3" t="inlineStr"/>
+      <c r="N566" s="3" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="3" t="inlineStr">
@@ -29825,6 +30448,7 @@
         </is>
       </c>
       <c r="M567" s="3" t="inlineStr"/>
+      <c r="N567" s="3" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="3" t="inlineStr">
@@ -29872,6 +30496,7 @@
         </is>
       </c>
       <c r="M568" s="3" t="inlineStr"/>
+      <c r="N568" s="3" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="3" t="inlineStr">
@@ -29919,6 +30544,7 @@
         </is>
       </c>
       <c r="M569" s="3" t="inlineStr"/>
+      <c r="N569" s="3" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="3" t="inlineStr">
@@ -29966,6 +30592,7 @@
         </is>
       </c>
       <c r="M570" s="3" t="inlineStr"/>
+      <c r="N570" s="3" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="3" t="inlineStr">
@@ -30013,6 +30640,7 @@
         </is>
       </c>
       <c r="M571" s="3" t="inlineStr"/>
+      <c r="N571" s="3" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="3" t="inlineStr">
@@ -30060,6 +30688,7 @@
         </is>
       </c>
       <c r="M572" s="3" t="inlineStr"/>
+      <c r="N572" s="3" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="3" t="inlineStr">
@@ -30107,6 +30736,7 @@
         </is>
       </c>
       <c r="M573" s="3" t="inlineStr"/>
+      <c r="N573" s="3" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="3" t="inlineStr">
@@ -30154,6 +30784,7 @@
         </is>
       </c>
       <c r="M574" s="3" t="inlineStr"/>
+      <c r="N574" s="3" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="3" t="inlineStr">
@@ -30201,6 +30832,7 @@
         </is>
       </c>
       <c r="M575" s="3" t="inlineStr"/>
+      <c r="N575" s="3" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="3" t="inlineStr">
@@ -30248,6 +30880,7 @@
         </is>
       </c>
       <c r="M576" s="3" t="inlineStr"/>
+      <c r="N576" s="3" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="3" t="inlineStr">
@@ -30295,6 +30928,7 @@
         </is>
       </c>
       <c r="M577" s="3" t="inlineStr"/>
+      <c r="N577" s="3" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="3" t="inlineStr">
@@ -30342,6 +30976,7 @@
         </is>
       </c>
       <c r="M578" s="3" t="inlineStr"/>
+      <c r="N578" s="3" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" s="3" t="inlineStr">
@@ -30389,6 +31024,7 @@
         </is>
       </c>
       <c r="M579" s="3" t="inlineStr"/>
+      <c r="N579" s="3" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="3" t="inlineStr">
@@ -30436,6 +31072,7 @@
         </is>
       </c>
       <c r="M580" s="3" t="inlineStr"/>
+      <c r="N580" s="3" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" s="3" t="inlineStr">
@@ -30483,6 +31120,7 @@
         </is>
       </c>
       <c r="M581" s="3" t="inlineStr"/>
+      <c r="N581" s="3" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="3" t="inlineStr">
@@ -30530,6 +31168,7 @@
         </is>
       </c>
       <c r="M582" s="3" t="inlineStr"/>
+      <c r="N582" s="3" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="3" t="inlineStr">
@@ -30577,6 +31216,7 @@
         </is>
       </c>
       <c r="M583" s="3" t="inlineStr"/>
+      <c r="N583" s="3" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="3" t="inlineStr">
@@ -30624,6 +31264,7 @@
         </is>
       </c>
       <c r="M584" s="3" t="inlineStr"/>
+      <c r="N584" s="3" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="3" t="inlineStr">
@@ -30671,6 +31312,7 @@
         </is>
       </c>
       <c r="M585" s="3" t="inlineStr"/>
+      <c r="N585" s="3" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="3" t="inlineStr">
@@ -30718,6 +31360,7 @@
         </is>
       </c>
       <c r="M586" s="3" t="inlineStr"/>
+      <c r="N586" s="3" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="3" t="inlineStr">
@@ -30765,6 +31408,7 @@
         </is>
       </c>
       <c r="M587" s="3" t="inlineStr"/>
+      <c r="N587" s="3" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="3" t="inlineStr">
@@ -30812,6 +31456,7 @@
         </is>
       </c>
       <c r="M588" s="3" t="inlineStr"/>
+      <c r="N588" s="3" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="3" t="inlineStr">
@@ -30859,6 +31504,7 @@
         </is>
       </c>
       <c r="M589" s="3" t="inlineStr"/>
+      <c r="N589" s="3" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="3" t="inlineStr">
@@ -30906,6 +31552,7 @@
         </is>
       </c>
       <c r="M590" s="3" t="inlineStr"/>
+      <c r="N590" s="3" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="3" t="inlineStr">
@@ -30953,6 +31600,7 @@
         </is>
       </c>
       <c r="M591" s="3" t="inlineStr"/>
+      <c r="N591" s="3" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="3" t="inlineStr">
@@ -31000,6 +31648,7 @@
         </is>
       </c>
       <c r="M592" s="3" t="inlineStr"/>
+      <c r="N592" s="3" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="3" t="inlineStr">
@@ -31047,6 +31696,7 @@
         </is>
       </c>
       <c r="M593" s="3" t="inlineStr"/>
+      <c r="N593" s="3" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="3" t="inlineStr">
@@ -31094,6 +31744,7 @@
         </is>
       </c>
       <c r="M594" s="3" t="inlineStr"/>
+      <c r="N594" s="3" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="3" t="inlineStr">
@@ -31141,6 +31792,7 @@
         </is>
       </c>
       <c r="M595" s="3" t="inlineStr"/>
+      <c r="N595" s="3" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="3" t="inlineStr">
@@ -31188,6 +31840,7 @@
         </is>
       </c>
       <c r="M596" s="3" t="inlineStr"/>
+      <c r="N596" s="3" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="3" t="inlineStr">
@@ -31235,6 +31888,7 @@
         </is>
       </c>
       <c r="M597" s="3" t="inlineStr"/>
+      <c r="N597" s="3" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="3" t="inlineStr">
@@ -31282,6 +31936,7 @@
         </is>
       </c>
       <c r="M598" s="3" t="inlineStr"/>
+      <c r="N598" s="3" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="3" t="inlineStr">
@@ -31329,6 +31984,7 @@
         </is>
       </c>
       <c r="M599" s="3" t="inlineStr"/>
+      <c r="N599" s="3" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="3" t="inlineStr">
@@ -31376,6 +32032,7 @@
         </is>
       </c>
       <c r="M600" s="3" t="inlineStr"/>
+      <c r="N600" s="3" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="3" t="inlineStr">
@@ -31423,6 +32080,7 @@
         </is>
       </c>
       <c r="M601" s="3" t="inlineStr"/>
+      <c r="N601" s="3" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="3" t="inlineStr">
@@ -31470,6 +32128,7 @@
         </is>
       </c>
       <c r="M602" s="3" t="inlineStr"/>
+      <c r="N602" s="3" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="3" t="inlineStr">
@@ -31517,6 +32176,7 @@
         </is>
       </c>
       <c r="M603" s="3" t="inlineStr"/>
+      <c r="N603" s="3" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="3" t="inlineStr">
@@ -31564,6 +32224,7 @@
         </is>
       </c>
       <c r="M604" s="3" t="inlineStr"/>
+      <c r="N604" s="3" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="3" t="inlineStr">
@@ -31611,6 +32272,7 @@
         </is>
       </c>
       <c r="M605" s="3" t="inlineStr"/>
+      <c r="N605" s="3" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="3" t="inlineStr">
@@ -31658,6 +32320,7 @@
         </is>
       </c>
       <c r="M606" s="3" t="inlineStr"/>
+      <c r="N606" s="3" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="3" t="inlineStr">
@@ -31705,6 +32368,7 @@
         </is>
       </c>
       <c r="M607" s="3" t="inlineStr"/>
+      <c r="N607" s="3" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="3" t="inlineStr">
@@ -31752,6 +32416,7 @@
         </is>
       </c>
       <c r="M608" s="3" t="inlineStr"/>
+      <c r="N608" s="3" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="3" t="inlineStr">
@@ -31799,6 +32464,7 @@
         </is>
       </c>
       <c r="M609" s="3" t="inlineStr"/>
+      <c r="N609" s="3" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="3" t="inlineStr">
@@ -31846,6 +32512,7 @@
         </is>
       </c>
       <c r="M610" s="3" t="inlineStr"/>
+      <c r="N610" s="3" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="3" t="inlineStr">
@@ -31893,6 +32560,7 @@
         </is>
       </c>
       <c r="M611" s="3" t="inlineStr"/>
+      <c r="N611" s="3" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" s="3" t="inlineStr">
@@ -31940,6 +32608,7 @@
         </is>
       </c>
       <c r="M612" s="3" t="inlineStr"/>
+      <c r="N612" s="3" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" s="3" t="inlineStr">
@@ -31987,6 +32656,7 @@
         </is>
       </c>
       <c r="M613" s="3" t="inlineStr"/>
+      <c r="N613" s="3" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="3" t="inlineStr">
@@ -32037,7 +32707,8 @@
           <t>Ø 15.0 m, Tiefe 0.83 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M614" s="3" t="inlineStr">
+      <c r="M614" s="3" t="inlineStr"/>
+      <c r="N614" s="3" t="inlineStr">
         <is>
           <t>w136072920</t>
         </is>
@@ -32093,6 +32764,7 @@
         </is>
       </c>
       <c r="M615" s="3" t="inlineStr"/>
+      <c r="N615" s="3" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" s="3" t="inlineStr">
@@ -32140,6 +32812,7 @@
         </is>
       </c>
       <c r="M616" s="3" t="inlineStr"/>
+      <c r="N616" s="3" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" s="3" t="inlineStr">
@@ -32187,6 +32860,7 @@
         </is>
       </c>
       <c r="M617" s="3" t="inlineStr"/>
+      <c r="N617" s="3" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="3" t="inlineStr">
@@ -32234,6 +32908,7 @@
         </is>
       </c>
       <c r="M618" s="3" t="inlineStr"/>
+      <c r="N618" s="3" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" s="3" t="inlineStr">
@@ -32281,6 +32956,7 @@
         </is>
       </c>
       <c r="M619" s="3" t="inlineStr"/>
+      <c r="N619" s="3" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" s="3" t="inlineStr">
@@ -32328,6 +33004,7 @@
         </is>
       </c>
       <c r="M620" s="3" t="inlineStr"/>
+      <c r="N620" s="3" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" s="3" t="inlineStr">
@@ -32375,6 +33052,7 @@
         </is>
       </c>
       <c r="M621" s="3" t="inlineStr"/>
+      <c r="N621" s="3" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" s="3" t="inlineStr">
@@ -32422,6 +33100,7 @@
         </is>
       </c>
       <c r="M622" s="3" t="inlineStr"/>
+      <c r="N622" s="3" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" s="3" t="inlineStr">
@@ -32469,6 +33148,7 @@
         </is>
       </c>
       <c r="M623" s="3" t="inlineStr"/>
+      <c r="N623" s="3" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="3" t="inlineStr">
@@ -32516,6 +33196,7 @@
         </is>
       </c>
       <c r="M624" s="3" t="inlineStr"/>
+      <c r="N624" s="3" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" s="3" t="inlineStr">
@@ -32563,6 +33244,7 @@
         </is>
       </c>
       <c r="M625" s="3" t="inlineStr"/>
+      <c r="N625" s="3" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" s="3" t="inlineStr">
@@ -32610,6 +33292,7 @@
         </is>
       </c>
       <c r="M626" s="3" t="inlineStr"/>
+      <c r="N626" s="3" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" s="3" t="inlineStr">
@@ -32657,6 +33340,7 @@
         </is>
       </c>
       <c r="M627" s="3" t="inlineStr"/>
+      <c r="N627" s="3" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" s="3" t="inlineStr">
@@ -32704,6 +33388,7 @@
         </is>
       </c>
       <c r="M628" s="3" t="inlineStr"/>
+      <c r="N628" s="3" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" s="3" t="inlineStr">
@@ -32751,6 +33436,7 @@
         </is>
       </c>
       <c r="M629" s="3" t="inlineStr"/>
+      <c r="N629" s="3" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" s="3" t="inlineStr">
@@ -32798,6 +33484,7 @@
         </is>
       </c>
       <c r="M630" s="3" t="inlineStr"/>
+      <c r="N630" s="3" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" s="3" t="inlineStr">
@@ -32845,6 +33532,7 @@
         </is>
       </c>
       <c r="M631" s="3" t="inlineStr"/>
+      <c r="N631" s="3" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" s="3" t="inlineStr">
@@ -32892,6 +33580,7 @@
         </is>
       </c>
       <c r="M632" s="3" t="inlineStr"/>
+      <c r="N632" s="3" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" s="3" t="inlineStr">
@@ -32939,6 +33628,7 @@
         </is>
       </c>
       <c r="M633" s="3" t="inlineStr"/>
+      <c r="N633" s="3" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" s="3" t="inlineStr">
@@ -32986,6 +33676,7 @@
         </is>
       </c>
       <c r="M634" s="3" t="inlineStr"/>
+      <c r="N634" s="3" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" s="3" t="inlineStr">
@@ -33033,6 +33724,7 @@
         </is>
       </c>
       <c r="M635" s="3" t="inlineStr"/>
+      <c r="N635" s="3" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" s="3" t="inlineStr">
@@ -33080,6 +33772,7 @@
         </is>
       </c>
       <c r="M636" s="3" t="inlineStr"/>
+      <c r="N636" s="3" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" s="3" t="inlineStr">
@@ -33127,6 +33820,7 @@
         </is>
       </c>
       <c r="M637" s="3" t="inlineStr"/>
+      <c r="N637" s="3" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" s="3" t="inlineStr">
@@ -33174,6 +33868,7 @@
         </is>
       </c>
       <c r="M638" s="3" t="inlineStr"/>
+      <c r="N638" s="3" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" s="3" t="inlineStr">
@@ -33221,6 +33916,7 @@
         </is>
       </c>
       <c r="M639" s="3" t="inlineStr"/>
+      <c r="N639" s="3" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" s="3" t="inlineStr">
@@ -33268,6 +33964,7 @@
         </is>
       </c>
       <c r="M640" s="3" t="inlineStr"/>
+      <c r="N640" s="3" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" s="3" t="inlineStr">
@@ -33315,6 +34012,7 @@
         </is>
       </c>
       <c r="M641" s="3" t="inlineStr"/>
+      <c r="N641" s="3" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" s="3" t="inlineStr">
@@ -33362,6 +34060,7 @@
         </is>
       </c>
       <c r="M642" s="3" t="inlineStr"/>
+      <c r="N642" s="3" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" s="3" t="inlineStr">
@@ -33408,7 +34107,8 @@
           <t>Ø 18.5 m, Tiefe 0.96 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M643" s="3" t="inlineStr">
+      <c r="M643" s="3" t="inlineStr"/>
+      <c r="N643" s="3" t="inlineStr">
         <is>
           <t>w377900236</t>
         </is>
@@ -33460,6 +34160,7 @@
         </is>
       </c>
       <c r="M644" s="3" t="inlineStr"/>
+      <c r="N644" s="3" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" s="3" t="inlineStr">
@@ -33507,6 +34208,7 @@
         </is>
       </c>
       <c r="M645" s="3" t="inlineStr"/>
+      <c r="N645" s="3" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" s="3" t="inlineStr">
@@ -33554,6 +34256,7 @@
         </is>
       </c>
       <c r="M646" s="3" t="inlineStr"/>
+      <c r="N646" s="3" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" s="3" t="inlineStr">
@@ -33601,6 +34304,7 @@
         </is>
       </c>
       <c r="M647" s="3" t="inlineStr"/>
+      <c r="N647" s="3" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" s="3" t="inlineStr">
@@ -33648,6 +34352,7 @@
         </is>
       </c>
       <c r="M648" s="3" t="inlineStr"/>
+      <c r="N648" s="3" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" s="3" t="inlineStr">
@@ -33695,6 +34400,7 @@
         </is>
       </c>
       <c r="M649" s="3" t="inlineStr"/>
+      <c r="N649" s="3" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" s="3" t="inlineStr">
@@ -33742,6 +34448,7 @@
         </is>
       </c>
       <c r="M650" s="3" t="inlineStr"/>
+      <c r="N650" s="3" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" s="3" t="inlineStr">
@@ -33789,6 +34496,7 @@
         </is>
       </c>
       <c r="M651" s="3" t="inlineStr"/>
+      <c r="N651" s="3" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" s="3" t="inlineStr">
@@ -33836,6 +34544,7 @@
         </is>
       </c>
       <c r="M652" s="3" t="inlineStr"/>
+      <c r="N652" s="3" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" s="3" t="inlineStr">
@@ -33883,6 +34592,7 @@
         </is>
       </c>
       <c r="M653" s="3" t="inlineStr"/>
+      <c r="N653" s="3" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" s="3" t="inlineStr">
@@ -33930,6 +34640,7 @@
         </is>
       </c>
       <c r="M654" s="3" t="inlineStr"/>
+      <c r="N654" s="3" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" s="3" t="inlineStr">
@@ -33977,6 +34688,7 @@
         </is>
       </c>
       <c r="M655" s="3" t="inlineStr"/>
+      <c r="N655" s="3" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="3" t="inlineStr">
@@ -34024,6 +34736,7 @@
         </is>
       </c>
       <c r="M656" s="3" t="inlineStr"/>
+      <c r="N656" s="3" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" s="3" t="inlineStr">
@@ -34071,6 +34784,7 @@
         </is>
       </c>
       <c r="M657" s="3" t="inlineStr"/>
+      <c r="N657" s="3" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" s="3" t="inlineStr">
@@ -34118,6 +34832,7 @@
         </is>
       </c>
       <c r="M658" s="3" t="inlineStr"/>
+      <c r="N658" s="3" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" s="3" t="inlineStr">
@@ -34165,6 +34880,7 @@
         </is>
       </c>
       <c r="M659" s="3" t="inlineStr"/>
+      <c r="N659" s="3" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" s="3" t="inlineStr">
@@ -34212,6 +34928,7 @@
         </is>
       </c>
       <c r="M660" s="3" t="inlineStr"/>
+      <c r="N660" s="3" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" s="3" t="inlineStr">
@@ -34259,6 +34976,7 @@
         </is>
       </c>
       <c r="M661" s="3" t="inlineStr"/>
+      <c r="N661" s="3" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" s="3" t="inlineStr">
@@ -34306,6 +35024,7 @@
         </is>
       </c>
       <c r="M662" s="3" t="inlineStr"/>
+      <c r="N662" s="3" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" s="3" t="inlineStr">
@@ -34353,6 +35072,7 @@
         </is>
       </c>
       <c r="M663" s="3" t="inlineStr"/>
+      <c r="N663" s="3" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" s="3" t="inlineStr">
@@ -34400,6 +35120,7 @@
         </is>
       </c>
       <c r="M664" s="3" t="inlineStr"/>
+      <c r="N664" s="3" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" s="3" t="inlineStr">
@@ -34447,6 +35168,7 @@
         </is>
       </c>
       <c r="M665" s="3" t="inlineStr"/>
+      <c r="N665" s="3" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" s="3" t="inlineStr">
@@ -34494,6 +35216,7 @@
         </is>
       </c>
       <c r="M666" s="3" t="inlineStr"/>
+      <c r="N666" s="3" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" s="3" t="inlineStr">
@@ -34541,6 +35264,7 @@
         </is>
       </c>
       <c r="M667" s="3" t="inlineStr"/>
+      <c r="N667" s="3" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" s="3" t="inlineStr">
@@ -34588,6 +35312,7 @@
         </is>
       </c>
       <c r="M668" s="3" t="inlineStr"/>
+      <c r="N668" s="3" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" s="3" t="inlineStr">
@@ -34635,6 +35360,7 @@
         </is>
       </c>
       <c r="M669" s="3" t="inlineStr"/>
+      <c r="N669" s="3" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" s="3" t="inlineStr">
@@ -34682,6 +35408,7 @@
         </is>
       </c>
       <c r="M670" s="3" t="inlineStr"/>
+      <c r="N670" s="3" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" s="3" t="inlineStr">
@@ -34729,6 +35456,7 @@
         </is>
       </c>
       <c r="M671" s="3" t="inlineStr"/>
+      <c r="N671" s="3" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="3" t="inlineStr">
@@ -34776,6 +35504,7 @@
         </is>
       </c>
       <c r="M672" s="3" t="inlineStr"/>
+      <c r="N672" s="3" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="3" t="inlineStr">
@@ -34823,6 +35552,7 @@
         </is>
       </c>
       <c r="M673" s="3" t="inlineStr"/>
+      <c r="N673" s="3" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" s="3" t="inlineStr">
@@ -34870,6 +35600,7 @@
         </is>
       </c>
       <c r="M674" s="3" t="inlineStr"/>
+      <c r="N674" s="3" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" s="3" t="inlineStr">
@@ -34917,6 +35648,7 @@
         </is>
       </c>
       <c r="M675" s="3" t="inlineStr"/>
+      <c r="N675" s="3" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" s="3" t="inlineStr">
@@ -34964,6 +35696,7 @@
         </is>
       </c>
       <c r="M676" s="3" t="inlineStr"/>
+      <c r="N676" s="3" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" s="3" t="inlineStr">
@@ -35011,6 +35744,7 @@
         </is>
       </c>
       <c r="M677" s="3" t="inlineStr"/>
+      <c r="N677" s="3" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" s="3" t="inlineStr">
@@ -35058,6 +35792,7 @@
         </is>
       </c>
       <c r="M678" s="3" t="inlineStr"/>
+      <c r="N678" s="3" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" s="3" t="inlineStr">
@@ -35105,6 +35840,7 @@
         </is>
       </c>
       <c r="M679" s="3" t="inlineStr"/>
+      <c r="N679" s="3" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" s="3" t="inlineStr">
@@ -35152,6 +35888,7 @@
         </is>
       </c>
       <c r="M680" s="3" t="inlineStr"/>
+      <c r="N680" s="3" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" s="3" t="inlineStr">
@@ -35199,6 +35936,7 @@
         </is>
       </c>
       <c r="M681" s="3" t="inlineStr"/>
+      <c r="N681" s="3" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" s="3" t="inlineStr">
@@ -35246,6 +35984,7 @@
         </is>
       </c>
       <c r="M682" s="3" t="inlineStr"/>
+      <c r="N682" s="3" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" s="3" t="inlineStr">
@@ -35293,6 +36032,7 @@
         </is>
       </c>
       <c r="M683" s="3" t="inlineStr"/>
+      <c r="N683" s="3" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" s="3" t="inlineStr">
@@ -35340,6 +36080,7 @@
         </is>
       </c>
       <c r="M684" s="3" t="inlineStr"/>
+      <c r="N684" s="3" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" s="3" t="inlineStr">
@@ -35387,6 +36128,7 @@
         </is>
       </c>
       <c r="M685" s="3" t="inlineStr"/>
+      <c r="N685" s="3" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" s="3" t="inlineStr">
@@ -35434,6 +36176,7 @@
         </is>
       </c>
       <c r="M686" s="3" t="inlineStr"/>
+      <c r="N686" s="3" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" s="3" t="inlineStr">
@@ -35484,7 +36227,8 @@
           <t>Ø 18.5 m, Tiefe 0.77 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M687" s="3" t="inlineStr">
+      <c r="M687" s="3" t="inlineStr"/>
+      <c r="N687" s="3" t="inlineStr">
         <is>
           <t>w136072916</t>
         </is>
@@ -35539,7 +36283,8 @@
           <t>Ø 11.0 m, Tiefe 1.55 m, Form deutlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M688" s="3" t="inlineStr">
+      <c r="M688" s="3" t="inlineStr"/>
+      <c r="N688" s="3" t="inlineStr">
         <is>
           <t>w1548447422</t>
         </is>
@@ -35591,6 +36336,7 @@
         </is>
       </c>
       <c r="M689" s="3" t="inlineStr"/>
+      <c r="N689" s="3" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" s="3" t="inlineStr">
@@ -35638,6 +36384,7 @@
         </is>
       </c>
       <c r="M690" s="3" t="inlineStr"/>
+      <c r="N690" s="3" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" s="3" t="inlineStr">
@@ -35685,6 +36432,7 @@
         </is>
       </c>
       <c r="M691" s="3" t="inlineStr"/>
+      <c r="N691" s="3" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" s="3" t="inlineStr">
@@ -35732,6 +36480,7 @@
         </is>
       </c>
       <c r="M692" s="3" t="inlineStr"/>
+      <c r="N692" s="3" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" s="3" t="inlineStr">
@@ -35779,6 +36528,7 @@
         </is>
       </c>
       <c r="M693" s="3" t="inlineStr"/>
+      <c r="N693" s="3" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" s="3" t="inlineStr">
@@ -35826,6 +36576,7 @@
         </is>
       </c>
       <c r="M694" s="3" t="inlineStr"/>
+      <c r="N694" s="3" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" s="3" t="inlineStr">
@@ -35873,6 +36624,7 @@
         </is>
       </c>
       <c r="M695" s="3" t="inlineStr"/>
+      <c r="N695" s="3" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" s="3" t="inlineStr">
@@ -35920,6 +36672,7 @@
         </is>
       </c>
       <c r="M696" s="3" t="inlineStr"/>
+      <c r="N696" s="3" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" s="3" t="inlineStr">
@@ -35967,6 +36720,7 @@
         </is>
       </c>
       <c r="M697" s="3" t="inlineStr"/>
+      <c r="N697" s="3" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" s="3" t="inlineStr">
@@ -36014,6 +36768,7 @@
         </is>
       </c>
       <c r="M698" s="3" t="inlineStr"/>
+      <c r="N698" s="3" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" s="3" t="inlineStr">
@@ -36061,6 +36816,7 @@
         </is>
       </c>
       <c r="M699" s="3" t="inlineStr"/>
+      <c r="N699" s="3" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" s="3" t="inlineStr">
@@ -36108,6 +36864,7 @@
         </is>
       </c>
       <c r="M700" s="3" t="inlineStr"/>
+      <c r="N700" s="3" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" s="3" t="inlineStr">
@@ -36155,6 +36912,7 @@
         </is>
       </c>
       <c r="M701" s="3" t="inlineStr"/>
+      <c r="N701" s="3" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" s="3" t="inlineStr">
@@ -36202,6 +36960,7 @@
         </is>
       </c>
       <c r="M702" s="3" t="inlineStr"/>
+      <c r="N702" s="3" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" s="3" t="inlineStr">
@@ -36249,6 +37008,7 @@
         </is>
       </c>
       <c r="M703" s="3" t="inlineStr"/>
+      <c r="N703" s="3" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" s="3" t="inlineStr">
@@ -36296,6 +37056,7 @@
         </is>
       </c>
       <c r="M704" s="3" t="inlineStr"/>
+      <c r="N704" s="3" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" s="3" t="inlineStr">
@@ -36342,7 +37103,8 @@
           <t>Ø 12.0 m, Tiefe 0.78 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M705" s="3" t="inlineStr">
+      <c r="M705" s="3" t="inlineStr"/>
+      <c r="N705" s="3" t="inlineStr">
         <is>
           <t>w377900235</t>
         </is>
@@ -36394,6 +37156,7 @@
         </is>
       </c>
       <c r="M706" s="3" t="inlineStr"/>
+      <c r="N706" s="3" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" s="3" t="inlineStr">
@@ -36441,6 +37204,7 @@
         </is>
       </c>
       <c r="M707" s="3" t="inlineStr"/>
+      <c r="N707" s="3" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" s="3" t="inlineStr">
@@ -36488,6 +37252,7 @@
         </is>
       </c>
       <c r="M708" s="3" t="inlineStr"/>
+      <c r="N708" s="3" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" s="3" t="inlineStr">
@@ -36535,6 +37300,7 @@
         </is>
       </c>
       <c r="M709" s="3" t="inlineStr"/>
+      <c r="N709" s="3" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" s="3" t="inlineStr">
@@ -36581,7 +37347,8 @@
           <t>Ø 16.5 m, Tiefe 0.88 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M710" s="3" t="inlineStr">
+      <c r="M710" s="3" t="inlineStr"/>
+      <c r="N710" s="3" t="inlineStr">
         <is>
           <t>w377900231</t>
         </is>
@@ -36633,6 +37400,7 @@
         </is>
       </c>
       <c r="M711" s="3" t="inlineStr"/>
+      <c r="N711" s="3" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" s="3" t="inlineStr">
@@ -36680,6 +37448,7 @@
         </is>
       </c>
       <c r="M712" s="3" t="inlineStr"/>
+      <c r="N712" s="3" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" s="3" t="inlineStr">
@@ -36727,6 +37496,7 @@
         </is>
       </c>
       <c r="M713" s="3" t="inlineStr"/>
+      <c r="N713" s="3" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" s="3" t="inlineStr">
@@ -36774,6 +37544,7 @@
         </is>
       </c>
       <c r="M714" s="3" t="inlineStr"/>
+      <c r="N714" s="3" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" s="3" t="inlineStr">
@@ -36821,6 +37592,7 @@
         </is>
       </c>
       <c r="M715" s="3" t="inlineStr"/>
+      <c r="N715" s="3" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" s="3" t="inlineStr">
@@ -36868,6 +37640,7 @@
         </is>
       </c>
       <c r="M716" s="3" t="inlineStr"/>
+      <c r="N716" s="3" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" s="3" t="inlineStr">
@@ -36915,6 +37688,7 @@
         </is>
       </c>
       <c r="M717" s="3" t="inlineStr"/>
+      <c r="N717" s="3" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" s="3" t="inlineStr">
@@ -36962,6 +37736,7 @@
         </is>
       </c>
       <c r="M718" s="3" t="inlineStr"/>
+      <c r="N718" s="3" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" s="3" t="inlineStr">
@@ -37009,6 +37784,7 @@
         </is>
       </c>
       <c r="M719" s="3" t="inlineStr"/>
+      <c r="N719" s="3" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" s="3" t="inlineStr">
@@ -37056,6 +37832,7 @@
         </is>
       </c>
       <c r="M720" s="3" t="inlineStr"/>
+      <c r="N720" s="3" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" s="3" t="inlineStr">
@@ -37103,6 +37880,7 @@
         </is>
       </c>
       <c r="M721" s="3" t="inlineStr"/>
+      <c r="N721" s="3" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" s="3" t="inlineStr">
@@ -37150,6 +37928,7 @@
         </is>
       </c>
       <c r="M722" s="3" t="inlineStr"/>
+      <c r="N722" s="3" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" s="3" t="inlineStr">
@@ -37197,6 +37976,7 @@
         </is>
       </c>
       <c r="M723" s="3" t="inlineStr"/>
+      <c r="N723" s="3" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" s="3" t="inlineStr">
@@ -37244,6 +38024,7 @@
         </is>
       </c>
       <c r="M724" s="3" t="inlineStr"/>
+      <c r="N724" s="3" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" s="3" t="inlineStr">
@@ -37291,6 +38072,7 @@
         </is>
       </c>
       <c r="M725" s="3" t="inlineStr"/>
+      <c r="N725" s="3" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" s="3" t="inlineStr">
@@ -37338,6 +38120,7 @@
         </is>
       </c>
       <c r="M726" s="3" t="inlineStr"/>
+      <c r="N726" s="3" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" s="3" t="inlineStr">
@@ -37385,6 +38168,7 @@
         </is>
       </c>
       <c r="M727" s="3" t="inlineStr"/>
+      <c r="N727" s="3" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" s="3" t="inlineStr">
@@ -37432,6 +38216,7 @@
         </is>
       </c>
       <c r="M728" s="3" t="inlineStr"/>
+      <c r="N728" s="3" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" s="3" t="inlineStr">
@@ -37479,6 +38264,7 @@
         </is>
       </c>
       <c r="M729" s="3" t="inlineStr"/>
+      <c r="N729" s="3" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" s="3" t="inlineStr">
@@ -37526,6 +38312,7 @@
         </is>
       </c>
       <c r="M730" s="3" t="inlineStr"/>
+      <c r="N730" s="3" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" s="3" t="inlineStr">
@@ -37573,6 +38360,7 @@
         </is>
       </c>
       <c r="M731" s="3" t="inlineStr"/>
+      <c r="N731" s="3" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" s="3" t="inlineStr">
@@ -37620,6 +38408,7 @@
         </is>
       </c>
       <c r="M732" s="3" t="inlineStr"/>
+      <c r="N732" s="3" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" s="3" t="inlineStr">
@@ -37667,6 +38456,7 @@
         </is>
       </c>
       <c r="M733" s="3" t="inlineStr"/>
+      <c r="N733" s="3" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" s="3" t="inlineStr">
@@ -37714,6 +38504,7 @@
         </is>
       </c>
       <c r="M734" s="3" t="inlineStr"/>
+      <c r="N734" s="3" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" s="3" t="inlineStr">
@@ -37761,6 +38552,7 @@
         </is>
       </c>
       <c r="M735" s="3" t="inlineStr"/>
+      <c r="N735" s="3" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" s="3" t="inlineStr">
@@ -37808,6 +38600,7 @@
         </is>
       </c>
       <c r="M736" s="3" t="inlineStr"/>
+      <c r="N736" s="3" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" s="3" t="inlineStr">
@@ -37855,6 +38648,7 @@
         </is>
       </c>
       <c r="M737" s="3" t="inlineStr"/>
+      <c r="N737" s="3" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" s="3" t="inlineStr">
@@ -37902,6 +38696,7 @@
         </is>
       </c>
       <c r="M738" s="3" t="inlineStr"/>
+      <c r="N738" s="3" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" s="3" t="inlineStr">
@@ -37949,6 +38744,7 @@
         </is>
       </c>
       <c r="M739" s="3" t="inlineStr"/>
+      <c r="N739" s="3" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="3" t="inlineStr">
@@ -37996,6 +38792,7 @@
         </is>
       </c>
       <c r="M740" s="3" t="inlineStr"/>
+      <c r="N740" s="3" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" s="3" t="inlineStr">
@@ -38043,6 +38840,7 @@
         </is>
       </c>
       <c r="M741" s="3" t="inlineStr"/>
+      <c r="N741" s="3" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" s="3" t="inlineStr">
@@ -38090,6 +38888,7 @@
         </is>
       </c>
       <c r="M742" s="3" t="inlineStr"/>
+      <c r="N742" s="3" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" s="3" t="inlineStr">
@@ -38137,6 +38936,7 @@
         </is>
       </c>
       <c r="M743" s="3" t="inlineStr"/>
+      <c r="N743" s="3" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" s="3" t="inlineStr">
@@ -38184,6 +38984,7 @@
         </is>
       </c>
       <c r="M744" s="3" t="inlineStr"/>
+      <c r="N744" s="3" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" s="3" t="inlineStr">
@@ -38231,6 +39032,7 @@
         </is>
       </c>
       <c r="M745" s="3" t="inlineStr"/>
+      <c r="N745" s="3" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" s="3" t="inlineStr">
@@ -38278,6 +39080,7 @@
         </is>
       </c>
       <c r="M746" s="3" t="inlineStr"/>
+      <c r="N746" s="3" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" s="3" t="inlineStr">
@@ -38325,6 +39128,7 @@
         </is>
       </c>
       <c r="M747" s="3" t="inlineStr"/>
+      <c r="N747" s="3" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" s="3" t="inlineStr">
@@ -38372,6 +39176,7 @@
         </is>
       </c>
       <c r="M748" s="3" t="inlineStr"/>
+      <c r="N748" s="3" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" s="3" t="inlineStr">
@@ -38419,6 +39224,7 @@
         </is>
       </c>
       <c r="M749" s="3" t="inlineStr"/>
+      <c r="N749" s="3" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" s="3" t="inlineStr">
@@ -38466,6 +39272,7 @@
         </is>
       </c>
       <c r="M750" s="3" t="inlineStr"/>
+      <c r="N750" s="3" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" s="3" t="inlineStr">
@@ -38513,6 +39320,7 @@
         </is>
       </c>
       <c r="M751" s="3" t="inlineStr"/>
+      <c r="N751" s="3" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" s="3" t="inlineStr">
@@ -38560,6 +39368,7 @@
         </is>
       </c>
       <c r="M752" s="3" t="inlineStr"/>
+      <c r="N752" s="3" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" s="3" t="inlineStr">
@@ -38607,6 +39416,7 @@
         </is>
       </c>
       <c r="M753" s="3" t="inlineStr"/>
+      <c r="N753" s="3" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" s="3" t="inlineStr">
@@ -38654,6 +39464,7 @@
         </is>
       </c>
       <c r="M754" s="3" t="inlineStr"/>
+      <c r="N754" s="3" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" s="3" t="inlineStr">
@@ -38701,6 +39512,7 @@
         </is>
       </c>
       <c r="M755" s="3" t="inlineStr"/>
+      <c r="N755" s="3" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" s="3" t="inlineStr">
@@ -38751,7 +39563,8 @@
           <t>Ø 13.0 m, Tiefe 0.48 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M756" s="3" t="inlineStr">
+      <c r="M756" s="3" t="inlineStr"/>
+      <c r="N756" s="3" t="inlineStr">
         <is>
           <t>w1548444175</t>
         </is>
@@ -38806,7 +39619,8 @@
           <t>Ø 9.0 m, Tiefe 0.77 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M757" s="3" t="inlineStr">
+      <c r="M757" s="3" t="inlineStr"/>
+      <c r="N757" s="3" t="inlineStr">
         <is>
           <t>w1548447423</t>
         </is>
@@ -38857,7 +39671,8 @@
           <t>Ø 12.0 m, Tiefe 0.75 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M758" s="3" t="inlineStr">
+      <c r="M758" s="3" t="inlineStr"/>
+      <c r="N758" s="3" t="inlineStr">
         <is>
           <t>w1548447419</t>
         </is>
@@ -38908,7 +39723,8 @@
           <t>Ø 17.5 m, Tiefe 0.79 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M759" s="3" t="inlineStr">
+      <c r="M759" s="3" t="inlineStr"/>
+      <c r="N759" s="3" t="inlineStr">
         <is>
           <t>w1548447421</t>
         </is>
@@ -38960,6 +39776,7 @@
         </is>
       </c>
       <c r="M760" s="3" t="inlineStr"/>
+      <c r="N760" s="3" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" s="3" t="inlineStr">
@@ -39007,6 +39824,7 @@
         </is>
       </c>
       <c r="M761" s="3" t="inlineStr"/>
+      <c r="N761" s="3" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" s="3" t="inlineStr">
@@ -39054,6 +39872,7 @@
         </is>
       </c>
       <c r="M762" s="3" t="inlineStr"/>
+      <c r="N762" s="3" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" s="3" t="inlineStr">
@@ -39101,6 +39920,7 @@
         </is>
       </c>
       <c r="M763" s="3" t="inlineStr"/>
+      <c r="N763" s="3" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" s="3" t="inlineStr">
@@ -39148,6 +39968,7 @@
         </is>
       </c>
       <c r="M764" s="3" t="inlineStr"/>
+      <c r="N764" s="3" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" s="3" t="inlineStr">
@@ -39195,6 +40016,7 @@
         </is>
       </c>
       <c r="M765" s="3" t="inlineStr"/>
+      <c r="N765" s="3" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" s="3" t="inlineStr">
@@ -39242,6 +40064,7 @@
         </is>
       </c>
       <c r="M766" s="3" t="inlineStr"/>
+      <c r="N766" s="3" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" s="3" t="inlineStr">
@@ -39289,6 +40112,7 @@
         </is>
       </c>
       <c r="M767" s="3" t="inlineStr"/>
+      <c r="N767" s="3" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" s="3" t="inlineStr">
@@ -39336,6 +40160,7 @@
         </is>
       </c>
       <c r="M768" s="3" t="inlineStr"/>
+      <c r="N768" s="3" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" s="3" t="inlineStr">
@@ -39383,6 +40208,7 @@
         </is>
       </c>
       <c r="M769" s="3" t="inlineStr"/>
+      <c r="N769" s="3" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" s="3" t="inlineStr">
@@ -39430,6 +40256,7 @@
         </is>
       </c>
       <c r="M770" s="3" t="inlineStr"/>
+      <c r="N770" s="3" t="inlineStr"/>
     </row>
     <row r="771">
       <c r="A771" s="3" t="inlineStr">
@@ -39477,6 +40304,7 @@
         </is>
       </c>
       <c r="M771" s="3" t="inlineStr"/>
+      <c r="N771" s="3" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" s="3" t="inlineStr">
@@ -39524,6 +40352,7 @@
         </is>
       </c>
       <c r="M772" s="3" t="inlineStr"/>
+      <c r="N772" s="3" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" s="3" t="inlineStr">
@@ -39571,6 +40400,7 @@
         </is>
       </c>
       <c r="M773" s="3" t="inlineStr"/>
+      <c r="N773" s="3" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" s="3" t="inlineStr">
@@ -39618,6 +40448,7 @@
         </is>
       </c>
       <c r="M774" s="3" t="inlineStr"/>
+      <c r="N774" s="3" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" s="3" t="inlineStr">
@@ -39665,6 +40496,7 @@
         </is>
       </c>
       <c r="M775" s="3" t="inlineStr"/>
+      <c r="N775" s="3" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" s="3" t="inlineStr">
@@ -39712,6 +40544,7 @@
         </is>
       </c>
       <c r="M776" s="3" t="inlineStr"/>
+      <c r="N776" s="3" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" s="3" t="inlineStr">
@@ -39759,6 +40592,7 @@
         </is>
       </c>
       <c r="M777" s="3" t="inlineStr"/>
+      <c r="N777" s="3" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" s="3" t="inlineStr">
@@ -39806,6 +40640,7 @@
         </is>
       </c>
       <c r="M778" s="3" t="inlineStr"/>
+      <c r="N778" s="3" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" s="3" t="inlineStr">
@@ -39853,6 +40688,7 @@
         </is>
       </c>
       <c r="M779" s="3" t="inlineStr"/>
+      <c r="N779" s="3" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" s="3" t="inlineStr">
@@ -39900,6 +40736,7 @@
         </is>
       </c>
       <c r="M780" s="3" t="inlineStr"/>
+      <c r="N780" s="3" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" s="3" t="inlineStr">
@@ -39947,6 +40784,7 @@
         </is>
       </c>
       <c r="M781" s="3" t="inlineStr"/>
+      <c r="N781" s="3" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" s="3" t="inlineStr">
@@ -39994,6 +40832,7 @@
         </is>
       </c>
       <c r="M782" s="3" t="inlineStr"/>
+      <c r="N782" s="3" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" s="3" t="inlineStr">
@@ -40041,6 +40880,7 @@
         </is>
       </c>
       <c r="M783" s="3" t="inlineStr"/>
+      <c r="N783" s="3" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" s="3" t="inlineStr">
@@ -40088,6 +40928,7 @@
         </is>
       </c>
       <c r="M784" s="3" t="inlineStr"/>
+      <c r="N784" s="3" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" s="3" t="inlineStr">
@@ -40135,6 +40976,7 @@
         </is>
       </c>
       <c r="M785" s="3" t="inlineStr"/>
+      <c r="N785" s="3" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" s="3" t="inlineStr">
@@ -40182,6 +41024,7 @@
         </is>
       </c>
       <c r="M786" s="3" t="inlineStr"/>
+      <c r="N786" s="3" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" s="3" t="inlineStr">
@@ -40229,6 +41072,7 @@
         </is>
       </c>
       <c r="M787" s="3" t="inlineStr"/>
+      <c r="N787" s="3" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" s="3" t="inlineStr">
@@ -40276,6 +41120,7 @@
         </is>
       </c>
       <c r="M788" s="3" t="inlineStr"/>
+      <c r="N788" s="3" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" s="3" t="inlineStr">
@@ -40323,6 +41168,7 @@
         </is>
       </c>
       <c r="M789" s="3" t="inlineStr"/>
+      <c r="N789" s="3" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" s="3" t="inlineStr">
@@ -40370,6 +41216,7 @@
         </is>
       </c>
       <c r="M790" s="3" t="inlineStr"/>
+      <c r="N790" s="3" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" s="3" t="inlineStr">
@@ -40417,6 +41264,7 @@
         </is>
       </c>
       <c r="M791" s="3" t="inlineStr"/>
+      <c r="N791" s="3" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" s="3" t="inlineStr">
@@ -40464,6 +41312,7 @@
         </is>
       </c>
       <c r="M792" s="3" t="inlineStr"/>
+      <c r="N792" s="3" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" s="3" t="inlineStr">
@@ -40511,6 +41360,7 @@
         </is>
       </c>
       <c r="M793" s="3" t="inlineStr"/>
+      <c r="N793" s="3" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" s="3" t="inlineStr">
@@ -40558,6 +41408,7 @@
         </is>
       </c>
       <c r="M794" s="3" t="inlineStr"/>
+      <c r="N794" s="3" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" s="3" t="inlineStr">
@@ -40605,6 +41456,7 @@
         </is>
       </c>
       <c r="M795" s="3" t="inlineStr"/>
+      <c r="N795" s="3" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" s="3" t="inlineStr">
@@ -40652,6 +41504,7 @@
         </is>
       </c>
       <c r="M796" s="3" t="inlineStr"/>
+      <c r="N796" s="3" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" s="3" t="inlineStr">
@@ -40699,6 +41552,7 @@
         </is>
       </c>
       <c r="M797" s="3" t="inlineStr"/>
+      <c r="N797" s="3" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" s="3" t="inlineStr">
@@ -40746,6 +41600,7 @@
         </is>
       </c>
       <c r="M798" s="3" t="inlineStr"/>
+      <c r="N798" s="3" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" s="3" t="inlineStr">
@@ -40793,6 +41648,7 @@
         </is>
       </c>
       <c r="M799" s="3" t="inlineStr"/>
+      <c r="N799" s="3" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" s="3" t="inlineStr">
@@ -40840,6 +41696,7 @@
         </is>
       </c>
       <c r="M800" s="3" t="inlineStr"/>
+      <c r="N800" s="3" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" s="3" t="inlineStr">
@@ -40887,6 +41744,7 @@
         </is>
       </c>
       <c r="M801" s="3" t="inlineStr"/>
+      <c r="N801" s="3" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" s="3" t="inlineStr">
@@ -40934,6 +41792,7 @@
         </is>
       </c>
       <c r="M802" s="3" t="inlineStr"/>
+      <c r="N802" s="3" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" s="3" t="inlineStr">
@@ -40981,6 +41840,7 @@
         </is>
       </c>
       <c r="M803" s="3" t="inlineStr"/>
+      <c r="N803" s="3" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" s="3" t="inlineStr">
@@ -41028,6 +41888,7 @@
         </is>
       </c>
       <c r="M804" s="3" t="inlineStr"/>
+      <c r="N804" s="3" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" s="3" t="inlineStr">
@@ -41075,6 +41936,7 @@
         </is>
       </c>
       <c r="M805" s="3" t="inlineStr"/>
+      <c r="N805" s="3" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" s="3" t="inlineStr">
@@ -41122,6 +41984,7 @@
         </is>
       </c>
       <c r="M806" s="3" t="inlineStr"/>
+      <c r="N806" s="3" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" s="3" t="inlineStr">
@@ -41173,6 +42036,7 @@
         </is>
       </c>
       <c r="M807" s="3" t="inlineStr"/>
+      <c r="N807" s="3" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" s="3" t="inlineStr">
@@ -41224,6 +42088,7 @@
         </is>
       </c>
       <c r="M808" s="3" t="inlineStr"/>
+      <c r="N808" s="3" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" s="3" t="inlineStr">
@@ -41275,6 +42140,7 @@
         </is>
       </c>
       <c r="M809" s="3" t="inlineStr"/>
+      <c r="N809" s="3" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" s="3" t="inlineStr">
@@ -41326,6 +42192,7 @@
         </is>
       </c>
       <c r="M810" s="3" t="inlineStr"/>
+      <c r="N810" s="3" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" s="3" t="inlineStr">
@@ -41377,6 +42244,7 @@
         </is>
       </c>
       <c r="M811" s="3" t="inlineStr"/>
+      <c r="N811" s="3" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" s="3" t="inlineStr">
@@ -41428,6 +42296,7 @@
         </is>
       </c>
       <c r="M812" s="3" t="inlineStr"/>
+      <c r="N812" s="3" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" s="3" t="inlineStr">
@@ -41475,6 +42344,7 @@
         </is>
       </c>
       <c r="M813" s="3" t="inlineStr"/>
+      <c r="N813" s="3" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" s="3" t="inlineStr">
@@ -41522,6 +42392,7 @@
         </is>
       </c>
       <c r="M814" s="3" t="inlineStr"/>
+      <c r="N814" s="3" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" s="3" t="inlineStr">
@@ -41569,6 +42440,7 @@
         </is>
       </c>
       <c r="M815" s="3" t="inlineStr"/>
+      <c r="N815" s="3" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" s="3" t="inlineStr">
@@ -41616,6 +42488,7 @@
         </is>
       </c>
       <c r="M816" s="3" t="inlineStr"/>
+      <c r="N816" s="3" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" s="3" t="inlineStr">
@@ -41663,6 +42536,7 @@
         </is>
       </c>
       <c r="M817" s="3" t="inlineStr"/>
+      <c r="N817" s="3" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" s="3" t="inlineStr">
@@ -41710,6 +42584,7 @@
         </is>
       </c>
       <c r="M818" s="3" t="inlineStr"/>
+      <c r="N818" s="3" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" s="3" t="inlineStr">
@@ -41757,6 +42632,7 @@
         </is>
       </c>
       <c r="M819" s="3" t="inlineStr"/>
+      <c r="N819" s="3" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" s="3" t="inlineStr">
@@ -41804,6 +42680,7 @@
         </is>
       </c>
       <c r="M820" s="3" t="inlineStr"/>
+      <c r="N820" s="3" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" s="3" t="inlineStr">
@@ -41851,6 +42728,7 @@
         </is>
       </c>
       <c r="M821" s="3" t="inlineStr"/>
+      <c r="N821" s="3" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" s="3" t="inlineStr">
@@ -41898,6 +42776,7 @@
         </is>
       </c>
       <c r="M822" s="3" t="inlineStr"/>
+      <c r="N822" s="3" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" s="3" t="inlineStr">
@@ -41945,6 +42824,7 @@
         </is>
       </c>
       <c r="M823" s="3" t="inlineStr"/>
+      <c r="N823" s="3" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" s="3" t="inlineStr">
@@ -41996,6 +42876,7 @@
         </is>
       </c>
       <c r="M824" s="3" t="inlineStr"/>
+      <c r="N824" s="3" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" s="3" t="inlineStr">
@@ -42047,6 +42928,7 @@
         </is>
       </c>
       <c r="M825" s="3" t="inlineStr"/>
+      <c r="N825" s="3" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" s="3" t="inlineStr">
@@ -42098,6 +42980,7 @@
         </is>
       </c>
       <c r="M826" s="3" t="inlineStr"/>
+      <c r="N826" s="3" t="inlineStr"/>
     </row>
     <row r="827">
       <c r="A827" s="3" t="inlineStr">
@@ -42149,6 +43032,7 @@
         </is>
       </c>
       <c r="M827" s="3" t="inlineStr"/>
+      <c r="N827" s="3" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" s="3" t="inlineStr">
@@ -42200,6 +43084,7 @@
         </is>
       </c>
       <c r="M828" s="3" t="inlineStr"/>
+      <c r="N828" s="3" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" s="3" t="inlineStr">
@@ -42247,6 +43132,7 @@
         </is>
       </c>
       <c r="M829" s="3" t="inlineStr"/>
+      <c r="N829" s="3" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" s="3" t="inlineStr">
@@ -42294,6 +43180,7 @@
         </is>
       </c>
       <c r="M830" s="3" t="inlineStr"/>
+      <c r="N830" s="3" t="inlineStr"/>
     </row>
     <row r="831">
       <c r="A831" s="3" t="inlineStr">
@@ -42340,7 +43227,8 @@
           <t>Ø 15.0 m, Tiefe 0.62 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M831" s="3" t="inlineStr">
+      <c r="M831" s="3" t="inlineStr"/>
+      <c r="N831" s="3" t="inlineStr">
         <is>
           <t>w377900233</t>
         </is>
@@ -42392,6 +43280,7 @@
         </is>
       </c>
       <c r="M832" s="3" t="inlineStr"/>
+      <c r="N832" s="3" t="inlineStr"/>
     </row>
     <row r="833">
       <c r="A833" s="3" t="inlineStr">
@@ -42439,6 +43328,7 @@
         </is>
       </c>
       <c r="M833" s="3" t="inlineStr"/>
+      <c r="N833" s="3" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" s="3" t="inlineStr">
@@ -42486,6 +43376,7 @@
         </is>
       </c>
       <c r="M834" s="3" t="inlineStr"/>
+      <c r="N834" s="3" t="inlineStr"/>
     </row>
     <row r="835">
       <c r="A835" s="3" t="inlineStr">
@@ -42532,7 +43423,8 @@
           <t>Ø 16.5 m, Tiefe 0.59 m, Form wahrscheinlich, Luftbild ja</t>
         </is>
       </c>
-      <c r="M835" s="3" t="inlineStr">
+      <c r="M835" s="3" t="inlineStr"/>
+      <c r="N835" s="3" t="inlineStr">
         <is>
           <t>w377900234</t>
         </is>
@@ -42584,6 +43476,7 @@
         </is>
       </c>
       <c r="M836" s="3" t="inlineStr"/>
+      <c r="N836" s="3" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" s="3" t="inlineStr">
@@ -42635,6 +43528,7 @@
         </is>
       </c>
       <c r="M837" s="3" t="inlineStr"/>
+      <c r="N837" s="3" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" s="3" t="inlineStr">
@@ -42686,6 +43580,7 @@
         </is>
       </c>
       <c r="M838" s="3" t="inlineStr"/>
+      <c r="N838" s="3" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" s="3" t="inlineStr">
@@ -42737,6 +43632,7 @@
         </is>
       </c>
       <c r="M839" s="3" t="inlineStr"/>
+      <c r="N839" s="3" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" s="3" t="inlineStr">
@@ -42788,6 +43684,7 @@
         </is>
       </c>
       <c r="M840" s="3" t="inlineStr"/>
+      <c r="N840" s="3" t="inlineStr"/>
     </row>
     <row r="841">
       <c r="A841" s="3" t="inlineStr">
@@ -42839,6 +43736,7 @@
         </is>
       </c>
       <c r="M841" s="3" t="inlineStr"/>
+      <c r="N841" s="3" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" s="3" t="inlineStr">
@@ -42886,6 +43784,7 @@
         </is>
       </c>
       <c r="M842" s="3" t="inlineStr"/>
+      <c r="N842" s="3" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" s="3" t="inlineStr">
@@ -42937,6 +43836,7 @@
         </is>
       </c>
       <c r="M843" s="3" t="inlineStr"/>
+      <c r="N843" s="3" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" s="3" t="inlineStr">
@@ -42988,6 +43888,7 @@
         </is>
       </c>
       <c r="M844" s="3" t="inlineStr"/>
+      <c r="N844" s="3" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" s="3" t="inlineStr">
@@ -43035,6 +43936,7 @@
         </is>
       </c>
       <c r="M845" s="3" t="inlineStr"/>
+      <c r="N845" s="3" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" s="3" t="inlineStr">
@@ -43082,6 +43984,7 @@
         </is>
       </c>
       <c r="M846" s="3" t="inlineStr"/>
+      <c r="N846" s="3" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" s="3" t="inlineStr">
@@ -43133,6 +44036,7 @@
         </is>
       </c>
       <c r="M847" s="3" t="inlineStr"/>
+      <c r="N847" s="3" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" s="3" t="inlineStr">
@@ -43184,6 +44088,7 @@
         </is>
       </c>
       <c r="M848" s="3" t="inlineStr"/>
+      <c r="N848" s="3" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" s="3" t="inlineStr">
@@ -43235,6 +44140,7 @@
         </is>
       </c>
       <c r="M849" s="3" t="inlineStr"/>
+      <c r="N849" s="3" t="inlineStr"/>
     </row>
     <row r="850">
       <c r="A850" s="3" t="inlineStr">
@@ -43286,6 +44192,7 @@
         </is>
       </c>
       <c r="M850" s="3" t="inlineStr"/>
+      <c r="N850" s="3" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" s="3" t="inlineStr">
@@ -43337,6 +44244,7 @@
         </is>
       </c>
       <c r="M851" s="3" t="inlineStr"/>
+      <c r="N851" s="3" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" s="3" t="inlineStr">
@@ -43388,6 +44296,7 @@
         </is>
       </c>
       <c r="M852" s="3" t="inlineStr"/>
+      <c r="N852" s="3" t="inlineStr"/>
     </row>
     <row r="853">
       <c r="A853" s="3" t="inlineStr">
@@ -43439,6 +44348,7 @@
         </is>
       </c>
       <c r="M853" s="3" t="inlineStr"/>
+      <c r="N853" s="3" t="inlineStr"/>
     </row>
     <row r="854">
       <c r="A854" s="3" t="inlineStr">
@@ -43490,6 +44400,7 @@
         </is>
       </c>
       <c r="M854" s="3" t="inlineStr"/>
+      <c r="N854" s="3" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" s="3" t="inlineStr">
@@ -43541,6 +44452,7 @@
         </is>
       </c>
       <c r="M855" s="3" t="inlineStr"/>
+      <c r="N855" s="3" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" s="3" t="inlineStr">
@@ -43592,6 +44504,7 @@
         </is>
       </c>
       <c r="M856" s="3" t="inlineStr"/>
+      <c r="N856" s="3" t="inlineStr"/>
     </row>
     <row r="857">
       <c r="A857" s="3" t="inlineStr">
@@ -43643,6 +44556,7 @@
         </is>
       </c>
       <c r="M857" s="3" t="inlineStr"/>
+      <c r="N857" s="3" t="inlineStr"/>
     </row>
     <row r="858">
       <c r="A858" s="3" t="inlineStr">
@@ -43694,6 +44608,7 @@
         </is>
       </c>
       <c r="M858" s="3" t="inlineStr"/>
+      <c r="N858" s="3" t="inlineStr"/>
     </row>
     <row r="859">
       <c r="A859" s="3" t="inlineStr">
@@ -43745,6 +44660,7 @@
         </is>
       </c>
       <c r="M859" s="3" t="inlineStr"/>
+      <c r="N859" s="3" t="inlineStr"/>
     </row>
     <row r="860">
       <c r="A860" s="3" t="inlineStr">
@@ -43796,6 +44712,7 @@
         </is>
       </c>
       <c r="M860" s="3" t="inlineStr"/>
+      <c r="N860" s="3" t="inlineStr"/>
     </row>
     <row r="861">
       <c r="A861" s="3" t="inlineStr">
@@ -43838,7 +44755,8 @@
       </c>
       <c r="K861" s="3" t="inlineStr"/>
       <c r="L861" s="3" t="inlineStr"/>
-      <c r="M861" s="3" t="inlineStr">
+      <c r="M861" s="3" t="inlineStr"/>
+      <c r="N861" s="3" t="inlineStr">
         <is>
           <t>n14017286988</t>
         </is>
@@ -43889,7 +44807,8 @@
       </c>
       <c r="K862" s="3" t="inlineStr"/>
       <c r="L862" s="3" t="inlineStr"/>
-      <c r="M862" s="3" t="inlineStr">
+      <c r="M862" s="3" t="inlineStr"/>
+      <c r="N862" s="3" t="inlineStr">
         <is>
           <t>w1548797258</t>
         </is>
@@ -43940,7 +44859,8 @@
       </c>
       <c r="K863" s="3" t="inlineStr"/>
       <c r="L863" s="3" t="inlineStr"/>
-      <c r="M863" s="3" t="inlineStr">
+      <c r="M863" s="3" t="inlineStr"/>
+      <c r="N863" s="3" t="inlineStr">
         <is>
           <t>w48648249</t>
         </is>
@@ -43991,7 +44911,8 @@
       </c>
       <c r="K864" s="3" t="inlineStr"/>
       <c r="L864" s="3" t="inlineStr"/>
-      <c r="M864" s="3" t="inlineStr">
+      <c r="M864" s="3" t="inlineStr"/>
+      <c r="N864" s="3" t="inlineStr">
         <is>
           <t>w139548406</t>
         </is>
@@ -44042,7 +44963,8 @@
       </c>
       <c r="K865" s="3" t="inlineStr"/>
       <c r="L865" s="3" t="inlineStr"/>
-      <c r="M865" s="3" t="inlineStr">
+      <c r="M865" s="3" t="inlineStr"/>
+      <c r="N865" s="3" t="inlineStr">
         <is>
           <t>w139548394</t>
         </is>
@@ -44093,7 +45015,8 @@
       </c>
       <c r="K866" s="3" t="inlineStr"/>
       <c r="L866" s="3" t="inlineStr"/>
-      <c r="M866" s="3" t="inlineStr">
+      <c r="M866" s="3" t="inlineStr"/>
+      <c r="N866" s="3" t="inlineStr">
         <is>
           <t>w139548391</t>
         </is>
@@ -44144,7 +45067,8 @@
       </c>
       <c r="K867" s="3" t="inlineStr"/>
       <c r="L867" s="3" t="inlineStr"/>
-      <c r="M867" s="3" t="inlineStr">
+      <c r="M867" s="3" t="inlineStr"/>
+      <c r="N867" s="3" t="inlineStr">
         <is>
           <t>w48648250</t>
         </is>
@@ -44195,7 +45119,8 @@
       </c>
       <c r="K868" s="3" t="inlineStr"/>
       <c r="L868" s="3" t="inlineStr"/>
-      <c r="M868" s="3" t="inlineStr">
+      <c r="M868" s="3" t="inlineStr"/>
+      <c r="N868" s="3" t="inlineStr">
         <is>
           <t>w48648252</t>
         </is>
@@ -44250,7 +45175,8 @@
           <t>Start</t>
         </is>
       </c>
-      <c r="M869" s="3" t="inlineStr">
+      <c r="M869" s="3" t="inlineStr"/>
+      <c r="N869" s="3" t="inlineStr">
         <is>
           <t>r5634075</t>
         </is>
@@ -44301,7 +45227,8 @@
       </c>
       <c r="K870" s="3" t="inlineStr"/>
       <c r="L870" s="3" t="inlineStr"/>
-      <c r="M870" s="3" t="inlineStr">
+      <c r="M870" s="3" t="inlineStr"/>
+      <c r="N870" s="3" t="inlineStr">
         <is>
           <t>w118083430</t>
         </is>
@@ -44352,7 +45279,8 @@
       </c>
       <c r="K871" s="3" t="inlineStr"/>
       <c r="L871" s="3" t="inlineStr"/>
-      <c r="M871" s="3" t="inlineStr">
+      <c r="M871" s="3" t="inlineStr"/>
+      <c r="N871" s="3" t="inlineStr">
         <is>
           <t>n9864435717</t>
         </is>
@@ -44403,7 +45331,8 @@
       </c>
       <c r="K872" s="3" t="inlineStr"/>
       <c r="L872" s="3" t="inlineStr"/>
-      <c r="M872" s="3" t="inlineStr">
+      <c r="M872" s="3" t="inlineStr"/>
+      <c r="N872" s="3" t="inlineStr">
         <is>
           <t>n282494436</t>
         </is>
@@ -44454,7 +45383,8 @@
           <t>2.03 ha</t>
         </is>
       </c>
-      <c r="M873" s="3" t="inlineStr">
+      <c r="M873" s="3" t="inlineStr"/>
+      <c r="N873" s="3" t="inlineStr">
         <is>
           <t>w135035484</t>
         </is>
@@ -44505,7 +45435,8 @@
           <t>0.99 ha</t>
         </is>
       </c>
-      <c r="M874" s="3" t="inlineStr">
+      <c r="M874" s="3" t="inlineStr"/>
+      <c r="N874" s="3" t="inlineStr">
         <is>
           <t>w135035483</t>
         </is>
@@ -44556,7 +45487,8 @@
           <t>0.18 ha</t>
         </is>
       </c>
-      <c r="M875" s="3" t="inlineStr">
+      <c r="M875" s="3" t="inlineStr"/>
+      <c r="N875" s="3" t="inlineStr">
         <is>
           <t>w1310761606</t>
         </is>
@@ -44607,7 +45539,8 @@
           <t>0.07 ha</t>
         </is>
       </c>
-      <c r="M876" s="3" t="inlineStr">
+      <c r="M876" s="3" t="inlineStr"/>
+      <c r="N876" s="3" t="inlineStr">
         <is>
           <t>w137468160</t>
         </is>
@@ -44658,7 +45591,8 @@
           <t>2.56 ha</t>
         </is>
       </c>
-      <c r="M877" s="3" t="inlineStr">
+      <c r="M877" s="3" t="inlineStr"/>
+      <c r="N877" s="3" t="inlineStr">
         <is>
           <t>w118083431</t>
         </is>
@@ -44713,7 +45647,8 @@
           <t>Kilometerstein Inselbahn, km 0,6</t>
         </is>
       </c>
-      <c r="M878" s="3" t="inlineStr">
+      <c r="M878" s="3" t="inlineStr"/>
+      <c r="N878" s="3" t="inlineStr">
         <is>
           <t>n1957257831</t>
         </is>
@@ -44768,7 +45703,8 @@
           <t>Kilometerstein Inselbahn, km 0,4</t>
         </is>
       </c>
-      <c r="M879" s="3" t="inlineStr">
+      <c r="M879" s="3" t="inlineStr"/>
+      <c r="N879" s="3" t="inlineStr">
         <is>
           <t>n12628336841</t>
         </is>
@@ -44827,7 +45763,8 @@
           <t>Kilometerstein Inselbahn, km 2,0</t>
         </is>
       </c>
-      <c r="M880" s="3" t="inlineStr">
+      <c r="M880" s="3" t="inlineStr"/>
+      <c r="N880" s="3" t="inlineStr">
         <is>
           <t>n12628336840</t>
         </is>
@@ -44886,7 +45823,8 @@
           <t>Kilometerstein Inselbahn, km 2,2</t>
         </is>
       </c>
-      <c r="M881" s="3" t="inlineStr">
+      <c r="M881" s="3" t="inlineStr"/>
+      <c r="N881" s="3" t="inlineStr">
         <is>
           <t>n12628336839</t>
         </is>
@@ -44945,7 +45883,8 @@
           <t>Kilometerstein Inselbahn, km 2,4</t>
         </is>
       </c>
-      <c r="M882" s="3" t="inlineStr">
+      <c r="M882" s="3" t="inlineStr"/>
+      <c r="N882" s="3" t="inlineStr">
         <is>
           <t>n12628336838</t>
         </is>
@@ -45004,7 +45943,8 @@
           <t>Kilometerstein Inselbahn, km 2,8</t>
         </is>
       </c>
-      <c r="M883" s="3" t="inlineStr">
+      <c r="M883" s="3" t="inlineStr"/>
+      <c r="N883" s="3" t="inlineStr">
         <is>
           <t>n12628336837</t>
         </is>
@@ -45063,7 +46003,8 @@
           <t>Kilometerstein Inselbahn, km 3,0</t>
         </is>
       </c>
-      <c r="M884" s="3" t="inlineStr">
+      <c r="M884" s="3" t="inlineStr"/>
+      <c r="N884" s="3" t="inlineStr">
         <is>
           <t>n12628336835</t>
         </is>
@@ -45122,15 +46063,16 @@
           <t>Kilometerstein Inselbahn, km 3,2</t>
         </is>
       </c>
-      <c r="M885" s="3" t="inlineStr">
+      <c r="M885" s="3" t="inlineStr"/>
+      <c r="N885" s="3" t="inlineStr">
         <is>
           <t>n12628336842</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M885"/>
-  <conditionalFormatting sqref="A2:M885">
+  <autoFilter ref="A1:N885"/>
+  <conditionalFormatting sqref="A2:N885">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E2="prüfen"</formula>
     </cfRule>
@@ -45187,7 +46129,11 @@
           <t>footway</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Fußweg (Erde), ca. 340 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 29 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45205,7 +46151,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Erde), ca. 100 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 15 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45223,7 +46173,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Gras), ca. 30 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 20 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45241,7 +46195,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Gras), ca. 190 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 35 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45259,7 +46217,11 @@
           <t>footway</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Fußweg, ca. 50 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 37 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45277,7 +46239,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Erde), ca. 40 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 23 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45295,7 +46261,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Sand), ca. 1310 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 31 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45313,7 +46283,11 @@
           <t>footway</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Fußweg, ca. 70 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 40 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45331,7 +46305,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Sand), ca. 10 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 43 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45349,7 +46327,11 @@
           <t>footway</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Fußweg, ca. 50 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 31 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45367,7 +46349,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Gras), ca. 100 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 5 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45385,7 +46371,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Sand), ca. 50 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 2 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45403,7 +46393,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Erde), ca. 20 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 24 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45421,7 +46415,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Erde), ca. 50 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 35 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45439,7 +46437,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Sand), ca. 150 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 34 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45457,7 +46459,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Erde), ca. 70 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 19 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45475,7 +46481,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Erde), ca. 250 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 41 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45493,7 +46503,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Gras), ca. 50 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 7 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45511,7 +46525,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Pfad, ca. 80 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 35 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45529,7 +46547,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Gras), ca. 150 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 29 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45547,7 +46569,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Erde), ca. 220 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 42 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45565,7 +46591,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Pfad, ca. 160 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 42 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45583,7 +46613,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Sand), ca. 30 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 8 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
@@ -45601,7 +46635,11 @@
           <t>path</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Pfad (Gras), ca. 60 m. Noch begehbar? Im Luftbild kaum sichtbar (auf 34 % der Strecke).</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
           <t>OSM; im Luftbild kaum sichtbar</t>
